--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="6090" yWindow="120" windowWidth="17940" windowHeight="7890"/>
+    <workbookView xWindow="6090" yWindow="120" windowWidth="14400" windowHeight="7890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$82</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -24,6 +24,86 @@
     <author>Author</author>
   </authors>
   <commentList>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+attach</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>和</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>detach</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>节点</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+编目组在每个故障场景都考虑
+节点交叉在各个场景测试</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G3" authorId="0">
       <text>
         <r>
@@ -50,12 +130,293 @@
         </r>
       </text>
     </comment>
+    <comment ref="F4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+目标主机</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CM</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>断网（创建</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>RG</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>所在主机断网）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+两个备节点断网
+一个备节点断网没有意义
+删除组之前需要先一个个删除节点？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+两个备节点断网
+一个备节点断网没有意义
+删除组之前需要先一个个删除节点？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D51" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+考虑编目、目标节点和处理节点，</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CPU</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>和内存交叉考虑
+协调节点抽测一个</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D64" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+CPU</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>和内存交叉考虑</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F103" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+catalog主节点所在主机内磁盘满，需要针对每个类型的节点和组</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F116" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+灌数据的时候添加节点
+同时往不同的组添加节点
+并发添加多个协调节点
+并发attach、detach</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A128" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+需要考虑编目、协调、数据节点主机异常重启（目标主机）</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="173">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -85,10 +446,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不考虑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>集群管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -121,10 +478,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>磁盘损坏（低优先级）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>umount盘（低优先级）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -133,10 +486,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>组合异常(包括同一异常多次出现)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>网络拥塞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -149,10 +498,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM所在主机断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>catalog备节点异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,27 +525,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>coordRG（协调组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cataRG（编目组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>删除cataRG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dataRG（数据组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>创建dataRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -294,10 +623,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>目标节点所在主机CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>操作过程中异常，节点启动成功/失败；
 故障恢复后重启节点，节点运行正常；连接coord对节点数据做基本操作，操作成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -311,38 +636,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>目标节点所在主机内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标节点所在主机时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>coord处理节点所在主机时间跳变</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>源节点所在主机CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标节点所在主机CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标节点所在主机内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源节点所在主机内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源节点所在主机时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>磁盘满</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -351,18 +648,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>目标节点所在主机磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源节点所在主机内磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>并发创建多个dataRG和dataNode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>重复多次启停coord主节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -391,15 +676,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同断网
-不同点：主节点闪断时间小于7s操作成功；超过7s重新选主，选主后各节点数据完整一致；对数据节点做CL等基本操作，操作成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM所在主机断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CM跟coord处理节点不在同一个主机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -412,11 +688,168 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM所在主机断网（一个主机）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM正在重启/异常停止</t>
+    <t>CM异常停止（kill -9）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复多次创建删除不同coord组和节点/catalog组和节点/dataRG和节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启停节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间跳变+catalog主节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反复多次启停coord节点、catalog节点、dataRG节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改一个主机的hostname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点连续降备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除成功；故障恢复后各个节点数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>少于(n+1/2)个catalog备节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超过(n+1/2)个catalog备节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除失败；故障恢复后再次创建/删除成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作过程中异常，cataRG创建失败；故障恢复后创建成功的cataRG正常可用，在cataRG创建catalog节点创建成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新选主，catalog节点删除成功；故障恢复后各节点数据一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM断网操作失败；故障恢复后可以再次创建组，创建后组可用（如在组内增删节点）；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM断网操作失败；故障恢复后可以再次删除组，删除成功，删除后可以再次创建；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM断网操作失败；故障恢复后可以再次删除节点，删除成功，删除后可以再次创建；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动catalog节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新选主，catalog节点启动成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM断网操作失败；故障恢复后可以再次启动节点，节点启动后正常可用；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM断网操作失败；故障恢复后查看该节点可用继续使用；重启节点，节点可用；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新选主，catalog节点创建成功；故障恢复后各节点数据一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM断网操作失败；故障恢复后可以再次创建节点；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ulimit配置异常(堆栈、句柄、线程数、虚存)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建节点组和节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程退出，操作失败；CM重启完成后可以继续创建/删除节点组和节点；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程退出，操作失败；CM重启完成后可以继续创建/删除节点组和节点，节点可以正常使用；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作失败；故障恢复后可以继续创建/删除节点组和节点，节点可以正常使用；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM跟该主机通信失败，操作失败；故障恢复后主机可以正常连接，节点间信息正常同步，同步后数据完整一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同闪断
+不同点：普通拥塞，操作成功；消息拥塞超过x重新选主，选主后各节点数据完整一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建coord节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cataRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机内磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批量创建多个dataRG和dataNode</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -424,91 +857,212 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM异常停止（kill -9）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复多次创建删除不同coord组和节点/catalog组和节点/dataRG和节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启停节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM正在重启/异常停止</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间跳变+catalog主节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建/删除节点组合节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反复多次启停coord节点、catalog节点、dataRG节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机hostname更改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改一个主机的hostname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点连续降备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建/删除成功；故障恢复后各个节点数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>少于(n+1/2)个catalog备节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>超过(n+1/2)个catalog备节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建/删除失败；故障恢复后再次创建/删除成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作过程中异常，cataRG创建失败；故障恢复后创建成功的cataRG正常可用，在cataRG创建catalog节点创建成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作过程中异常，cataRG删除成功/失败；故障恢复后删除成功的cataRG不存在；删除失败可以再次删除（删除失败是否需要考虑可用性？）；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重新选主，catalog节点删除成功；故障恢复后各节点数据一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM断网操作失败；故障恢复后可以再次创建组，创建后组可用（如在组内增删节点）；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM断网操作失败；故障恢复后可以再次删除组，删除成功，删除后可以再次创建；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建catalog（编目节点）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord处理节点断网</t>
+    <t>主机hostname/IP更改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM异常停止（kill -9 kill -15重复操作）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog 2个备节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3g3h3d时2个备节点异常，主节点降备，删除cataRG失败；故障恢复后重新选主，重新删除cataRG可以删除成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机CM断网</t>
+  </si>
+  <si>
+    <t>编目信息同步，检查同步信息跟其他节点一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机CM断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3g3h3d时2个备节点异常，主节点降备，删除dataRG失败；故障恢复后重新选主，重新删除dataRG可以删除成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM所在主机网络断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除coord节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cataRG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的测试点在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>网络闪断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故障场景覆盖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止dataNode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>停止</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>catalog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的测试点在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>网络闪断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故障场景覆盖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dataRG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的测试点在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>断网</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故障场景覆盖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作过程中异常，cataRG删除成功/失败；故障恢复后删除成功的cataRG不存在；删除失败可以再次删除；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新选主，coord节点删除成功；故障恢复后各节点数据一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除dataNode（数据节点）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新选主，dataNode删除成功；故障恢复后各节点数据一致；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -516,47 +1070,395 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM断网操作失败；故障恢复后可以再次删除节点，删除成功，删除后可以再次创建；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动catalog节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重新选主，catalog节点启动成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM断网操作失败；故障恢复后可以再次启动节点，节点启动后正常可用；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM断网操作失败；故障恢复后查看该节点可用继续使用；重启节点，节点可用；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重新选主，catalog节点创建成功；故障恢复后各节点数据一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM断网操作失败；故障恢复后可以再次创建节点；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ulimit配置异常(堆栈、句柄、线程数、虚存)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点正常/异常重启、主机正常/异常重启,在其他特性都要测试，不单独考虑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点正常重启</t>
+    <r>
+      <t>删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>catalog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的测试点在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>网络拥塞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故障场景覆盖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动dataNode（数据节点）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新选主，dataNode节点启动成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止coord节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>停止</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>coord</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的测试点在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>网络拥塞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故障场景覆盖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建coord节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动dataNode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>停止</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dataNode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的测试点在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>断网</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故障场景已经覆盖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建coordRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>coordRG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的测试点在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>网络拥塞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故障场景覆盖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dataNode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的测试点在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>网络闪断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故障场景覆盖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>coord</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的测试点在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>断网</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故障场景覆盖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机CPU耗尽</t>
+  </si>
+  <si>
+    <t>目标主机内存耗尽</t>
+  </si>
+  <si>
+    <t>目标主机时间跳变</t>
+  </si>
+  <si>
+    <t>目标主机磁盘满</t>
+  </si>
+  <si>
+    <t>catalog主节点所在主机CUP耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各节点启停流程是一样的，在CPU耗尽和内存耗尽交叉考虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据节点启停操作在内存耗尽故障场景考虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批量插入数据的同时添加节点（并发操作）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发往不同的组添加节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发添加多个协调节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attach节点的同时detach节点（并发操作）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在其他特性有覆盖，不考虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点异常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -564,25 +1466,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建节点组和节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同闪断
-不同点：普通拥塞，操作成功；消息拥塞超过7s重新选主，选主后各节点数据完整一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点断网（数据备节点断网时删除节点所在数据组）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其中一个节点断网，删除节点所在组，删除结果？（dataRG删除成功？备节点故障恢复后是已经删除了还是未删除？是否有垃圾文件未被删除？
-删除失败，是否可用继续使用）</t>
+    <t>集群管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不考虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建组和节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘损坏（低优先级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合异常(包括同一异常多次出现)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord节点所在主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点运行过程中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启后CM和节点会自动拉起，拉起后各节点运行正常,对节点做基本操作，操作成功（如连接coord做数据操作）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -590,7 +1526,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -623,15 +1559,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -679,6 +1606,26 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -765,7 +1712,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -800,13 +1747,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -815,10 +1765,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1120,15 +2070,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
     <col min="2" max="2" width="6.25" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16" style="10" customWidth="1"/>
-    <col min="4" max="4" width="15.625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="16.25" style="6" customWidth="1"/>
-    <col min="6" max="6" width="30" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="18.125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23.625" style="6" customWidth="1"/>
     <col min="7" max="7" width="53.875" style="6" customWidth="1"/>
     <col min="8" max="8" width="27.5" style="6" customWidth="1"/>
     <col min="9" max="16384" width="9" style="6"/>
@@ -1139,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -1161,36 +2111,36 @@
       </c>
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
-    </row>
-    <row r="3" spans="1:8" ht="27">
+      <c r="A2" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="3" spans="1:8" ht="40.5">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="H3" s="11"/>
     </row>
@@ -1200,31 +2150,31 @@
       <c r="C4" s="8"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" ht="40.5">
+    <row r="5" spans="1:8" ht="27">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="7" t="s">
-        <v>33</v>
+      <c r="D5" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="F5" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H5" s="7"/>
+      <c r="F5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="27">
       <c r="A6" s="7"/>
@@ -1232,42 +2182,38 @@
       <c r="C6" s="8"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>110</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="G6" s="7"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="54">
+    <row r="7" spans="1:8" ht="27">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>130</v>
+      <c r="F7" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:8" ht="27">
+    <row r="8" spans="1:8" ht="54">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="8" t="s">
-        <v>36</v>
-      </c>
+      <c r="C8" s="8"/>
       <c r="D8" s="7" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -1279,26 +2225,24 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" ht="27">
+    <row r="10" spans="1:8">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>84</v>
+      <c r="E10" s="7"/>
+      <c r="F10" s="18" t="s">
+        <v>101</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -1306,15 +2250,15 @@
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="G11" s="7" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="H11" s="7"/>
     </row>
@@ -1322,65 +2266,67 @@
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="D12" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8">
+        <v>124</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="27">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="F13" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="27">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7" t="s">
+      <c r="C14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" ht="27">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="F15" s="7" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="H15" s="7"/>
     </row>
@@ -1388,92 +2334,92 @@
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7" t="s">
-        <v>46</v>
-      </c>
+      <c r="D16" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="40.5">
-      <c r="A17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="27">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" ht="40.5">
+      <c r="A18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="27">
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="13" t="s">
-        <v>24</v>
+      <c r="F19" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="G19" s="7"/>
-      <c r="H19" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" ht="27">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>54</v>
+      <c r="E20" s="7"/>
+      <c r="F20" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="H20" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="27">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F21" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -1482,28 +2428,34 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="D22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="27">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="7"/>
+        <v>115</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>82</v>
+      </c>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="27">
@@ -1511,25 +2463,25 @@
       <c r="B24" s="7"/>
       <c r="C24" s="8"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>112</v>
+      </c>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" ht="27">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="8"/>
       <c r="D25" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -1539,36 +2491,28 @@
       <c r="B26" s="7"/>
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="7" t="s">
-        <v>46</v>
-      </c>
+      <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>88</v>
+      </c>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" ht="40.5">
-      <c r="A27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H27" s="4"/>
+    <row r="27" spans="1:8">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="7"/>
     </row>
     <row r="28" spans="1:8" ht="27">
       <c r="A28" s="7"/>
@@ -1576,168 +2520,188 @@
       <c r="C28" s="8"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="7"/>
+        <v>113</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" ht="27">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="7"/>
+      <c r="D29" s="13" t="s">
+        <v>125</v>
+      </c>
       <c r="E29" s="7"/>
-      <c r="F29" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="F29" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F30" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G30" s="7"/>
+        <v>113</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="H30" s="7"/>
     </row>
     <row r="31" spans="1:8" ht="27">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7" t="s">
-        <v>46</v>
-      </c>
+      <c r="C31" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" s="7"/>
       <c r="F31" s="7" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" ht="54">
+    <row r="32" spans="1:8" ht="27">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="8"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>130</v>
-      </c>
+      <c r="E32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32" s="7"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" ht="27">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="7" t="s">
-        <v>40</v>
+      <c r="D33" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="E33" s="7"/>
-      <c r="F33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="F33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="27">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="8"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="E34" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F34" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" s="7"/>
+        <v>113</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>87</v>
+      </c>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" ht="27">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="1:8">
+    <row r="35" spans="1:8" ht="40.5">
+      <c r="A35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" ht="27">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F36" s="7" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" ht="27">
+    <row r="37" spans="1:8">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="8"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>23</v>
+      <c r="E37" s="7"/>
+      <c r="F37" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" ht="40.5">
-      <c r="A38" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8">
+    <row r="38" spans="1:8" ht="27">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="27">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F39" s="7" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
@@ -1746,191 +2710,194 @@
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
+      <c r="D40" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" ht="27">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G41" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>88</v>
+      </c>
       <c r="H41" s="7"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="D42" s="7"/>
       <c r="E42" s="7"/>
-      <c r="F42" s="7" t="s">
-        <v>67</v>
+      <c r="F42" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" ht="27">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F43" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G43" s="7"/>
+        <v>113</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="27">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="7" t="s">
-        <v>58</v>
+      <c r="D44" s="13" t="s">
+        <v>127</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-    </row>
-    <row r="45" spans="1:8" ht="40.5">
+        <v>81</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="27">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
-      <c r="C45" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="7"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F45" s="7" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" ht="27">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="8"/>
+      <c r="C46" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="D46" s="7" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="E46" s="7"/>
-      <c r="F46" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>61</v>
-      </c>
+      <c r="F46" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="7"/>
       <c r="H46" s="7"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" ht="27">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="7"/>
+      <c r="E48" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" ht="27">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="7" t="s">
-        <v>40</v>
+      <c r="D49" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="H49" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="27">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
-      <c r="D50" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F50" s="7" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
     <row r="51" spans="1:8" ht="40.5">
       <c r="A51" s="4" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" ht="27">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
-      <c r="D52" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
@@ -1939,24 +2906,24 @@
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="8"/>
-      <c r="D53" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" ht="27">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="8"/>
-      <c r="D54" s="7"/>
+      <c r="D54" s="7" t="s">
+        <v>103</v>
+      </c>
       <c r="E54" s="7"/>
       <c r="F54" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -1965,88 +2932,76 @@
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" ht="27">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="8"/>
       <c r="D56" s="7" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
     </row>
-    <row r="57" spans="1:8" ht="27">
+    <row r="57" spans="1:8">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8"/>
-      <c r="D57" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
     </row>
-    <row r="58" spans="1:8" ht="40.5">
+    <row r="58" spans="1:8" ht="27">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
-      <c r="C58" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="C58" s="8"/>
       <c r="D58" s="7" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>60</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="G58" s="7"/>
       <c r="H58" s="7"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="8"/>
-      <c r="D59" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>61</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="G59" s="7"/>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" ht="27">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
       <c r="D60" s="7" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -2055,26 +3010,24 @@
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="8"/>
-      <c r="D61" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="F61" s="7" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" ht="27">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8"/>
       <c r="D62" s="7" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -2083,164 +3036,162 @@
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="8"/>
-      <c r="D63" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" ht="27">
-      <c r="A64" s="4" t="s">
+    <row r="64" spans="1:8" ht="40.5">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G64" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H64" s="4"/>
+      <c r="H64" s="13" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="7"/>
+      <c r="D65" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="E65" s="7"/>
       <c r="F65" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G65" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" ht="27">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
       <c r="D66" s="7" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" ht="27">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="8"/>
       <c r="D67" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="H67" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="40.5">
+      <c r="A68" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:8" ht="27">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="8"/>
-      <c r="D69" s="7" t="s">
-        <v>35</v>
-      </c>
+      <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" ht="27">
+    <row r="70" spans="1:8">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
-      <c r="D70" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="D70" s="7"/>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" ht="27">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
-      <c r="C71" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="C71" s="8"/>
       <c r="D71" s="7" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>82</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G71" s="7"/>
       <c r="H71" s="7"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="8"/>
-      <c r="D72" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="D72" s="7"/>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>61</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G72" s="7"/>
       <c r="H72" s="7"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" ht="27">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="8"/>
       <c r="D73" s="7" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -2252,21 +3203,21 @@
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" ht="27">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="8"/>
       <c r="D75" s="7" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
@@ -2275,62 +3226,50 @@
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="8"/>
-      <c r="D76" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="D76" s="7"/>
       <c r="E76" s="7"/>
       <c r="F76" s="7" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" ht="27">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="8"/>
       <c r="D77" s="7" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" ht="40.5">
-      <c r="A78" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H78" s="4"/>
-    </row>
-    <row r="79" spans="1:8">
+    <row r="78" spans="1:8">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+    </row>
+    <row r="79" spans="1:8" ht="27">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
       <c r="D79" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
@@ -2339,86 +3278,94 @@
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
-      <c r="D80" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D80" s="7"/>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" ht="40.5">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="8"/>
-      <c r="D81" s="7"/>
+      <c r="D81" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
+        <v>142</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="8"/>
       <c r="D82" s="7" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G82" s="7"/>
+        <v>142</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
+    <row r="83" spans="1:8" ht="40.5">
+      <c r="A83" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H83" s="4"/>
     </row>
     <row r="84" spans="1:8" ht="27">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8"/>
-      <c r="D84" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="D84" s="7"/>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
     </row>
-    <row r="85" spans="1:8" ht="40.5">
+    <row r="85" spans="1:8">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
-      <c r="C85" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="C85" s="8"/>
       <c r="D85" s="7" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>60</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="G85" s="7"/>
       <c r="H85" s="7"/>
     </row>
     <row r="86" spans="1:8">
@@ -2426,27 +3373,25 @@
       <c r="B86" s="7"/>
       <c r="C86" s="8"/>
       <c r="D86" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>61</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="G86" s="7"/>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" ht="27">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
       <c r="D87" s="7" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
@@ -2456,79 +3401,75 @@
       <c r="B88" s="7"/>
       <c r="C88" s="8"/>
       <c r="D88" s="7" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E88" s="7"/>
       <c r="F88" s="7" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" ht="27">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
       <c r="D89" s="7" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" ht="27">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
-      <c r="C90" s="8"/>
+      <c r="C90" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="D90" s="7" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G90" s="7"/>
+        <v>143</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="40.5">
-      <c r="A91" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H91" s="4"/>
-    </row>
-    <row r="92" spans="1:8">
+    <row r="91" spans="1:8">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H91" s="7"/>
+    </row>
+    <row r="92" spans="1:8" ht="27">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
-      <c r="C92" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D92" s="7"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E92" s="7"/>
       <c r="F92" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>80</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="G92" s="7"/>
       <c r="H92" s="7"/>
     </row>
     <row r="93" spans="1:8" ht="27">
@@ -2538,42 +3479,38 @@
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>79</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G93" s="7"/>
       <c r="H93" s="7"/>
     </row>
     <row r="94" spans="1:8" ht="27">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="7"/>
+      <c r="D94" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="E94" s="7"/>
       <c r="F94" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>79</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="G94" s="7"/>
       <c r="H94" s="7"/>
     </row>
-    <row r="95" spans="1:8" ht="67.5">
-      <c r="A95" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
+    <row r="95" spans="1:8" ht="27">
+      <c r="A95" s="7"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="7"/>
@@ -2581,304 +3518,860 @@
       <c r="C96" s="8"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
+      <c r="F96" s="7" t="s">
+        <v>143</v>
+      </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
     </row>
-    <row r="97" spans="1:8" ht="39" customHeight="1">
-      <c r="A97" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="8"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7"/>
-    </row>
-    <row r="99" spans="1:8" ht="67.5">
-      <c r="A99" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D99" s="5"/>
-      <c r="E99" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="8"/>
-      <c r="B100" s="8"/>
+    <row r="97" spans="1:8">
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+    </row>
+    <row r="98" spans="1:8" ht="40.5">
+      <c r="A98" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" ht="27">
+      <c r="A99" s="7"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+    </row>
+    <row r="100" spans="1:8" ht="27">
+      <c r="A100" s="7"/>
+      <c r="B100" s="7"/>
       <c r="C100" s="8"/>
-      <c r="D100" s="7"/>
+      <c r="D100" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="8"/>
-      <c r="B101" s="8"/>
+      <c r="A101" s="7"/>
+      <c r="B101" s="7"/>
       <c r="C101" s="8"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
       <c r="F101" s="7" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
     </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="8"/>
-      <c r="B102" s="8"/>
+    <row r="102" spans="1:8" ht="27">
+      <c r="A102" s="7"/>
+      <c r="B102" s="7"/>
       <c r="C102" s="8"/>
-      <c r="D102" s="7"/>
+      <c r="D102" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="E102" s="7"/>
       <c r="F102" s="7" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
     </row>
-    <row r="103" spans="1:8" ht="27">
-      <c r="A103" s="8"/>
-      <c r="B103" s="8"/>
+    <row r="103" spans="1:8">
+      <c r="A103" s="7"/>
+      <c r="B103" s="7"/>
       <c r="C103" s="8"/>
       <c r="D103" s="7"/>
-      <c r="E103" s="7" t="s">
-        <v>99</v>
-      </c>
+      <c r="E103" s="7"/>
       <c r="F103" s="7" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
     </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="8"/>
-      <c r="B104" s="8"/>
+    <row r="104" spans="1:8" ht="27">
+      <c r="A104" s="7"/>
+      <c r="B104" s="7"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="7"/>
+      <c r="D104" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="E104" s="7"/>
-      <c r="F104" s="17" t="s">
-        <v>100</v>
+      <c r="F104" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="8"/>
-      <c r="B105" s="8"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
       <c r="C105" s="8"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>101</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G105" s="7"/>
       <c r="H105" s="7"/>
     </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="8"/>
-      <c r="B106" s="8"/>
+    <row r="106" spans="1:8" ht="27">
+      <c r="A106" s="7"/>
+      <c r="B106" s="7"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="7"/>
+      <c r="D106" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>104</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G106" s="7"/>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8" ht="54">
-      <c r="A107" s="8"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8" t="s">
-        <v>93</v>
-      </c>
+    <row r="107" spans="1:8">
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="8"/>
       <c r="D107" s="7"/>
-      <c r="E107" s="7" t="s">
-        <v>97</v>
-      </c>
+      <c r="E107" s="7"/>
       <c r="F107" s="7" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
     </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="8"/>
-      <c r="B108" s="8"/>
+    <row r="108" spans="1:8" ht="27">
+      <c r="A108" s="7"/>
+      <c r="B108" s="7"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="7"/>
+      <c r="D108" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="E108" s="7"/>
       <c r="F108" s="7" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="8"/>
-      <c r="B109" s="8"/>
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
       <c r="C109" s="8"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7"/>
       <c r="F109" s="7" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
     </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="7"/>
+    <row r="110" spans="1:8" ht="40.5">
+      <c r="A110" s="7"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G110" s="7"/>
+        <v>144</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="H110" s="7"/>
     </row>
-    <row r="111" spans="1:8" ht="27">
-      <c r="A111" s="8"/>
-      <c r="B111" s="8"/>
+    <row r="111" spans="1:8">
+      <c r="A111" s="7"/>
+      <c r="B111" s="7"/>
       <c r="C111" s="8"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7" t="s">
-        <v>99</v>
-      </c>
+      <c r="D111" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E111" s="7"/>
       <c r="F111" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G111" s="7"/>
+        <v>144</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="H111" s="7"/>
     </row>
-    <row r="112" spans="1:8" ht="40.5">
-      <c r="A112" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4"/>
-    </row>
-    <row r="113" spans="1:8">
+    <row r="112" spans="1:8" ht="27">
+      <c r="A112" s="7"/>
+      <c r="B112" s="7"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+    </row>
+    <row r="113" spans="1:8" ht="27">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="8"/>
-      <c r="D113" s="7"/>
+      <c r="D113" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
+      <c r="F113" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8" ht="40.5">
-      <c r="A114" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4"/>
+    <row r="114" spans="1:8">
+      <c r="A114" s="7"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
     </row>
     <row r="115" spans="1:8">
+      <c r="A115" s="7"/>
+      <c r="B115" s="7"/>
       <c r="C115" s="8"/>
-      <c r="D115" s="7"/>
+      <c r="D115" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
+      <c r="F115" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
     </row>
     <row r="116" spans="1:8" ht="40.5">
-      <c r="A116" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C116" s="5"/>
-      <c r="D116" s="4"/>
+      <c r="A116" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="E116" s="4"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
+      <c r="F116" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="H116" s="4"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="8"/>
-      <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
+      <c r="A117" s="7"/>
+      <c r="B117" s="7"/>
+      <c r="C117" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
+      <c r="F117" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="8"/>
-      <c r="B118" s="8"/>
+    <row r="118" spans="1:8" ht="27">
+      <c r="A118" s="7"/>
+      <c r="B118" s="7"/>
       <c r="C118" s="8"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
+      <c r="F118" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8">
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
-      <c r="F119" s="9"/>
-      <c r="G119" s="9"/>
+    <row r="119" spans="1:8" ht="27">
+      <c r="A119" s="7"/>
+      <c r="B119" s="7"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H119" s="7"/>
+    </row>
+    <row r="120" spans="1:8" ht="27">
+      <c r="A120" s="7"/>
+      <c r="B120" s="7"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G120" s="7"/>
+      <c r="H120" s="7"/>
+    </row>
+    <row r="121" spans="1:8" ht="27">
+      <c r="A121" s="7"/>
+      <c r="B121" s="7"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="7"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G122" s="7"/>
+      <c r="H122" s="7"/>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="7"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G123" s="7"/>
+      <c r="H123" s="7"/>
+    </row>
+    <row r="124" spans="1:8" ht="54">
+      <c r="A124" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D124" s="4"/>
+      <c r="E124" s="11"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="7"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="8"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
+    </row>
+    <row r="126" spans="1:8" ht="27">
+      <c r="A126" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D126" s="4"/>
+      <c r="E126" s="11"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="4"/>
+      <c r="H126" s="4"/>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="7"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7"/>
+      <c r="G127" s="7"/>
+      <c r="H127" s="7"/>
+    </row>
+    <row r="128" spans="1:8" ht="27">
+      <c r="A128" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="11"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="H128" s="4"/>
+    </row>
+    <row r="129" spans="1:8" ht="27">
+      <c r="A129" s="7"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="8"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="H129" s="7"/>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="7"/>
+      <c r="B130" s="7"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H130" s="7"/>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="7"/>
+      <c r="B131" s="7"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H131" s="7"/>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="7"/>
+      <c r="B132" s="7"/>
+      <c r="C132" s="8"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H132" s="7"/>
+    </row>
+    <row r="133" spans="1:8" ht="27">
+      <c r="A133" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="11"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="H133" s="4"/>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="7"/>
+      <c r="B134" s="7"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H134" s="7"/>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="7"/>
+      <c r="B135" s="7"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H135" s="7"/>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="7"/>
+      <c r="B136" s="7"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H136" s="7"/>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="7"/>
+      <c r="B137" s="7"/>
+      <c r="C137" s="8"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G137" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H137" s="7"/>
+    </row>
+    <row r="138" spans="1:8" ht="39" customHeight="1">
+      <c r="A138" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C138" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D138" s="4"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4"/>
+      <c r="G138" s="4"/>
+      <c r="H138" s="4"/>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="7"/>
+      <c r="B139" s="7"/>
+      <c r="C139" s="8"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
+      <c r="G139" s="7"/>
+      <c r="H139" s="7"/>
+    </row>
+    <row r="140" spans="1:8" ht="54">
+      <c r="A140" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D140" s="5"/>
+      <c r="E140" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H140" s="4"/>
+    </row>
+    <row r="141" spans="1:8" ht="27">
+      <c r="A141" s="8"/>
+      <c r="B141" s="8"/>
+      <c r="C141" s="8"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H141" s="7"/>
+    </row>
+    <row r="142" spans="1:8" ht="27">
+      <c r="A142" s="8"/>
+      <c r="B142" s="8"/>
+      <c r="C142" s="8"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H142" s="7"/>
+    </row>
+    <row r="143" spans="1:8" ht="27">
+      <c r="A143" s="8"/>
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="H143" s="7"/>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="8"/>
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G144" s="7"/>
+      <c r="H144" s="7"/>
+    </row>
+    <row r="145" spans="1:8" ht="27">
+      <c r="A145" s="8"/>
+      <c r="B145" s="8"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H145" s="7"/>
+    </row>
+    <row r="146" spans="1:8" ht="27">
+      <c r="A146" s="8"/>
+      <c r="B146" s="8"/>
+      <c r="C146" s="8"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H146" s="7"/>
+    </row>
+    <row r="147" spans="1:8" ht="54">
+      <c r="A147" s="8"/>
+      <c r="B147" s="8"/>
+      <c r="C147" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
+    </row>
+    <row r="148" spans="1:8" ht="27">
+      <c r="A148" s="8"/>
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+    </row>
+    <row r="149" spans="1:8" ht="27">
+      <c r="A149" s="8"/>
+      <c r="B149" s="8"/>
+      <c r="C149" s="8"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
+    </row>
+    <row r="150" spans="1:8" ht="40.5">
+      <c r="A150" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="5"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4"/>
+      <c r="G150" s="4"/>
+      <c r="H150" s="4"/>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="7"/>
+      <c r="B151" s="7"/>
+      <c r="C151" s="8"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
+    </row>
+    <row r="152" spans="1:8" ht="40.5">
+      <c r="A152" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="5"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="C153" s="8"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
+    </row>
+    <row r="154" spans="1:8" ht="40.5">
+      <c r="A154" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="5"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4"/>
+      <c r="G154" s="4"/>
+      <c r="H154" s="4"/>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="8"/>
+      <c r="B155" s="8"/>
+      <c r="C155" s="8"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="8"/>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="D157" s="9"/>
+      <c r="E157" s="9"/>
+      <c r="F157" s="9"/>
+      <c r="G157" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H63">
+  <autoFilter ref="A1:H82">
     <filterColumn colId="4"/>
   </autoFilter>
   <mergeCells count="1">

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$94</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -99,7 +99,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-编目组在每个故障场景都考虑
+编目组在每个故障场景都考虑（创建编目组会同时创建一个节点，并启动节点，流程不一样）
 节点交叉在各个场景测试</t>
         </r>
       </text>
@@ -222,7 +222,177 @@
         </r>
       </text>
     </comment>
-    <comment ref="F24" authorId="0">
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+attach</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>和</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>detach</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>节点</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+编目组在每个故障场景都考虑（创建编目组会同时创建一个节点，并启动节点，流程不一样）
+节点交叉在各个场景测试</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+失败</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+目标主机</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CM</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>断网（创建</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>RG</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>所在主机断网）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -250,18 +420,46 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0">
+    <comment ref="B37" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+attach</t>
+        </r>
+        <r>
+          <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>Author:</t>
+          <t>和</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>detach</t>
         </r>
         <r>
           <rPr>
@@ -271,52 +469,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">
-考虑编目、目标节点和处理节点，</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>CPU</t>
-        </r>
-        <r>
-          <rPr>
+          <t>节点</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>和内存交叉考虑
-协调节点抽测一个</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D64" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
           <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-CPU</t>
         </r>
         <r>
           <rPr>
@@ -326,11 +494,13 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>和内存交叉考虑</t>
+          <t xml:space="preserve">
+编目组在每个故障场景都考虑（创建编目组会同时创建一个节点，并启动节点，流程不一样）
+节点交叉在各个场景测试</t>
         </r>
       </text>
     </comment>
-    <comment ref="F103" authorId="0">
+    <comment ref="G37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -352,11 +522,233 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-catalog主节点所在主机内磁盘满，需要针对每个类型的节点和组</t>
+失败</t>
         </r>
       </text>
     </comment>
-    <comment ref="F116" authorId="0">
+    <comment ref="F38" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+目标主机</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CM</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>断网（创建</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>RG</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>所在主机断网）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D55" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+考虑编目、目标节点和处理节点，</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CPU</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>和内存交叉考虑
+协调节点抽测一个</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D68" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+删除只需要考虑一个组合节点</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D72" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+CPU</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>和内存交叉考虑</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D81" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+删除只需要考虑一个组合节点</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F115" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+catalog主节点所在主机内磁盘满，需要针对每个类型的节点和组</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F128" authorId="0">
       <text>
         <r>
           <rPr>
@@ -385,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A128" authorId="0">
+    <comment ref="A140" authorId="0">
       <text>
         <r>
           <rPr>
@@ -416,7 +808,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="171">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -562,14 +954,6 @@
   </si>
   <si>
     <t>catalog主节点网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM跟coord处理节点不在同一个主机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -603,10 +987,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM所在主机网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>coord处理节点所在主机CPU耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -676,10 +1056,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM跟coord处理节点不在同一个主机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>coord处理节点网络闪断</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -756,10 +1132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>启动catalog节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>重新选主，catalog节点启动成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -828,19 +1200,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同闪断
-不同点：普通拥塞，操作成功；消息拥塞超过x重新选主，选主后各节点数据完整一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>创建coord节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建cataRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>catalog主节点所在主机时间跳变</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -873,26 +1236,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>目标主机CM断网</t>
-  </si>
-  <si>
     <t>编目信息同步，检查同步信息跟其他节点一致</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>目标主机CM断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3g3h3d时2个备节点异常，主节点降备，删除dataRG失败；故障恢复后重新选主，重新删除dataRG可以删除成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM所在主机网络断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除coord节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1520,6 +1868,42 @@
   <si>
     <t>重启后CM和节点会自动拉起，拉起后各节点运行正常,对节点做基本操作，操作成功（如连接coord做数据操作）</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除coord节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cataRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cataRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同闪断
+不同点：普通拥塞，操作成功；消息拥塞超过x重新选主，选主后各节点数据完整一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord处理节点网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机CM网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除catalog节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机断网</t>
   </si>
 </sst>
 </file>
@@ -1756,6 +2140,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1764,12 +2154,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2070,7 +2454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2111,16 +2495,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
+      <c r="A2" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:8" ht="40.5">
       <c r="A3" s="4" t="s">
@@ -2130,17 +2514,17 @@
         <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>164</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H3" s="11"/>
     </row>
@@ -2149,14 +2533,12 @@
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H4" s="7"/>
     </row>
@@ -2169,23 +2551,21 @@
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="27">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -2197,19 +2577,19 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:8" ht="54">
+    <row r="8" spans="1:8" ht="27">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
@@ -2225,10 +2605,10 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H9" s="7"/>
     </row>
@@ -2238,27 +2618,25 @@
       <c r="C10" s="8"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="18" t="s">
-        <v>101</v>
+      <c r="F10" s="15" t="s">
+        <v>96</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" ht="27">
+    <row r="11" spans="1:8">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H11" s="7"/>
     </row>
@@ -2267,17 +2645,17 @@
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
       <c r="D12" s="13" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27">
@@ -2285,14 +2663,12 @@
       <c r="B13" s="7"/>
       <c r="C13" s="8"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="7" t="s">
-        <v>64</v>
-      </c>
+      <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H13" s="7"/>
     </row>
@@ -2300,17 +2676,17 @@
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H14" s="7"/>
     </row>
@@ -2319,14 +2695,12 @@
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="7" t="s">
-        <v>64</v>
-      </c>
+      <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H15" s="7"/>
     </row>
@@ -2335,7 +2709,7 @@
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
       <c r="D16" s="13" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
@@ -2343,19 +2717,17 @@
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="27">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -2368,21 +2740,19 @@
         <v>7</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="11"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="7"/>
@@ -2391,35 +2761,35 @@
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" ht="27">
+    <row r="20" spans="1:8" ht="40.5">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="12" t="s">
-        <v>20</v>
+      <c r="D20" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="G20" s="7"/>
-      <c r="H20" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="27">
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -2428,62 +2798,58 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="13" t="s">
-        <v>27</v>
-      </c>
+      <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>123</v>
-      </c>
+      <c r="F22" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="7"/>
       <c r="H22" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="27">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="8"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>82</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="27">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="7"/>
+      <c r="D24" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="E24" s="7"/>
       <c r="F24" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="G24" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="7" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="27">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="7"/>
+        <v>170</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:8" ht="27">
@@ -2492,26 +2858,26 @@
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>88</v>
+      <c r="F26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" ht="27">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="7"/>
+      <c r="D27" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="E27" s="7"/>
-      <c r="F27" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>114</v>
-      </c>
+      <c r="F27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="7"/>
       <c r="H27" s="7"/>
     </row>
     <row r="28" spans="1:8" ht="27">
@@ -2519,376 +2885,348 @@
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E28" s="7"/>
       <c r="F28" s="7" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" ht="27">
+    <row r="29" spans="1:8">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="13" t="s">
-        <v>125</v>
-      </c>
+      <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="7" t="s">
-        <v>81</v>
+      <c r="F29" s="15" t="s">
+        <v>96</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>128</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="H29" s="7"/>
     </row>
     <row r="30" spans="1:8" ht="27">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
       <c r="D30" s="7"/>
-      <c r="E30" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E30" s="7"/>
       <c r="F30" s="7" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H30" s="7"/>
     </row>
     <row r="31" spans="1:8" ht="27">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>129</v>
+      <c r="C31" s="8"/>
+      <c r="D31" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="27">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="8"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E32" s="7"/>
       <c r="F32" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G32" s="7"/>
+        <v>170</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="H32" s="7"/>
     </row>
     <row r="33" spans="1:8" ht="27">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="13" t="s">
-        <v>30</v>
+      <c r="C33" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>132</v>
-      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8" ht="27">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="8"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>87</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="G34" s="7"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" ht="40.5">
-      <c r="A35" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H35" s="4"/>
+    <row r="35" spans="1:8" ht="27">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="36" spans="1:8" ht="27">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E36" s="7"/>
       <c r="F36" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G36" s="7"/>
+        <v>170</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>82</v>
+      </c>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
+    <row r="37" spans="1:8" ht="40.5">
+      <c r="A37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H37" s="11"/>
     </row>
     <row r="38" spans="1:8" ht="27">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="8"/>
-      <c r="D38" s="13" t="s">
-        <v>25</v>
-      </c>
+      <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="G38" s="7"/>
-      <c r="H38" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="27">
+      <c r="H38" s="7"/>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="D39" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="7"/>
       <c r="F39" s="7" t="s">
-        <v>46</v>
+        <v>165</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" ht="27">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
-      <c r="D40" s="7" t="s">
-        <v>133</v>
-      </c>
+      <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27">
+    <row r="41" spans="1:8">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="8"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
-      <c r="F41" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="F41" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" ht="27">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="7"/>
+      <c r="D42" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="E42" s="7"/>
-      <c r="F42" s="12" t="s">
-        <v>134</v>
+      <c r="F42" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
+      <c r="H42" s="7" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="43" spans="1:8" ht="27">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="8"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>89</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="G43" s="7"/>
       <c r="H43" s="7"/>
     </row>
-    <row r="44" spans="1:8" ht="27">
+    <row r="44" spans="1:8">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="13" t="s">
-        <v>127</v>
+      <c r="D44" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>140</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="27">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="8"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="E45" s="7"/>
       <c r="F45" s="7" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>83</v>
       </c>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8" ht="27">
+    <row r="46" spans="1:8">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>135</v>
-      </c>
+      <c r="C46" s="8"/>
+      <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="12" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" ht="27">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="8"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" s="7"/>
+        <v>170</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="H47" s="7"/>
     </row>
     <row r="48" spans="1:8" ht="27">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="D48" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="49" spans="1:8" ht="27">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="13" t="s">
-        <v>131</v>
-      </c>
+      <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7" t="s">
-        <v>136</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H49" s="7"/>
     </row>
     <row r="50" spans="1:8" ht="27">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>46</v>
+      <c r="C50" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E50" s="7"/>
+      <c r="F50" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="40.5">
-      <c r="A51" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H51" s="4"/>
+    <row r="51" spans="1:8">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
     </row>
     <row r="52" spans="1:8" ht="27">
       <c r="A52" s="7"/>
@@ -2897,59 +3235,69 @@
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" ht="27">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="8"/>
-      <c r="D53" s="7"/>
+      <c r="D53" s="13" t="s">
+        <v>120</v>
+      </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
+      <c r="H53" s="7" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="54" spans="1:8" ht="27">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="8"/>
-      <c r="D54" s="7" t="s">
-        <v>103</v>
-      </c>
+      <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
+    <row r="55" spans="1:8" ht="40.5">
+      <c r="A55" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8" ht="27">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="7" t="s">
-        <v>104</v>
-      </c>
+      <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -2961,7 +3309,7 @@
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
@@ -2971,11 +3319,11 @@
       <c r="B58" s="7"/>
       <c r="C58" s="8"/>
       <c r="D58" s="7" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="7" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -2987,7 +3335,7 @@
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
@@ -2997,11 +3345,11 @@
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
       <c r="D60" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -3013,7 +3361,7 @@
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="F61" s="7" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
@@ -3023,11 +3371,11 @@
       <c r="B62" s="7"/>
       <c r="C62" s="8"/>
       <c r="D62" s="7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -3039,45 +3387,35 @@
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" ht="40.5">
+    <row r="64" spans="1:8" ht="27">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
-      <c r="C64" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>10</v>
+      <c r="C64" s="8"/>
+      <c r="D64" s="13" t="s">
+        <v>169</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H64" s="13" t="s">
-        <v>148</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="G65" s="7"/>
       <c r="H65" s="7"/>
     </row>
     <row r="66" spans="1:8" ht="27">
@@ -3085,125 +3423,125 @@
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
       <c r="D66" s="7" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" ht="27">
+    <row r="67" spans="1:8">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="8"/>
-      <c r="D67" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G67" s="7"/>
-      <c r="H67" s="13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="40.5">
-      <c r="A68" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H68" s="4"/>
-    </row>
-    <row r="69" spans="1:8" ht="27">
+      <c r="H67" s="7"/>
+    </row>
+    <row r="68" spans="1:8" ht="27">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="8"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" ht="27">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
-      <c r="D70" s="7"/>
+      <c r="D70" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27">
+    <row r="71" spans="1:8">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="8"/>
-      <c r="D71" s="7" t="s">
-        <v>103</v>
-      </c>
+      <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" ht="40.5">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="7"/>
+      <c r="C72" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-    </row>
-    <row r="73" spans="1:8" ht="27">
+        <v>130</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="8"/>
       <c r="D73" s="7" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G73" s="7"/>
+        <v>130</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" ht="27">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="8"/>
-      <c r="D74" s="7"/>
+      <c r="D74" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
@@ -3213,37 +3551,47 @@
       <c r="B75" s="7"/>
       <c r="C75" s="8"/>
       <c r="D75" s="7" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
+      <c r="H75" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="40.5">
+      <c r="A76" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8" ht="27">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="8"/>
-      <c r="D77" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
@@ -3255,7 +3603,7 @@
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
@@ -3265,11 +3613,11 @@
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
       <c r="D79" s="7" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
@@ -3281,89 +3629,73 @@
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="40.5">
+    <row r="81" spans="1:8" ht="27">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="8"/>
-      <c r="D81" s="7" t="s">
-        <v>32</v>
+      <c r="D81" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H81" s="13" t="s">
-        <v>148</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="8"/>
-      <c r="D82" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="D82" s="7"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="G82" s="7"/>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8" ht="40.5">
-      <c r="A83" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H83" s="4"/>
-    </row>
-    <row r="84" spans="1:8" ht="27">
+    <row r="83" spans="1:8" ht="27">
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" ht="27">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="7" t="s">
-        <v>40</v>
+      <c r="D85" s="13" t="s">
+        <v>169</v>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
@@ -3372,12 +3704,10 @@
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="8"/>
-      <c r="D86" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="D86" s="7"/>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
@@ -3387,11 +3717,11 @@
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
       <c r="D87" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
@@ -3400,12 +3730,10 @@
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D88" s="7"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
@@ -3415,111 +3743,117 @@
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
       <c r="D89" s="7" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8" ht="27">
+    <row r="90" spans="1:8">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
-      <c r="C90" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C90" s="8"/>
+      <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>63</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" ht="27">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="8"/>
       <c r="D91" s="7" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="G91" s="7"/>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8" ht="27">
+    <row r="92" spans="1:8">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="8"/>
-      <c r="D92" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
     </row>
-    <row r="93" spans="1:8" ht="27">
+    <row r="93" spans="1:8" ht="40.5">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="7"/>
+      <c r="D93" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-    </row>
-    <row r="94" spans="1:8" ht="27">
+        <v>131</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H93" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="8"/>
       <c r="D94" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E94" s="7"/>
       <c r="F94" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G94" s="7"/>
+        <v>131</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="H94" s="7"/>
     </row>
-    <row r="95" spans="1:8" ht="27">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-    </row>
-    <row r="96" spans="1:8">
+    <row r="95" spans="1:8" ht="40.5">
+      <c r="A95" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" ht="27">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="8"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
@@ -3529,71 +3863,67 @@
       <c r="B97" s="7"/>
       <c r="C97" s="8"/>
       <c r="D97" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
     </row>
-    <row r="98" spans="1:8" ht="40.5">
-      <c r="A98" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H98" s="4"/>
+    <row r="98" spans="1:8">
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
     </row>
     <row r="99" spans="1:8" ht="27">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="7"/>
+      <c r="D99" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
     </row>
-    <row r="100" spans="1:8" ht="27">
+    <row r="100" spans="1:8">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="8"/>
       <c r="D100" s="7" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" ht="27">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="7"/>
+      <c r="D101" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
@@ -3601,27 +3931,35 @@
     <row r="102" spans="1:8" ht="27">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
-      <c r="C102" s="8"/>
+      <c r="C102" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="D102" s="7" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G102" s="7"/>
+        <v>132</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="H102" s="7"/>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="7"/>
+      <c r="D103" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="E103" s="7"/>
       <c r="F103" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="G103" s="7"/>
+        <v>132</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="H103" s="7"/>
     </row>
     <row r="104" spans="1:8" ht="27">
@@ -3629,23 +3967,23 @@
       <c r="B104" s="7"/>
       <c r="C104" s="8"/>
       <c r="D104" s="7" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" ht="27">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="8"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
@@ -3655,37 +3993,37 @@
       <c r="B106" s="7"/>
       <c r="C106" s="8"/>
       <c r="D106" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" ht="27">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="7"/>
+      <c r="D107" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E107" s="7"/>
       <c r="F107" s="7" t="s">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
     </row>
-    <row r="108" spans="1:8" ht="27">
+    <row r="108" spans="1:8">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="7" t="s">
-        <v>50</v>
-      </c>
+      <c r="D108" s="7"/>
       <c r="E108" s="7"/>
       <c r="F108" s="7" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
@@ -3694,46 +4032,48 @@
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="7"/>
+      <c r="D109" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="E109" s="7"/>
       <c r="F109" s="7" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
     </row>
     <row r="110" spans="1:8" ht="40.5">
-      <c r="A110" s="7"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H110" s="7"/>
-    </row>
-    <row r="111" spans="1:8">
+      <c r="A110" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" ht="27">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="8"/>
-      <c r="D111" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="D111" s="7"/>
       <c r="E111" s="7"/>
       <c r="F111" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G111" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="G111" s="7"/>
       <c r="H111" s="7"/>
     </row>
     <row r="112" spans="1:8" ht="27">
@@ -3741,39 +4081,37 @@
       <c r="B112" s="7"/>
       <c r="C112" s="8"/>
       <c r="D112" s="7" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="7" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8" ht="27">
+    <row r="113" spans="1:8">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="8"/>
-      <c r="D113" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="D113" s="7"/>
       <c r="E113" s="7"/>
       <c r="F113" s="7" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" ht="27">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="8"/>
       <c r="D114" s="7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="7" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
@@ -3782,277 +4120,271 @@
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="8"/>
-      <c r="D115" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="D115" s="7"/>
       <c r="E115" s="7"/>
       <c r="F115" s="7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
     </row>
-    <row r="116" spans="1:8" ht="40.5">
-      <c r="A116" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E116" s="4"/>
-      <c r="F116" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H116" s="4"/>
+    <row r="116" spans="1:8" ht="27">
+      <c r="A116" s="7"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E116" s="7"/>
+      <c r="F116" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
-      <c r="C117" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="C117" s="8"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
       <c r="F117" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G117" s="7" t="s">
-        <v>61</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G117" s="7"/>
       <c r="H117" s="7"/>
     </row>
     <row r="118" spans="1:8" ht="27">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="8"/>
-      <c r="D118" s="7"/>
+      <c r="D118" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>60</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="G118" s="7"/>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8" ht="27">
+    <row r="119" spans="1:8">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
       <c r="F119" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>60</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G119" s="7"/>
       <c r="H119" s="7"/>
     </row>
     <row r="120" spans="1:8" ht="27">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="8"/>
-      <c r="D120" s="7"/>
+      <c r="D120" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" ht="27">
+    <row r="121" spans="1:8">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="8"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
       <c r="F121" s="7" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" ht="40.5">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="7"/>
+      <c r="C122" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E122" s="7"/>
       <c r="F122" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G122" s="7"/>
+        <v>133</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="H122" s="7"/>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="8"/>
-      <c r="D123" s="7"/>
+      <c r="D123" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="E123" s="7"/>
       <c r="F123" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="G123" s="7"/>
+        <v>133</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" ht="54">
-      <c r="A124" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D124" s="4"/>
-      <c r="E124" s="11"/>
-      <c r="F124" s="4"/>
-      <c r="G124" s="4"/>
-      <c r="H124" s="4"/>
-    </row>
-    <row r="125" spans="1:8">
+    <row r="124" spans="1:8" ht="27">
+      <c r="A124" s="7"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G124" s="7"/>
+      <c r="H124" s="7"/>
+    </row>
+    <row r="125" spans="1:8" ht="27">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="8"/>
-      <c r="D125" s="7"/>
+      <c r="D125" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
+      <c r="F125" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
     </row>
-    <row r="126" spans="1:8" ht="27">
-      <c r="A126" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C126" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D126" s="4"/>
-      <c r="E126" s="11"/>
-      <c r="F126" s="4"/>
-      <c r="G126" s="4"/>
-      <c r="H126" s="4"/>
+    <row r="126" spans="1:8">
+      <c r="A126" s="7"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="8"/>
+      <c r="D126" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="8"/>
-      <c r="D127" s="7"/>
+      <c r="D127" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
+      <c r="F127" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
     </row>
-    <row r="128" spans="1:8" ht="27">
+    <row r="128" spans="1:8" ht="40.5">
       <c r="A128" s="4" t="s">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128" s="11"/>
-      <c r="D128" s="4"/>
-      <c r="E128" s="19" t="s">
-        <v>167</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E128" s="4"/>
       <c r="F128" s="4" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="H128" s="4"/>
     </row>
     <row r="129" spans="1:8" ht="27">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
-      <c r="C129" s="8"/>
+      <c r="C129" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="G129" s="7" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" ht="27">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="8"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
       <c r="F130" s="7" t="s">
-        <v>169</v>
+        <v>55</v>
       </c>
       <c r="G130" s="7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H130" s="7"/>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" ht="27">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="8"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7" t="s">
-        <v>170</v>
+        <v>56</v>
       </c>
       <c r="G131" s="7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H131" s="7"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" ht="27">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="8"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
       <c r="F132" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="G132" s="7"/>
       <c r="H132" s="7"/>
     </row>
     <row r="133" spans="1:8" ht="27">
-      <c r="A133" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C133" s="11"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="H133" s="4"/>
+      <c r="A133" s="7"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="8"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G133" s="7"/>
+      <c r="H133" s="7"/>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="7"/>
@@ -4061,11 +4393,9 @@
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
       <c r="F134" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="G134" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G134" s="7"/>
       <c r="H134" s="7"/>
     </row>
     <row r="135" spans="1:8">
@@ -4075,26 +4405,26 @@
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G135" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="G135" s="7"/>
       <c r="H135" s="7"/>
     </row>
-    <row r="136" spans="1:8">
-      <c r="A136" s="7"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="8"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G136" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H136" s="7"/>
+    <row r="136" spans="1:8" ht="54">
+      <c r="A136" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D136" s="4"/>
+      <c r="E136" s="11"/>
+      <c r="F136" s="4"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="7"/>
@@ -4102,26 +4432,22 @@
       <c r="C137" s="8"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
-      <c r="F137" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="G137" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="F137" s="7"/>
+      <c r="G137" s="7"/>
       <c r="H137" s="7"/>
     </row>
-    <row r="138" spans="1:8" ht="39" customHeight="1">
+    <row r="138" spans="1:8" ht="27">
       <c r="A138" s="4" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>158</v>
+        <v>7</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="D138" s="4"/>
-      <c r="E138" s="4"/>
+      <c r="E138" s="11"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
@@ -4136,161 +4462,169 @@
       <c r="G139" s="7"/>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" ht="54">
+    <row r="140" spans="1:8" ht="27">
       <c r="A140" s="4" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C140" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="11"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D140" s="5"/>
-      <c r="E140" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="H140" s="4"/>
     </row>
     <row r="141" spans="1:8" ht="27">
-      <c r="A141" s="8"/>
-      <c r="B141" s="8"/>
+      <c r="A141" s="7"/>
+      <c r="B141" s="7"/>
       <c r="C141" s="8"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
       <c r="F141" s="7" t="s">
-        <v>67</v>
+        <v>157</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8" ht="27">
-      <c r="A142" s="8"/>
-      <c r="B142" s="8"/>
+    <row r="142" spans="1:8">
+      <c r="A142" s="7"/>
+      <c r="B142" s="7"/>
       <c r="C142" s="8"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
-      <c r="F142" s="12" t="s">
-        <v>108</v>
+      <c r="F142" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H142" s="7"/>
     </row>
-    <row r="143" spans="1:8" ht="27">
-      <c r="A143" s="8"/>
-      <c r="B143" s="8"/>
+    <row r="143" spans="1:8">
+      <c r="A143" s="7"/>
+      <c r="B143" s="7"/>
       <c r="C143" s="8"/>
       <c r="D143" s="7"/>
-      <c r="E143" s="7" t="s">
-        <v>72</v>
-      </c>
+      <c r="E143" s="7"/>
       <c r="F143" s="7" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="H143" s="7"/>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="8"/>
-      <c r="B144" s="8"/>
+      <c r="A144" s="7"/>
+      <c r="B144" s="7"/>
       <c r="C144" s="8"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
-      <c r="F144" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G144" s="7"/>
+      <c r="F144" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="H144" s="7"/>
     </row>
     <row r="145" spans="1:8" ht="27">
-      <c r="A145" s="8"/>
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G145" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H145" s="7"/>
-    </row>
-    <row r="146" spans="1:8" ht="27">
-      <c r="A146" s="8"/>
-      <c r="B146" s="8"/>
+      <c r="A145" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" s="11"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H145" s="4"/>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="7"/>
+      <c r="B146" s="7"/>
       <c r="C146" s="8"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
       <c r="F146" s="7" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H146" s="7"/>
     </row>
-    <row r="147" spans="1:8" ht="54">
-      <c r="A147" s="8"/>
-      <c r="B147" s="8"/>
-      <c r="C147" s="8" t="s">
-        <v>69</v>
-      </c>
+    <row r="147" spans="1:8">
+      <c r="A147" s="7"/>
+      <c r="B147" s="7"/>
+      <c r="C147" s="8"/>
       <c r="D147" s="7"/>
-      <c r="E147" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="H147" s="7"/>
     </row>
-    <row r="148" spans="1:8" ht="27">
-      <c r="A148" s="8"/>
-      <c r="B148" s="8"/>
+    <row r="148" spans="1:8">
+      <c r="A148" s="7"/>
+      <c r="B148" s="7"/>
       <c r="C148" s="8"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
       <c r="F148" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="G148" s="7"/>
+        <v>159</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="H148" s="7"/>
     </row>
-    <row r="149" spans="1:8" ht="27">
-      <c r="A149" s="8"/>
-      <c r="B149" s="8"/>
+    <row r="149" spans="1:8">
+      <c r="A149" s="7"/>
+      <c r="B149" s="7"/>
       <c r="C149" s="8"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
-      <c r="F149" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G149" s="7"/>
+      <c r="F149" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="H149" s="7"/>
     </row>
-    <row r="150" spans="1:8" ht="40.5">
+    <row r="150" spans="1:8" ht="39" customHeight="1">
       <c r="A150" s="4" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D150" s="5"/>
+        <v>147</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D150" s="4"/>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
       <c r="G150" s="4"/>
@@ -4306,52 +4640,70 @@
       <c r="G151" s="7"/>
       <c r="H151" s="7"/>
     </row>
-    <row r="152" spans="1:8" ht="40.5">
+    <row r="152" spans="1:8" ht="54">
       <c r="A152" s="4" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="D152" s="5"/>
-      <c r="E152" s="4"/>
-      <c r="F152" s="4"/>
-      <c r="G152" s="4"/>
+      <c r="E152" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="H152" s="4"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" ht="27">
+      <c r="A153" s="8"/>
+      <c r="B153" s="8"/>
       <c r="C153" s="8"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
-      <c r="F153" s="7"/>
-      <c r="G153" s="7"/>
+      <c r="F153" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>92</v>
+      </c>
       <c r="H153" s="7"/>
     </row>
-    <row r="154" spans="1:8" ht="40.5">
-      <c r="A154" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C154" s="5"/>
-      <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
-      <c r="F154" s="4"/>
-      <c r="G154" s="4"/>
-      <c r="H154" s="4"/>
-    </row>
-    <row r="155" spans="1:8">
+    <row r="154" spans="1:8" ht="27">
+      <c r="A154" s="8"/>
+      <c r="B154" s="8"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H154" s="7"/>
+    </row>
+    <row r="155" spans="1:8" ht="27">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
       <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="7"/>
+      <c r="E155" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="H155" s="7"/>
     </row>
     <row r="156" spans="1:8">
@@ -4360,18 +4712,170 @@
       <c r="C156" s="8"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
+      <c r="F156" s="13" t="s">
+        <v>69</v>
+      </c>
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8">
-      <c r="D157" s="9"/>
-      <c r="E157" s="9"/>
-      <c r="F157" s="9"/>
-      <c r="G157" s="9"/>
+    <row r="157" spans="1:8" ht="27">
+      <c r="A157" s="8"/>
+      <c r="B157" s="8"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H157" s="7"/>
+    </row>
+    <row r="158" spans="1:8" ht="27">
+      <c r="A158" s="8"/>
+      <c r="B158" s="8"/>
+      <c r="C158" s="8"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H158" s="7"/>
+    </row>
+    <row r="159" spans="1:8" ht="40.5">
+      <c r="A159" s="8"/>
+      <c r="B159" s="8"/>
+      <c r="C159" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
+    </row>
+    <row r="160" spans="1:8" ht="27">
+      <c r="A160" s="8"/>
+      <c r="B160" s="8"/>
+      <c r="C160" s="8"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
+    </row>
+    <row r="161" spans="1:8" ht="27">
+      <c r="A161" s="8"/>
+      <c r="B161" s="8"/>
+      <c r="C161" s="8"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G161" s="7"/>
+      <c r="H161" s="7"/>
+    </row>
+    <row r="162" spans="1:8" ht="40.5">
+      <c r="A162" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="5"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
+      <c r="G162" s="4"/>
+      <c r="H162" s="4"/>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" s="7"/>
+      <c r="B163" s="7"/>
+      <c r="C163" s="8"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="7"/>
+      <c r="H163" s="7"/>
+    </row>
+    <row r="164" spans="1:8" ht="40.5">
+      <c r="A164" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" s="5"/>
+      <c r="E164" s="4"/>
+      <c r="F164" s="4"/>
+      <c r="G164" s="4"/>
+      <c r="H164" s="4"/>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="C165" s="8"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="7"/>
+      <c r="H165" s="7"/>
+    </row>
+    <row r="166" spans="1:8" ht="40.5">
+      <c r="A166" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="5"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4"/>
+      <c r="G166" s="4"/>
+      <c r="H166" s="4"/>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="8"/>
+      <c r="B167" s="8"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
+      <c r="G167" s="7"/>
+      <c r="H167" s="7"/>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="8"/>
+      <c r="B168" s="8"/>
+      <c r="C168" s="8"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="7"/>
+      <c r="H168" s="7"/>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="D169" s="9"/>
+      <c r="E169" s="9"/>
+      <c r="F169" s="9"/>
+      <c r="G169" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H82">
+  <autoFilter ref="A1:H94">
     <filterColumn colId="4"/>
   </autoFilter>
   <mergeCells count="1">

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -808,7 +808,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="172">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1904,6 +1904,10 @@
   </si>
   <si>
     <t>目标主机断网</t>
+  </si>
+  <si>
+    <t>编目分区组上已经没有数据节点及协调节点的信息。删除编目分区组将会把该组中所有的编目节点都删除。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2838,7 +2842,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="27">
+    <row r="25" spans="1:8" ht="54">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="8"/>
@@ -2850,7 +2854,9 @@
       <c r="G25" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H25" s="7"/>
+      <c r="H25" s="7" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="27">
       <c r="A26" s="7"/>
@@ -2908,7 +2914,7 @@
       </c>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" ht="27">
+    <row r="30" spans="1:8">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -2970,7 +2976,7 @@
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" ht="27">
+    <row r="34" spans="1:8">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="8"/>
@@ -3036,7 +3042,7 @@
       </c>
       <c r="H37" s="11"/>
     </row>
-    <row r="38" spans="1:8" ht="27">
+    <row r="38" spans="1:8">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="8"/>
@@ -3062,7 +3068,7 @@
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" ht="27">
+    <row r="40" spans="1:8">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -3102,7 +3108,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27">
+    <row r="43" spans="1:8">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="8"/>
@@ -3154,7 +3160,7 @@
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
     </row>
-    <row r="47" spans="1:8" ht="27">
+    <row r="47" spans="1:8">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="8"/>
@@ -3228,7 +3234,7 @@
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" ht="27">
+    <row r="52" spans="1:8">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
@@ -3256,7 +3262,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27">
+    <row r="54" spans="1:8">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="8"/>

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$110</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -222,7 +222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B18" authorId="0">
+    <comment ref="B22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -275,7 +275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="0">
+    <comment ref="D22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -302,7 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0">
+    <comment ref="G22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -328,7 +328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F19" authorId="0">
+    <comment ref="F23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -392,7 +392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F26" authorId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -420,7 +420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B37" authorId="0">
+    <comment ref="B45" authorId="0">
       <text>
         <r>
           <rPr>
@@ -473,7 +473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D37" authorId="0">
+    <comment ref="D45" authorId="0">
       <text>
         <r>
           <rPr>
@@ -500,7 +500,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G37" authorId="0">
+    <comment ref="G45" authorId="0">
       <text>
         <r>
           <rPr>
@@ -526,7 +526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F38" authorId="0">
+    <comment ref="F46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -590,7 +590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D55" authorId="0">
+    <comment ref="D67" authorId="0">
       <text>
         <r>
           <rPr>
@@ -636,7 +636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D68" authorId="0">
+    <comment ref="D80" authorId="0">
       <text>
         <r>
           <rPr>
@@ -662,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D72" authorId="0">
+    <comment ref="D84" authorId="0">
       <text>
         <r>
           <rPr>
@@ -696,7 +696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0">
+    <comment ref="D97" authorId="0">
       <text>
         <r>
           <rPr>
@@ -722,7 +722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F115" authorId="0">
+    <comment ref="F139" authorId="0">
       <text>
         <r>
           <rPr>
@@ -748,7 +748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="0">
+    <comment ref="F156" authorId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A140" authorId="0">
+    <comment ref="A169" authorId="0">
       <text>
         <r>
           <rPr>
@@ -808,7 +808,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="195">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -890,10 +890,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>catalog备节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>备节点影响不大，在创建其他节点时覆盖考虑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -946,10 +942,6 @@
   </si>
   <si>
     <t>停止coord节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络闪断</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1060,10 +1052,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>coord处理节点网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CM异常停止（kill -9）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1132,10 +1120,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>重新选主，catalog节点启动成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CM断网操作失败；故障恢复后可以再次启动节点，节点启动后正常可用；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1172,10 +1156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>进程退出，操作失败；CM重启完成后可以继续创建/删除节点组和节点；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1189,10 +1169,6 @@
   </si>
   <si>
     <t>CM跟该主机通信失败，操作失败；故障恢复后主机可以正常连接，节点间信息正常同步，同步后数据完整一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点断网</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1294,10 +1270,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>停止dataNode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>停止</t>
     </r>
@@ -1534,10 +1506,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>catalog备节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>启动dataNode</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1895,18 +1863,142 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>删除catalog节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机断网</t>
+  </si>
+  <si>
+    <t>编目分区组上已经没有数据节点及协调节点的信息。删除编目分区组将会把该组中所有的编目节点都删除。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止dataNode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attach/detach节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attach节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detach节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新选主，catalog节点启动成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attach成功/失败；重新选主，故障恢复后检查attach成功的节点正常可用，编目各节点信息完整一致；故障恢复后检查attach失败的节点，保留在节点的数据不丢失，目标主机和编目上没有该节点信息，可以再次attach成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attach失败；故障恢复后重新attach成功，节点正常可用，编目各节点信息完整一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detach成功/失败；重新选主，故障恢复后检查detach成功的节点在目标主机和编目上没有该节点信息，可以再次attach成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detach失败；故障恢复后检查detach成功的节点，目标主机和编目上没有该节点信息，可以再次attach成功，节点正常可用；故障恢复后检查detach失败的节点，可以再次detach，detach后目标主机和编目节点没有该节点的信息；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog 2个备节点网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>目标主机CM网络拥塞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>删除catalog节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标主机断网</t>
-  </si>
-  <si>
-    <t>编目分区组上已经没有数据节点及协调节点的信息。删除编目分区组将会把该组中所有的编目节点都删除。</t>
+    <t>coord处理节点网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord处理节点所在主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复多次强制detach节点后再次attach到同一个节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2458,7 +2550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2477,10 +2569,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -2500,7 +2592,7 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="33.75" customHeight="1">
       <c r="A2" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -2518,17 +2610,17 @@
         <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H3" s="11"/>
     </row>
@@ -2539,10 +2631,10 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H4" s="7"/>
     </row>
@@ -2551,7 +2643,7 @@
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
@@ -2559,7 +2651,7 @@
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2569,7 +2661,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -2581,10 +2673,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H7" s="7"/>
     </row>
@@ -2593,7 +2685,7 @@
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
@@ -2609,10 +2701,10 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H9" s="7"/>
     </row>
@@ -2623,10 +2715,10 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -2637,10 +2729,10 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H11" s="7"/>
     </row>
@@ -2649,17 +2741,17 @@
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
       <c r="D12" s="13" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27">
@@ -2669,10 +2761,10 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H13" s="7"/>
     </row>
@@ -2680,17 +2772,17 @@
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="H14" s="7"/>
     </row>
@@ -2701,10 +2793,10 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H15" s="7"/>
     </row>
@@ -2713,7 +2805,7 @@
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
       <c r="D16" s="13" t="s">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
@@ -2721,7 +2813,7 @@
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2731,86 +2823,94 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" ht="40.5">
-      <c r="A18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="11"/>
-    </row>
-    <row r="19" spans="1:8">
+    <row r="18" spans="1:8" ht="54">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" ht="27">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" ht="40.5">
+    <row r="20" spans="1:8" ht="27">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
       <c r="D20" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>42</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>171</v>
+      </c>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" ht="54">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="7"/>
+        <v>166</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>172</v>
+      </c>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" ht="27">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7" t="s">
-        <v>21</v>
-      </c>
+    <row r="22" spans="1:8" ht="40.5">
+      <c r="A22" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="11"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="7"/>
@@ -2819,44 +2919,38 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" ht="27">
+    <row r="24" spans="1:8" ht="40.5">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="54">
+      <c r="D24" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="8"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>171</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:8" ht="27">
       <c r="A26" s="7"/>
@@ -2864,24 +2958,22 @@
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" spans="1:8" ht="27">
+      <c r="F26" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -2890,41 +2982,47 @@
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="7"/>
+      <c r="D28" s="13" t="s">
+        <v>26</v>
+      </c>
       <c r="E28" s="7"/>
-      <c r="F28" s="7" t="s">
-        <v>77</v>
+      <c r="F28" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:8">
+        <v>105</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="54">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="15" t="s">
-        <v>96</v>
+      <c r="F29" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:8">
+        <v>75</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>84</v>
+      <c r="F30" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="H30" s="7"/>
     </row>
@@ -2932,19 +3030,15 @@
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="13" t="s">
-        <v>114</v>
+      <c r="D31" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>117</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
     </row>
     <row r="32" spans="1:8" ht="27">
       <c r="A32" s="7"/>
@@ -2953,27 +3047,25 @@
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" ht="27">
+    <row r="33" spans="1:8">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>118</v>
-      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="7"/>
-      <c r="F33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="7"/>
+      <c r="F33" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8">
@@ -2983,9 +3075,11 @@
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G34" s="7"/>
+        <v>174</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:8" ht="27">
@@ -2993,17 +3087,17 @@
       <c r="B35" s="7"/>
       <c r="C35" s="8"/>
       <c r="D35" s="13" t="s">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27">
@@ -3013,34 +3107,28 @@
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" ht="40.5">
-      <c r="A37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="H37" s="11"/>
+    <row r="37" spans="1:8" ht="27">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="7"/>
@@ -3049,73 +3137,81 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" ht="27">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="7" t="s">
-        <v>28</v>
+      <c r="D39" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-    </row>
-    <row r="40" spans="1:8">
+        <v>176</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="27">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G40" s="7"/>
+        <v>174</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" ht="40.5">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="7"/>
+      <c r="C41" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="E41" s="7"/>
-      <c r="F41" s="14" t="s">
-        <v>62</v>
+      <c r="F41" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" ht="27">
+    <row r="42" spans="1:8">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="13" t="s">
-        <v>25</v>
-      </c>
+      <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7" t="s">
-        <v>36</v>
+        <v>174</v>
       </c>
       <c r="G42" s="7"/>
-      <c r="H42" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="H42" s="7"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="7"/>
+      <c r="D43" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -3124,29 +3220,35 @@
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="7" t="s">
-        <v>122</v>
-      </c>
+      <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" ht="27">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H45" s="7"/>
+    <row r="45" spans="1:8" ht="40.5">
+      <c r="A45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="H45" s="11"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="7"/>
@@ -3154,8 +3256,8 @@
       <c r="C46" s="8"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="12" t="s">
-        <v>123</v>
+      <c r="F46" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
@@ -3164,63 +3266,55 @@
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="7"/>
+      <c r="D47" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>84</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" ht="27">
+    <row r="48" spans="1:8">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="13" t="s">
-        <v>116</v>
-      </c>
+      <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="27">
+        <v>41</v>
+      </c>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="8"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
-      <c r="F49" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="F49" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="G49" s="7"/>
       <c r="H49" s="7"/>
     </row>
     <row r="50" spans="1:8" ht="27">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
-      <c r="C50" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>124</v>
+      <c r="C50" s="8"/>
+      <c r="D50" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="E50" s="7"/>
-      <c r="F50" s="12" t="s">
-        <v>19</v>
+      <c r="F50" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
+      <c r="H50" s="7" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="7"/>
@@ -3229,7 +3323,7 @@
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
@@ -3238,10 +3332,12 @@
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
-      <c r="D52" s="7"/>
+      <c r="D52" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
@@ -3250,17 +3346,15 @@
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="8"/>
-      <c r="D53" s="13" t="s">
-        <v>120</v>
-      </c>
+      <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7" t="s">
-        <v>125</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H53" s="7"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="7"/>
@@ -3268,68 +3362,70 @@
       <c r="C54" s="8"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
-      <c r="F54" s="7" t="s">
-        <v>170</v>
+      <c r="F54" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8" ht="40.5">
-      <c r="A55" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H55" s="4"/>
+    <row r="55" spans="1:8">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H55" s="7"/>
     </row>
     <row r="56" spans="1:8" ht="27">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="7"/>
+      <c r="D56" s="13" t="s">
+        <v>109</v>
+      </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-    </row>
-    <row r="57" spans="1:8">
+        <v>180</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="27">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G57" s="7"/>
+        <v>181</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="H57" s="7"/>
     </row>
     <row r="58" spans="1:8" ht="27">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
-      <c r="C58" s="8"/>
+      <c r="C58" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="D58" s="7" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E58" s="7"/>
-      <c r="F58" s="7" t="s">
-        <v>134</v>
+      <c r="F58" s="12" t="s">
+        <v>179</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -3341,73 +3437,75 @@
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8" ht="27">
+    <row r="60" spans="1:8">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
-      <c r="D60" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" ht="27">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="8"/>
-      <c r="D61" s="7"/>
+      <c r="D61" s="13" t="s">
+        <v>113</v>
+      </c>
       <c r="E61" s="7"/>
       <c r="F61" s="7" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-    </row>
-    <row r="62" spans="1:8" ht="27">
+      <c r="H61" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" ht="40.5">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="7"/>
+      <c r="C63" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" ht="27">
+    <row r="64" spans="1:8">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="8"/>
-      <c r="D64" s="13" t="s">
-        <v>169</v>
-      </c>
+      <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -3416,50 +3514,58 @@
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="7"/>
+      <c r="D65" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E65" s="7"/>
       <c r="F65" s="7" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" ht="27">
+    <row r="66" spans="1:8">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
-      <c r="D66" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D66" s="7"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
+    <row r="67" spans="1:8" ht="40.5">
+      <c r="A67" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8" ht="27">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="8"/>
-      <c r="D68" s="13" t="s">
-        <v>29</v>
-      </c>
+      <c r="D68" s="7"/>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -3471,7 +3577,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -3481,11 +3587,11 @@
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
       <c r="D70" s="7" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -3497,45 +3603,35 @@
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8" ht="40.5">
+    <row r="72" spans="1:8" ht="27">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
-      <c r="C72" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="C72" s="8"/>
       <c r="D72" s="7" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H72" s="13" t="s">
-        <v>137</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="G73" s="7"/>
       <c r="H73" s="7"/>
     </row>
     <row r="74" spans="1:8" ht="27">
@@ -3543,177 +3639,177 @@
       <c r="B74" s="7"/>
       <c r="C74" s="8"/>
       <c r="D74" s="7" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" ht="27">
+    <row r="75" spans="1:8">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="8"/>
-      <c r="D75" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G75" s="7"/>
-      <c r="H75" s="13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="40.5">
-      <c r="A76" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H76" s="4"/>
-    </row>
-    <row r="77" spans="1:8" ht="27">
+      <c r="H75" s="7"/>
+    </row>
+    <row r="76" spans="1:8" ht="27">
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="8"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" ht="27">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8"/>
-      <c r="D78" s="7"/>
+      <c r="D78" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
     </row>
-    <row r="79" spans="1:8" ht="27">
+    <row r="79" spans="1:8">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
-      <c r="D79" s="7" t="s">
-        <v>97</v>
-      </c>
+      <c r="D79" s="7"/>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" ht="27">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
-      <c r="D80" s="7"/>
+      <c r="D80" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27">
+    <row r="81" spans="1:8">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="8"/>
-      <c r="D81" s="13" t="s">
-        <v>27</v>
-      </c>
+      <c r="D81" s="7"/>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" ht="27">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="8"/>
-      <c r="D82" s="7"/>
+      <c r="D82" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8" ht="27">
+    <row r="83" spans="1:8">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="D83" s="7"/>
       <c r="E83" s="7"/>
       <c r="F83" s="7" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" ht="40.5">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="7"/>
+      <c r="C84" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-    </row>
-    <row r="85" spans="1:8" ht="27">
+        <v>122</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="13" t="s">
-        <v>169</v>
+      <c r="D85" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="G85" s="7"/>
+        <v>122</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" ht="27">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="8"/>
-      <c r="D86" s="7"/>
+      <c r="D86" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
@@ -3723,37 +3819,41 @@
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
       <c r="D87" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-    </row>
-    <row r="88" spans="1:8">
+      <c r="H87" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="40.5">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="7"/>
+      <c r="C88" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="E88" s="7"/>
       <c r="F88" s="7" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" ht="27">
+    <row r="89" spans="1:8">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D89" s="7"/>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
@@ -3762,118 +3862,110 @@
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
-      <c r="D90" s="7"/>
+      <c r="D90" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="27">
+    <row r="91" spans="1:8">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="D91" s="7"/>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-    </row>
-    <row r="93" spans="1:8" ht="40.5">
+    <row r="92" spans="1:8" ht="40.5">
+      <c r="A92" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" ht="27">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="D93" s="7"/>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H93" s="13" t="s">
-        <v>137</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="G94" s="7"/>
       <c r="H94" s="7"/>
     </row>
-    <row r="95" spans="1:8" ht="40.5">
-      <c r="A95" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H95" s="4"/>
-    </row>
-    <row r="96" spans="1:8" ht="27">
+    <row r="95" spans="1:8" ht="27">
+      <c r="A95" s="7"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="8"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" ht="27">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="7" t="s">
-        <v>38</v>
+      <c r="D97" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
@@ -3882,12 +3974,10 @@
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="8"/>
-      <c r="D98" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="D98" s="7"/>
       <c r="E98" s="7"/>
       <c r="F98" s="7" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
@@ -3897,11 +3987,11 @@
       <c r="B99" s="7"/>
       <c r="C99" s="8"/>
       <c r="D99" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
@@ -3910,12 +4000,10 @@
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="8"/>
-      <c r="D100" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D100" s="7"/>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
@@ -3924,60 +4012,50 @@
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="7" t="s">
-        <v>47</v>
+      <c r="D101" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
     </row>
-    <row r="102" spans="1:8" ht="27">
+    <row r="102" spans="1:8">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
-      <c r="C102" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C102" s="8"/>
+      <c r="D102" s="7"/>
       <c r="E102" s="7"/>
       <c r="F102" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>60</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="G102" s="7"/>
       <c r="H102" s="7"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" ht="27">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="8"/>
       <c r="D103" s="7" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G103" s="7"/>
       <c r="H103" s="7"/>
     </row>
-    <row r="104" spans="1:8" ht="27">
+    <row r="104" spans="1:8">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
@@ -3986,24 +4064,24 @@
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="8"/>
-      <c r="D105" s="7"/>
+      <c r="D105" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
     </row>
-    <row r="106" spans="1:8" ht="27">
+    <row r="106" spans="1:8">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="D106" s="7"/>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
@@ -4013,11 +4091,11 @@
       <c r="B107" s="7"/>
       <c r="C107" s="8"/>
       <c r="D107" s="7" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="7" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
@@ -4029,69 +4107,69 @@
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
       <c r="F108" s="7" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" ht="40.5">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="8"/>
       <c r="D109" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-    </row>
-    <row r="110" spans="1:8" ht="40.5">
-      <c r="A110" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C110" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G109" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D110" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E110" s="4"/>
-      <c r="F110" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H110" s="4"/>
-    </row>
-    <row r="111" spans="1:8" ht="27">
+      <c r="H109" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="7"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H110" s="7"/>
+    </row>
+    <row r="111" spans="1:8" ht="40.5">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="7"/>
+      <c r="C111" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
     </row>
-    <row r="112" spans="1:8" ht="27">
+    <row r="112" spans="1:8">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="8"/>
-      <c r="D112" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="D112" s="7"/>
       <c r="E112" s="7"/>
       <c r="F112" s="7" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
@@ -4100,50 +4178,58 @@
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="8"/>
-      <c r="D113" s="7"/>
+      <c r="D113" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E113" s="7"/>
       <c r="F113" s="7" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8" ht="27">
+    <row r="114" spans="1:8">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="8"/>
-      <c r="D114" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="D114" s="7"/>
       <c r="E114" s="7"/>
       <c r="F114" s="7" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="7"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
+    <row r="115" spans="1:8" ht="40.5">
+      <c r="A115" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H115" s="4"/>
     </row>
     <row r="116" spans="1:8" ht="27">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="8"/>
-      <c r="D116" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="D116" s="7"/>
       <c r="E116" s="7"/>
       <c r="F116" s="7" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
@@ -4152,81 +4238,87 @@
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="8"/>
-      <c r="D117" s="7"/>
+      <c r="D117" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="E117" s="7"/>
       <c r="F117" s="7" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" ht="27">
+    <row r="118" spans="1:8">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="8"/>
       <c r="D118" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" ht="27">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
-      <c r="D119" s="7"/>
+      <c r="D119" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="E119" s="7"/>
       <c r="F119" s="7" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" ht="27">
+    <row r="120" spans="1:8">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="8"/>
       <c r="D120" s="7" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" ht="27">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="8"/>
-      <c r="D121" s="7"/>
+      <c r="D121" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="E121" s="7"/>
       <c r="F121" s="7" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8" ht="40.5">
+    <row r="122" spans="1:8" ht="27">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E122" s="7"/>
       <c r="F122" s="7" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H122" s="7"/>
     </row>
@@ -4235,14 +4327,14 @@
       <c r="B123" s="7"/>
       <c r="C123" s="8"/>
       <c r="D123" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E123" s="7"/>
       <c r="F123" s="7" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H123" s="7"/>
     </row>
@@ -4255,7 +4347,7 @@
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
@@ -4264,173 +4356,169 @@
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="8"/>
-      <c r="D125" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" ht="27">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="8"/>
       <c r="D126" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E126" s="7"/>
       <c r="F126" s="7" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" ht="27">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="8"/>
       <c r="D127" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E127" s="7"/>
       <c r="F127" s="7" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
     </row>
-    <row r="128" spans="1:8" ht="40.5">
-      <c r="A128" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E128" s="4"/>
-      <c r="F128" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H128" s="4"/>
-    </row>
-    <row r="129" spans="1:8" ht="27">
+    <row r="128" spans="1:8">
+      <c r="A128" s="7"/>
+      <c r="B128" s="7"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
-      <c r="C129" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D129" s="7"/>
+      <c r="C129" s="8"/>
+      <c r="D129" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E129" s="7"/>
       <c r="F129" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G129" s="7" t="s">
-        <v>58</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="G129" s="7"/>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" ht="27">
+    <row r="130" spans="1:8" ht="40.5">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
-      <c r="C130" s="8"/>
-      <c r="D130" s="7"/>
+      <c r="C130" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="E130" s="7"/>
       <c r="F130" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>57</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="G130" s="7"/>
       <c r="H130" s="7"/>
     </row>
-    <row r="131" spans="1:8" ht="27">
+    <row r="131" spans="1:8">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="8"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>57</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="G131" s="7"/>
       <c r="H131" s="7"/>
     </row>
     <row r="132" spans="1:8" ht="27">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="8"/>
-      <c r="D132" s="7"/>
+      <c r="D132" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E132" s="7"/>
       <c r="F132" s="7" t="s">
-        <v>144</v>
+        <v>189</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
     </row>
-    <row r="133" spans="1:8" ht="27">
+    <row r="133" spans="1:8">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="8"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
     </row>
-    <row r="134" spans="1:8">
-      <c r="A134" s="7"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-    </row>
-    <row r="135" spans="1:8">
+    <row r="134" spans="1:8" ht="40.5">
+      <c r="A134" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H134" s="4"/>
+    </row>
+    <row r="135" spans="1:8" ht="27">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="8"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="G135" s="7"/>
       <c r="H135" s="7"/>
     </row>
-    <row r="136" spans="1:8" ht="54">
-      <c r="A136" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C136" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D136" s="4"/>
-      <c r="E136" s="11"/>
-      <c r="F136" s="4"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
+    <row r="136" spans="1:8" ht="27">
+      <c r="A136" s="7"/>
+      <c r="B136" s="7"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="7"/>
@@ -4438,25 +4526,25 @@
       <c r="C137" s="8"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
+      <c r="F137" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
     </row>
     <row r="138" spans="1:8" ht="27">
-      <c r="A138" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C138" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D138" s="4"/>
-      <c r="E138" s="11"/>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="7"/>
+      <c r="C138" s="8"/>
+      <c r="D138" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="7"/>
@@ -4464,56 +4552,50 @@
       <c r="C139" s="8"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
+      <c r="F139" s="7" t="s">
+        <v>132</v>
+      </c>
       <c r="G139" s="7"/>
       <c r="H139" s="7"/>
     </row>
     <row r="140" spans="1:8" ht="27">
-      <c r="A140" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C140" s="11"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="H140" s="4"/>
-    </row>
-    <row r="141" spans="1:8" ht="27">
+      <c r="A140" s="7"/>
+      <c r="B140" s="7"/>
+      <c r="C140" s="8"/>
+      <c r="D140" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E140" s="7"/>
+      <c r="F140" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="8"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
       <c r="F141" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="G141" s="7" t="s">
-        <v>161</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="G141" s="7"/>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" ht="27">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="8"/>
-      <c r="D142" s="7"/>
+      <c r="D142" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E142" s="7"/>
       <c r="F142" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G142" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G142" s="7"/>
       <c r="H142" s="7"/>
     </row>
     <row r="143" spans="1:8">
@@ -4523,58 +4605,52 @@
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
       <c r="F143" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G143" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="G143" s="7"/>
       <c r="H143" s="7"/>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" ht="27">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="8"/>
-      <c r="D144" s="7"/>
+      <c r="D144" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="E144" s="7"/>
       <c r="F144" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G144" s="7"/>
       <c r="H144" s="7"/>
     </row>
-    <row r="145" spans="1:8" ht="27">
-      <c r="A145" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C145" s="11"/>
-      <c r="D145" s="4"/>
-      <c r="E145" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="H145" s="4"/>
-    </row>
-    <row r="146" spans="1:8">
+    <row r="145" spans="1:8">
+      <c r="A145" s="7"/>
+      <c r="B145" s="7"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
+    </row>
+    <row r="146" spans="1:8" ht="40.5">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="8"/>
-      <c r="D146" s="7"/>
+      <c r="C146" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E146" s="7"/>
       <c r="F146" s="7" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H146" s="7"/>
     </row>
@@ -4582,229 +4658,229 @@
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
       <c r="C147" s="8"/>
-      <c r="D147" s="7"/>
+      <c r="D147" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="E147" s="7"/>
       <c r="F147" s="7" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H147" s="7"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" ht="27">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="8"/>
-      <c r="D148" s="7"/>
+      <c r="D148" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E148" s="7"/>
       <c r="F148" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G148" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="G148" s="7"/>
       <c r="H148" s="7"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" ht="27">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
       <c r="C149" s="8"/>
-      <c r="D149" s="7"/>
+      <c r="D149" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="E149" s="7"/>
       <c r="F149" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G149" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="G149" s="7"/>
       <c r="H149" s="7"/>
     </row>
-    <row r="150" spans="1:8" ht="39" customHeight="1">
-      <c r="A150" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D150" s="4"/>
-      <c r="E150" s="4"/>
-      <c r="F150" s="4"/>
-      <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
+    <row r="150" spans="1:8">
+      <c r="A150" s="7"/>
+      <c r="B150" s="7"/>
+      <c r="C150" s="8"/>
+      <c r="D150" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G150" s="7"/>
+      <c r="H150" s="7"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="8"/>
-      <c r="D151" s="7"/>
+      <c r="D151" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
+      <c r="F151" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="G151" s="7"/>
       <c r="H151" s="7"/>
     </row>
-    <row r="152" spans="1:8" ht="54">
-      <c r="A152" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D152" s="5"/>
-      <c r="E152" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G152" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H152" s="4"/>
-    </row>
-    <row r="153" spans="1:8" ht="27">
-      <c r="A153" s="8"/>
-      <c r="B153" s="8"/>
+    <row r="152" spans="1:8" ht="40.5">
+      <c r="A152" s="7"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="7"/>
+      <c r="B153" s="7"/>
       <c r="C153" s="8"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
       <c r="F153" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G153" s="7" t="s">
-        <v>92</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G153" s="7"/>
       <c r="H153" s="7"/>
     </row>
     <row r="154" spans="1:8" ht="27">
-      <c r="A154" s="8"/>
-      <c r="B154" s="8"/>
+      <c r="A154" s="7"/>
+      <c r="B154" s="7"/>
       <c r="C154" s="8"/>
-      <c r="D154" s="7"/>
+      <c r="D154" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E154" s="7"/>
-      <c r="F154" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="G154" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="F154" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="G154" s="7"/>
       <c r="H154" s="7"/>
     </row>
-    <row r="155" spans="1:8" ht="27">
-      <c r="A155" s="8"/>
-      <c r="B155" s="8"/>
+    <row r="155" spans="1:8">
+      <c r="A155" s="7"/>
+      <c r="B155" s="7"/>
       <c r="C155" s="8"/>
       <c r="D155" s="7"/>
-      <c r="E155" s="7" t="s">
-        <v>68</v>
-      </c>
+      <c r="E155" s="7"/>
       <c r="F155" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G155" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+    </row>
+    <row r="156" spans="1:8" ht="40.5">
+      <c r="A156" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E156" s="4"/>
+      <c r="F156" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H155" s="7"/>
-    </row>
-    <row r="156" spans="1:8">
-      <c r="A156" s="8"/>
-      <c r="B156" s="8"/>
-      <c r="C156" s="8"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G156" s="7"/>
-      <c r="H156" s="7"/>
+      <c r="G156" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H156" s="4"/>
     </row>
     <row r="157" spans="1:8" ht="27">
-      <c r="A157" s="8"/>
-      <c r="B157" s="8"/>
-      <c r="C157" s="8"/>
+      <c r="A157" s="7"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
       <c r="F157" s="7" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="H157" s="7"/>
     </row>
     <row r="158" spans="1:8" ht="27">
-      <c r="A158" s="8"/>
-      <c r="B158" s="8"/>
+      <c r="A158" s="7"/>
+      <c r="B158" s="7"/>
       <c r="C158" s="8"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
       <c r="F158" s="7" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H158" s="7"/>
     </row>
-    <row r="159" spans="1:8" ht="40.5">
-      <c r="A159" s="8"/>
-      <c r="B159" s="8"/>
-      <c r="C159" s="8" t="s">
-        <v>65</v>
-      </c>
+    <row r="159" spans="1:8" ht="27">
+      <c r="A159" s="7"/>
+      <c r="B159" s="7"/>
+      <c r="C159" s="8"/>
       <c r="D159" s="7"/>
-      <c r="E159" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F159" s="7"/>
-      <c r="G159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="H159" s="7"/>
     </row>
     <row r="160" spans="1:8" ht="27">
-      <c r="A160" s="8"/>
-      <c r="B160" s="8"/>
+      <c r="A160" s="7"/>
+      <c r="B160" s="7"/>
       <c r="C160" s="8"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
       <c r="F160" s="7" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
     </row>
     <row r="161" spans="1:8" ht="27">
-      <c r="A161" s="8"/>
-      <c r="B161" s="8"/>
+      <c r="A161" s="7"/>
+      <c r="B161" s="7"/>
       <c r="C161" s="8"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
-      <c r="F161" s="12" t="s">
-        <v>66</v>
+      <c r="F161" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
     </row>
-    <row r="162" spans="1:8" ht="40.5">
-      <c r="A162" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D162" s="5"/>
-      <c r="E162" s="4"/>
-      <c r="F162" s="4"/>
-      <c r="G162" s="4"/>
-      <c r="H162" s="4"/>
+    <row r="162" spans="1:8" ht="27">
+      <c r="A162" s="7"/>
+      <c r="B162" s="7"/>
+      <c r="C162" s="8"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G162" s="7"/>
+      <c r="H162" s="7"/>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="7"/>
@@ -4812,61 +4888,69 @@
       <c r="C163" s="8"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
+      <c r="F163" s="7" t="s">
+        <v>134</v>
+      </c>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
     </row>
-    <row r="164" spans="1:8" ht="40.5">
-      <c r="A164" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" s="4" t="s">
+    <row r="164" spans="1:8">
+      <c r="A164" s="7"/>
+      <c r="B164" s="7"/>
+      <c r="C164" s="8"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G164" s="7"/>
+      <c r="H164" s="7"/>
+    </row>
+    <row r="165" spans="1:8" ht="54">
+      <c r="A165" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C165" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D165" s="4"/>
+      <c r="E165" s="11"/>
+      <c r="F165" s="4"/>
+      <c r="G165" s="4"/>
+      <c r="H165" s="4"/>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="7"/>
+      <c r="B166" s="7"/>
+      <c r="C166" s="8"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
+    </row>
+    <row r="167" spans="1:8" ht="27">
+      <c r="A167" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B167" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C164" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D164" s="5"/>
-      <c r="E164" s="4"/>
-      <c r="F164" s="4"/>
-      <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
-    </row>
-    <row r="165" spans="1:8">
-      <c r="C165" s="8"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
-    </row>
-    <row r="166" spans="1:8" ht="40.5">
-      <c r="A166" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C166" s="5"/>
-      <c r="D166" s="4"/>
-      <c r="E166" s="4"/>
-      <c r="F166" s="4"/>
-      <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
-    </row>
-    <row r="167" spans="1:8">
-      <c r="A167" s="8"/>
-      <c r="B167" s="8"/>
-      <c r="C167" s="8"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-      <c r="G167" s="7"/>
-      <c r="H167" s="7"/>
+      <c r="C167" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D167" s="4"/>
+      <c r="E167" s="11"/>
+      <c r="F167" s="4"/>
+      <c r="G167" s="4"/>
+      <c r="H167" s="4"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="8"/>
-      <c r="B168" s="8"/>
+      <c r="A168" s="7"/>
+      <c r="B168" s="7"/>
       <c r="C168" s="8"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
@@ -4874,14 +4958,476 @@
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
     </row>
-    <row r="169" spans="1:8">
-      <c r="D169" s="9"/>
-      <c r="E169" s="9"/>
-      <c r="F169" s="9"/>
-      <c r="G169" s="9"/>
+    <row r="169" spans="1:8" ht="27">
+      <c r="A169" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="11"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H169" s="4"/>
+    </row>
+    <row r="170" spans="1:8" ht="27">
+      <c r="A170" s="7"/>
+      <c r="B170" s="7"/>
+      <c r="C170" s="8"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G170" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H170" s="7"/>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="7"/>
+      <c r="B171" s="7"/>
+      <c r="C171" s="8"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G171" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H171" s="7"/>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="7"/>
+      <c r="B172" s="7"/>
+      <c r="C172" s="8"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H172" s="7"/>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="7"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="8"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H173" s="7"/>
+    </row>
+    <row r="174" spans="1:8" ht="27">
+      <c r="A174" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="11"/>
+      <c r="D174" s="4"/>
+      <c r="E174" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H174" s="4"/>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="7"/>
+      <c r="B175" s="7"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H175" s="7"/>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="7"/>
+      <c r="B176" s="7"/>
+      <c r="C176" s="8"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="7"/>
+      <c r="F176" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H176" s="7"/>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="7"/>
+      <c r="B177" s="7"/>
+      <c r="C177" s="8"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G177" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H177" s="7"/>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="7"/>
+      <c r="B178" s="7"/>
+      <c r="C178" s="8"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G178" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H178" s="7"/>
+    </row>
+    <row r="179" spans="1:8" ht="39" customHeight="1">
+      <c r="A179" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C179" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D179" s="4"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4"/>
+      <c r="G179" s="4"/>
+      <c r="H179" s="4"/>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" s="7"/>
+      <c r="B180" s="7"/>
+      <c r="C180" s="8"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="7"/>
+      <c r="F180" s="7"/>
+      <c r="G180" s="7"/>
+      <c r="H180" s="7"/>
+    </row>
+    <row r="181" spans="1:8" ht="54">
+      <c r="A181" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D181" s="5"/>
+      <c r="E181" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H181" s="4"/>
+    </row>
+    <row r="182" spans="1:8" ht="27">
+      <c r="A182" s="8"/>
+      <c r="B182" s="8"/>
+      <c r="C182" s="8"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G182" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H182" s="7"/>
+    </row>
+    <row r="183" spans="1:8" ht="27">
+      <c r="A183" s="8"/>
+      <c r="B183" s="8"/>
+      <c r="C183" s="8"/>
+      <c r="D183" s="7"/>
+      <c r="E183" s="7"/>
+      <c r="F183" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G183" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H183" s="7"/>
+    </row>
+    <row r="184" spans="1:8" ht="27">
+      <c r="A184" s="8"/>
+      <c r="B184" s="8"/>
+      <c r="C184" s="8"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G184" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H184" s="7"/>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="8"/>
+      <c r="B185" s="8"/>
+      <c r="C185" s="8"/>
+      <c r="D185" s="7"/>
+      <c r="E185" s="7"/>
+      <c r="F185" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G185" s="7"/>
+      <c r="H185" s="7"/>
+    </row>
+    <row r="186" spans="1:8" ht="27">
+      <c r="A186" s="8"/>
+      <c r="B186" s="8"/>
+      <c r="C186" s="8"/>
+      <c r="D186" s="7"/>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G186" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H186" s="7"/>
+    </row>
+    <row r="187" spans="1:8" ht="27">
+      <c r="A187" s="8"/>
+      <c r="B187" s="8"/>
+      <c r="C187" s="8"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G187" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H187" s="7"/>
+    </row>
+    <row r="188" spans="1:8" ht="40.5">
+      <c r="A188" s="8"/>
+      <c r="B188" s="8"/>
+      <c r="C188" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D188" s="7"/>
+      <c r="E188" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G188" s="7"/>
+      <c r="H188" s="7"/>
+    </row>
+    <row r="189" spans="1:8" ht="27">
+      <c r="A189" s="8"/>
+      <c r="B189" s="8"/>
+      <c r="C189" s="8"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
+    </row>
+    <row r="190" spans="1:8" ht="27">
+      <c r="A190" s="8"/>
+      <c r="B190" s="8"/>
+      <c r="C190" s="8"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
+      <c r="F190" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
+    </row>
+    <row r="191" spans="1:8" ht="40.5">
+      <c r="A191" s="7"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G191" s="7"/>
+      <c r="H191" s="7"/>
+    </row>
+    <row r="192" spans="1:8" ht="27">
+      <c r="A192" s="7"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="8"/>
+      <c r="D192" s="7"/>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G192" s="7"/>
+      <c r="H192" s="7"/>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="7"/>
+      <c r="B193" s="7"/>
+      <c r="C193" s="8"/>
+      <c r="D193" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G193" s="7"/>
+      <c r="H193" s="7"/>
+    </row>
+    <row r="194" spans="1:8" ht="27">
+      <c r="A194" s="7"/>
+      <c r="B194" s="7"/>
+      <c r="C194" s="8"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G194" s="7"/>
+      <c r="H194" s="7"/>
+    </row>
+    <row r="195" spans="1:8" ht="40.5">
+      <c r="A195" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195" s="5"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
+      <c r="G195" s="4"/>
+      <c r="H195" s="4"/>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" s="7"/>
+      <c r="B196" s="7"/>
+      <c r="C196" s="8"/>
+      <c r="D196" s="7"/>
+      <c r="E196" s="7"/>
+      <c r="F196" s="7"/>
+      <c r="G196" s="7"/>
+      <c r="H196" s="7"/>
+    </row>
+    <row r="197" spans="1:8" ht="40.5">
+      <c r="A197" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D197" s="5"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
+      <c r="H197" s="4"/>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="C198" s="8"/>
+      <c r="D198" s="7"/>
+      <c r="E198" s="7"/>
+      <c r="F198" s="7"/>
+      <c r="G198" s="7"/>
+      <c r="H198" s="7"/>
+    </row>
+    <row r="199" spans="1:8" ht="40.5">
+      <c r="A199" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C199" s="5"/>
+      <c r="D199" s="4"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4"/>
+      <c r="G199" s="4"/>
+      <c r="H199" s="4"/>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="8"/>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
+      <c r="D200" s="7"/>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
+      <c r="G200" s="7"/>
+      <c r="H200" s="7"/>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="8"/>
+      <c r="B201" s="8"/>
+      <c r="C201" s="8"/>
+      <c r="D201" s="7"/>
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
+      <c r="G201" s="7"/>
+      <c r="H201" s="7"/>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="D202" s="9"/>
+      <c r="E202" s="9"/>
+      <c r="F202" s="9"/>
+      <c r="G202" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H94">
+  <autoFilter ref="A1:H110">
     <filterColumn colId="4"/>
   </autoFilter>
   <mergeCells count="1">

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$106</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -590,7 +590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D67" authorId="0">
+    <comment ref="D65" authorId="0">
       <text>
         <r>
           <rPr>
@@ -636,7 +636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D80" authorId="0">
+    <comment ref="D78" authorId="0">
       <text>
         <r>
           <rPr>
@@ -662,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D84" authorId="0">
+    <comment ref="D82" authorId="0">
       <text>
         <r>
           <rPr>
@@ -696,7 +696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D97" authorId="0">
+    <comment ref="D93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -722,7 +722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F139" authorId="0">
+    <comment ref="F133" authorId="0">
       <text>
         <r>
           <rPr>
@@ -748,7 +748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F156" authorId="0">
+    <comment ref="F150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A169" authorId="0">
+    <comment ref="A163" authorId="0">
       <text>
         <r>
           <rPr>
@@ -808,7 +808,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="198">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1958,18 +1958,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>catalog主节点CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目标主机内存耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>catalog主节点内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目标主机时间跳变</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1999,6 +1991,26 @@
   </si>
   <si>
     <t>重复多次强制detach节点后再次attach到同一个节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分离前节点所在主机断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机内存耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2550,7 +2562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2881,9 +2893,11 @@
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>194</v>
+      </c>
       <c r="F21" s="7" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>172</v>
@@ -3223,7 +3237,7 @@
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
@@ -3493,7 +3507,7 @@
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -3502,67 +3516,69 @@
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="8"/>
-      <c r="D64" s="7"/>
+      <c r="D64" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-    </row>
-    <row r="66" spans="1:8">
+    <row r="65" spans="1:8" ht="40.5">
+      <c r="A65" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" spans="1:8" ht="27">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" ht="40.5">
-      <c r="A67" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H67" s="4"/>
+    <row r="67" spans="1:8">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
     </row>
     <row r="68" spans="1:8" ht="27">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="8"/>
-      <c r="D68" s="7"/>
+      <c r="D68" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
         <v>126</v>
@@ -3587,7 +3603,7 @@
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
       <c r="D70" s="7" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
@@ -3613,7 +3629,7 @@
       <c r="B72" s="7"/>
       <c r="C72" s="8"/>
       <c r="D72" s="7" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
@@ -3638,8 +3654,8 @@
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="8"/>
-      <c r="D74" s="7" t="s">
-        <v>43</v>
+      <c r="D74" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
@@ -3664,8 +3680,8 @@
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="8"/>
-      <c r="D76" s="13" t="s">
-        <v>160</v>
+      <c r="D76" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="7" t="s">
@@ -3690,8 +3706,8 @@
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8"/>
-      <c r="D78" s="7" t="s">
-        <v>27</v>
+      <c r="D78" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
@@ -3716,8 +3732,8 @@
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
-      <c r="D80" s="13" t="s">
-        <v>28</v>
+      <c r="D80" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
@@ -3738,74 +3754,80 @@
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" ht="27">
+    <row r="82" spans="1:8" ht="40.5">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="8"/>
+      <c r="C82" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="D82" s="7" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
+        <v>122</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H82" s="13" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="7"/>
+      <c r="D83" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="E83" s="7"/>
       <c r="F83" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G83" s="7"/>
+      <c r="G83" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8" ht="40.5">
+    <row r="84" spans="1:8" ht="27">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="C84" s="8"/>
       <c r="D84" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>183</v>
+      </c>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+    </row>
+    <row r="85" spans="1:8" ht="27">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
       <c r="D85" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H85" s="7"/>
-    </row>
-    <row r="86" spans="1:8" ht="27">
+        <v>183</v>
+      </c>
+      <c r="G85" s="7"/>
+      <c r="H85" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="40.5">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
-      <c r="C86" s="8"/>
+      <c r="C86" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="D86" s="7" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
@@ -3814,46 +3836,48 @@
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" ht="27">
+    <row r="87" spans="1:8">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="D87" s="7"/>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="G87" s="7"/>
-      <c r="H87" s="13" t="s">
-        <v>130</v>
-      </c>
+      <c r="H87" s="7"/>
     </row>
     <row r="88" spans="1:8" ht="40.5">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-    </row>
-    <row r="89" spans="1:8">
+      <c r="A88" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" ht="27">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
-        <v>183</v>
+        <v>128</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
@@ -3862,55 +3886,47 @@
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
-      <c r="D90" s="7" t="s">
-        <v>167</v>
-      </c>
+      <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" ht="27">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="7"/>
+      <c r="D91" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
-        <v>183</v>
+        <v>128</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8" ht="40.5">
-      <c r="A92" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H92" s="4"/>
+    <row r="92" spans="1:8">
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
     </row>
     <row r="93" spans="1:8" ht="27">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="7"/>
+      <c r="D93" s="13" t="s">
+        <v>26</v>
+      </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
         <v>128</v>
@@ -3925,7 +3941,7 @@
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
@@ -3935,11 +3951,11 @@
       <c r="B95" s="7"/>
       <c r="C95" s="8"/>
       <c r="D95" s="7" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
@@ -3951,7 +3967,7 @@
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
@@ -3961,7 +3977,7 @@
       <c r="B97" s="7"/>
       <c r="C97" s="8"/>
       <c r="D97" s="13" t="s">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
@@ -3991,7 +4007,7 @@
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
@@ -4003,7 +4019,7 @@
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
@@ -4012,8 +4028,8 @@
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="13" t="s">
-        <v>160</v>
+      <c r="D101" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7" t="s">
@@ -4029,7 +4045,7 @@
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
       <c r="F102" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
@@ -4039,7 +4055,7 @@
       <c r="B103" s="7"/>
       <c r="C103" s="8"/>
       <c r="D103" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="7" t="s">
@@ -4055,47 +4071,57 @@
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
     </row>
-    <row r="105" spans="1:8" ht="27">
+    <row r="105" spans="1:8" ht="40.5">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="8"/>
       <c r="D105" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
+        <v>184</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="7"/>
+      <c r="D106" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G106" s="7"/>
+      <c r="G106" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8" ht="27">
+    <row r="107" spans="1:8" ht="40.5">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
-      <c r="C107" s="8"/>
+      <c r="C107" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="D107" s="7" t="s">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
@@ -4104,60 +4130,60 @@
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="7"/>
+      <c r="D108" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E108" s="7"/>
       <c r="F108" s="7" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
     </row>
     <row r="109" spans="1:8" ht="40.5">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H109" s="13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
+      <c r="A109" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" ht="27">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="8"/>
-      <c r="D110" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="D110" s="7"/>
       <c r="E110" s="7"/>
       <c r="F110" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>47</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="G110" s="7"/>
       <c r="H110" s="7"/>
     </row>
-    <row r="111" spans="1:8" ht="40.5">
+    <row r="111" spans="1:8">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
-      <c r="C111" s="8" t="s">
-        <v>164</v>
-      </c>
+      <c r="C111" s="8"/>
       <c r="D111" s="7" t="s">
-        <v>165</v>
+        <v>36</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
@@ -4166,24 +4192,26 @@
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="8"/>
-      <c r="D112" s="7"/>
+      <c r="D112" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="E112" s="7"/>
       <c r="F112" s="7" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" ht="27">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="8"/>
       <c r="D113" s="7" t="s">
-        <v>167</v>
+        <v>43</v>
       </c>
       <c r="E113" s="7"/>
       <c r="F113" s="7" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
@@ -4192,46 +4220,46 @@
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="8"/>
-      <c r="D114" s="7"/>
+      <c r="D114" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E114" s="7"/>
       <c r="F114" s="7" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" ht="40.5">
-      <c r="A115" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E115" s="4"/>
-      <c r="F115" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H115" s="4"/>
+    <row r="115" spans="1:8" ht="27">
+      <c r="A115" s="7"/>
+      <c r="B115" s="7"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
     </row>
     <row r="116" spans="1:8" ht="27">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="7"/>
+      <c r="C116" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E116" s="7"/>
       <c r="F116" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G116" s="7"/>
+        <v>124</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="H116" s="7"/>
     </row>
     <row r="117" spans="1:8">
@@ -4239,21 +4267,23 @@
       <c r="B117" s="7"/>
       <c r="C117" s="8"/>
       <c r="D117" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E117" s="7"/>
       <c r="F117" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G117" s="7"/>
+      <c r="G117" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" ht="27">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="8"/>
       <c r="D118" s="7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7" t="s">
@@ -4266,22 +4296,20 @@
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
-      <c r="D119" s="7" t="s">
-        <v>43</v>
-      </c>
+      <c r="D119" s="7"/>
       <c r="E119" s="7"/>
       <c r="F119" s="7" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" ht="27">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="8"/>
       <c r="D120" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7" t="s">
@@ -4295,31 +4323,25 @@
       <c r="B121" s="7"/>
       <c r="C121" s="8"/>
       <c r="D121" s="7" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E121" s="7"/>
       <c r="F121" s="7" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8" ht="27">
+    <row r="122" spans="1:8">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
-      <c r="C122" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C122" s="8"/>
+      <c r="D122" s="7"/>
       <c r="E122" s="7"/>
       <c r="F122" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>58</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="G122" s="7"/>
       <c r="H122" s="7"/>
     </row>
     <row r="123" spans="1:8">
@@ -4327,39 +4349,39 @@
       <c r="B123" s="7"/>
       <c r="C123" s="8"/>
       <c r="D123" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E123" s="7"/>
       <c r="F123" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G123" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="G123" s="7"/>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" ht="27">
+    <row r="124" spans="1:8" ht="40.5">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
-      <c r="C124" s="8"/>
+      <c r="C124" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="D124" s="7" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
     </row>
-    <row r="125" spans="1:8" ht="27">
+    <row r="125" spans="1:8">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="8"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
@@ -4369,67 +4391,71 @@
       <c r="B126" s="7"/>
       <c r="C126" s="8"/>
       <c r="D126" s="7" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="E126" s="7"/>
       <c r="F126" s="7" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
     </row>
-    <row r="127" spans="1:8" ht="27">
+    <row r="127" spans="1:8">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="8"/>
-      <c r="D127" s="7" t="s">
-        <v>31</v>
-      </c>
+      <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
     </row>
-    <row r="128" spans="1:8">
-      <c r="A128" s="7"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="8"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-    </row>
-    <row r="129" spans="1:8">
+    <row r="128" spans="1:8" ht="40.5">
+      <c r="A128" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H128" s="4"/>
+    </row>
+    <row r="129" spans="1:8" ht="27">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="8"/>
-      <c r="D129" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" ht="40.5">
+    <row r="130" spans="1:8" ht="27">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
-      <c r="C130" s="8" t="s">
-        <v>164</v>
-      </c>
+      <c r="C130" s="8"/>
       <c r="D130" s="7" t="s">
-        <v>165</v>
+        <v>36</v>
       </c>
       <c r="E130" s="7"/>
       <c r="F130" s="7" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
@@ -4441,7 +4467,7 @@
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7" t="s">
-        <v>187</v>
+        <v>131</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="7"/>
@@ -4451,11 +4477,11 @@
       <c r="B132" s="7"/>
       <c r="C132" s="8"/>
       <c r="D132" s="7" t="s">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="E132" s="7"/>
       <c r="F132" s="7" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
@@ -4467,41 +4493,33 @@
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
     </row>
-    <row r="134" spans="1:8" ht="40.5">
-      <c r="A134" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E134" s="4"/>
-      <c r="F134" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H134" s="4"/>
-    </row>
-    <row r="135" spans="1:8" ht="27">
+    <row r="134" spans="1:8" ht="27">
+      <c r="A134" s="7"/>
+      <c r="B134" s="7"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="8"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="G135" s="7"/>
       <c r="H135" s="7"/>
@@ -4511,7 +4529,7 @@
       <c r="B136" s="7"/>
       <c r="C136" s="8"/>
       <c r="D136" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E136" s="7"/>
       <c r="F136" s="7" t="s">
@@ -4537,7 +4555,7 @@
       <c r="B138" s="7"/>
       <c r="C138" s="8"/>
       <c r="D138" s="7" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="7" t="s">
@@ -4553,35 +4571,43 @@
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
       <c r="F139" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G139" s="7"/>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" ht="27">
+    <row r="140" spans="1:8" ht="40.5">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="8"/>
+      <c r="C140" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="D140" s="7" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G140" s="7"/>
+        <v>125</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="H140" s="7"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="8"/>
-      <c r="D141" s="7"/>
+      <c r="D141" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="E141" s="7"/>
       <c r="F141" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="G141" s="7"/>
+        <v>125</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="H141" s="7"/>
     </row>
     <row r="142" spans="1:8" ht="27">
@@ -4589,37 +4615,39 @@
       <c r="B142" s="7"/>
       <c r="C142" s="8"/>
       <c r="D142" s="7" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E142" s="7"/>
       <c r="F142" s="7" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="G142" s="7"/>
       <c r="H142" s="7"/>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" ht="27">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="8"/>
-      <c r="D143" s="7"/>
+      <c r="D143" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="E143" s="7"/>
       <c r="F143" s="7" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G143" s="7"/>
       <c r="H143" s="7"/>
     </row>
-    <row r="144" spans="1:8" ht="27">
+    <row r="144" spans="1:8">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="8"/>
       <c r="D144" s="7" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E144" s="7"/>
       <c r="F144" s="7" t="s">
-        <v>93</v>
+        <v>188</v>
       </c>
       <c r="G144" s="7"/>
       <c r="H144" s="7"/>
@@ -4628,10 +4656,12 @@
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
       <c r="C145" s="8"/>
-      <c r="D145" s="7"/>
+      <c r="D145" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E145" s="7"/>
       <c r="F145" s="7" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="7"/>
@@ -4640,34 +4670,28 @@
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="8" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="E146" s="7"/>
       <c r="F146" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>46</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="G146" s="7"/>
       <c r="H146" s="7"/>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
       <c r="C147" s="8"/>
-      <c r="D147" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="D147" s="7"/>
       <c r="E147" s="7"/>
       <c r="F147" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>47</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="G147" s="7"/>
       <c r="H147" s="7"/>
     </row>
     <row r="148" spans="1:8" ht="27">
@@ -4675,252 +4699,252 @@
       <c r="B148" s="7"/>
       <c r="C148" s="8"/>
       <c r="D148" s="7" t="s">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="E148" s="7"/>
       <c r="F148" s="7" t="s">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="G148" s="7"/>
       <c r="H148" s="7"/>
     </row>
-    <row r="149" spans="1:8" ht="27">
+    <row r="149" spans="1:8">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
       <c r="C149" s="8"/>
-      <c r="D149" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="D149" s="7"/>
       <c r="E149" s="7"/>
       <c r="F149" s="7" t="s">
-        <v>125</v>
+        <v>188</v>
       </c>
       <c r="G149" s="7"/>
       <c r="H149" s="7"/>
     </row>
-    <row r="150" spans="1:8">
-      <c r="A150" s="7"/>
-      <c r="B150" s="7"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G150" s="7"/>
-      <c r="H150" s="7"/>
-    </row>
-    <row r="151" spans="1:8">
+    <row r="150" spans="1:8" ht="40.5">
+      <c r="A150" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H150" s="4"/>
+    </row>
+    <row r="151" spans="1:8" ht="27">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
-      <c r="C151" s="8"/>
-      <c r="D151" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="C151" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D151" s="7"/>
       <c r="E151" s="7"/>
       <c r="F151" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G151" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="H151" s="7"/>
     </row>
-    <row r="152" spans="1:8" ht="40.5">
+    <row r="152" spans="1:8" ht="27">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
-      <c r="C152" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D152" s="7" t="s">
-        <v>165</v>
-      </c>
+      <c r="C152" s="8"/>
+      <c r="D152" s="7"/>
       <c r="E152" s="7"/>
       <c r="F152" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="G152" s="7"/>
+        <v>53</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="H152" s="7"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" ht="27">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
       <c r="C153" s="8"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
       <c r="F153" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G153" s="7"/>
+        <v>54</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="H153" s="7"/>
     </row>
     <row r="154" spans="1:8" ht="27">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="8"/>
-      <c r="D154" s="7" t="s">
-        <v>167</v>
-      </c>
+      <c r="D154" s="7"/>
       <c r="E154" s="7"/>
       <c r="F154" s="7" t="s">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" ht="27">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="8"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
       <c r="F155" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G155" s="7"/>
       <c r="H155" s="7"/>
     </row>
-    <row r="156" spans="1:8" ht="40.5">
-      <c r="A156" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D156" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E156" s="4"/>
-      <c r="F156" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G156" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H156" s="4"/>
-    </row>
-    <row r="157" spans="1:8" ht="27">
+    <row r="156" spans="1:8" ht="27">
+      <c r="A156" s="7"/>
+      <c r="B156" s="7"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
-      <c r="C157" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="C157" s="8"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
       <c r="F157" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>56</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G157" s="7"/>
       <c r="H157" s="7"/>
     </row>
-    <row r="158" spans="1:8" ht="27">
+    <row r="158" spans="1:8">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="8"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
       <c r="F158" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="G158" s="7"/>
       <c r="H158" s="7"/>
     </row>
-    <row r="159" spans="1:8" ht="27">
-      <c r="A159" s="7"/>
-      <c r="B159" s="7"/>
-      <c r="C159" s="8"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G159" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H159" s="7"/>
-    </row>
-    <row r="160" spans="1:8" ht="27">
+    <row r="159" spans="1:8" ht="54">
+      <c r="A159" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D159" s="4"/>
+      <c r="E159" s="11"/>
+      <c r="F159" s="4"/>
+      <c r="G159" s="4"/>
+      <c r="H159" s="4"/>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
       <c r="C160" s="8"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
-      <c r="F160" s="7" t="s">
-        <v>136</v>
-      </c>
+      <c r="F160" s="7"/>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
     </row>
     <row r="161" spans="1:8" ht="27">
-      <c r="A161" s="7"/>
-      <c r="B161" s="7"/>
-      <c r="C161" s="8"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="G161" s="7"/>
-      <c r="H161" s="7"/>
-    </row>
-    <row r="162" spans="1:8" ht="27">
+      <c r="A161" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D161" s="4"/>
+      <c r="E161" s="11"/>
+      <c r="F161" s="4"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="8"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
-      <c r="F162" s="7" t="s">
-        <v>133</v>
-      </c>
+      <c r="F162" s="7"/>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
     </row>
-    <row r="163" spans="1:8">
-      <c r="A163" s="7"/>
-      <c r="B163" s="7"/>
-      <c r="C163" s="8"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="G163" s="7"/>
-      <c r="H163" s="7"/>
-    </row>
-    <row r="164" spans="1:8">
+    <row r="163" spans="1:8" ht="27">
+      <c r="A163" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="11"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H163" s="4"/>
+    </row>
+    <row r="164" spans="1:8" ht="27">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="8"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G164" s="7"/>
+        <v>149</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>153</v>
+      </c>
       <c r="H164" s="7"/>
     </row>
-    <row r="165" spans="1:8" ht="54">
-      <c r="A165" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C165" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D165" s="4"/>
-      <c r="E165" s="11"/>
-      <c r="F165" s="4"/>
-      <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
+    <row r="165" spans="1:8">
+      <c r="A165" s="7"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="8"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G165" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H165" s="7"/>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="7"/>
@@ -4928,67 +4952,73 @@
       <c r="C166" s="8"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
-      <c r="G166" s="7"/>
+      <c r="F166" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G166" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="H166" s="7"/>
     </row>
-    <row r="167" spans="1:8" ht="27">
-      <c r="A167" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B167" s="4" t="s">
+    <row r="167" spans="1:8">
+      <c r="A167" s="7"/>
+      <c r="B167" s="7"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G167" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H167" s="7"/>
+    </row>
+    <row r="168" spans="1:8" ht="27">
+      <c r="A168" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B168" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C167" s="11" t="s">
+      <c r="C168" s="11"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H168" s="4"/>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="7"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="8"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G169" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D167" s="4"/>
-      <c r="E167" s="11"/>
-      <c r="F167" s="4"/>
-      <c r="G167" s="4"/>
-      <c r="H167" s="4"/>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="A168" s="7"/>
-      <c r="B168" s="7"/>
-      <c r="C168" s="8"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
-      <c r="G168" s="7"/>
-      <c r="H168" s="7"/>
-    </row>
-    <row r="169" spans="1:8" ht="27">
-      <c r="A169" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C169" s="11"/>
-      <c r="D169" s="4"/>
-      <c r="E169" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F169" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H169" s="4"/>
-    </row>
-    <row r="170" spans="1:8" ht="27">
+      <c r="H169" s="7"/>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="8"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
       <c r="F170" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="H170" s="7"/>
     </row>
@@ -4999,7 +5029,7 @@
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
       <c r="F171" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>47</v>
@@ -5013,163 +5043,159 @@
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
       <c r="F172" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>47</v>
       </c>
       <c r="H172" s="7"/>
     </row>
-    <row r="173" spans="1:8">
-      <c r="A173" s="7"/>
-      <c r="B173" s="7"/>
-      <c r="C173" s="8"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G173" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H173" s="7"/>
-    </row>
-    <row r="174" spans="1:8" ht="27">
-      <c r="A174" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174" s="11"/>
-      <c r="D174" s="4"/>
-      <c r="E174" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F174" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G174" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H174" s="4"/>
-    </row>
-    <row r="175" spans="1:8">
-      <c r="A175" s="7"/>
-      <c r="B175" s="7"/>
-      <c r="C175" s="8"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G175" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H175" s="7"/>
-    </row>
-    <row r="176" spans="1:8">
-      <c r="A176" s="7"/>
-      <c r="B176" s="7"/>
+    <row r="173" spans="1:8" ht="39" customHeight="1">
+      <c r="A173" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C173" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D173" s="4"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4"/>
+      <c r="G173" s="4"/>
+      <c r="H173" s="4"/>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="7"/>
+      <c r="B174" s="7"/>
+      <c r="C174" s="8"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="7"/>
+      <c r="G174" s="7"/>
+      <c r="H174" s="7"/>
+    </row>
+    <row r="175" spans="1:8" ht="54">
+      <c r="A175" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D175" s="5"/>
+      <c r="E175" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H175" s="4"/>
+    </row>
+    <row r="176" spans="1:8" ht="27">
+      <c r="A176" s="8"/>
+      <c r="B176" s="8"/>
       <c r="C176" s="8"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
       <c r="F176" s="7" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="H176" s="7"/>
     </row>
-    <row r="177" spans="1:8">
-      <c r="A177" s="7"/>
-      <c r="B177" s="7"/>
+    <row r="177" spans="1:8" ht="27">
+      <c r="A177" s="8"/>
+      <c r="B177" s="8"/>
       <c r="C177" s="8"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
-      <c r="F177" s="7" t="s">
-        <v>151</v>
+      <c r="F177" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H177" s="7"/>
     </row>
-    <row r="178" spans="1:8">
-      <c r="A178" s="7"/>
-      <c r="B178" s="7"/>
+    <row r="178" spans="1:8" ht="27">
+      <c r="A178" s="8"/>
+      <c r="B178" s="8"/>
       <c r="C178" s="8"/>
       <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
+      <c r="E178" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="F178" s="7" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="H178" s="7"/>
     </row>
-    <row r="179" spans="1:8" ht="39" customHeight="1">
-      <c r="A179" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C179" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D179" s="4"/>
-      <c r="E179" s="4"/>
-      <c r="F179" s="4"/>
-      <c r="G179" s="4"/>
-      <c r="H179" s="4"/>
-    </row>
-    <row r="180" spans="1:8">
-      <c r="A180" s="7"/>
-      <c r="B180" s="7"/>
+    <row r="179" spans="1:8">
+      <c r="A179" s="8"/>
+      <c r="B179" s="8"/>
+      <c r="C179" s="8"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="7"/>
+      <c r="F179" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G179" s="7"/>
+      <c r="H179" s="7"/>
+    </row>
+    <row r="180" spans="1:8" ht="27">
+      <c r="A180" s="8"/>
+      <c r="B180" s="8"/>
       <c r="C180" s="8"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
-      <c r="F180" s="7"/>
-      <c r="G180" s="7"/>
+      <c r="F180" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G180" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="H180" s="7"/>
     </row>
-    <row r="181" spans="1:8" ht="54">
-      <c r="A181" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D181" s="5"/>
-      <c r="E181" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F181" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="G181" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="H181" s="4"/>
-    </row>
-    <row r="182" spans="1:8" ht="27">
+    <row r="181" spans="1:8" ht="27">
+      <c r="A181" s="8"/>
+      <c r="B181" s="8"/>
+      <c r="C181" s="8"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="7"/>
+      <c r="F181" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G181" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H181" s="7"/>
+    </row>
+    <row r="182" spans="1:8" ht="40.5">
       <c r="A182" s="8"/>
       <c r="B182" s="8"/>
-      <c r="C182" s="8"/>
+      <c r="C182" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
+      <c r="E182" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="F182" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G182" s="7" t="s">
-        <v>87</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="G182" s="7"/>
       <c r="H182" s="7"/>
     </row>
     <row r="183" spans="1:8" ht="27">
@@ -5178,12 +5204,10 @@
       <c r="C183" s="8"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
-      <c r="F183" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G183" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="F183" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G183" s="7"/>
       <c r="H183" s="7"/>
     </row>
     <row r="184" spans="1:8" ht="27">
@@ -5191,243 +5215,159 @@
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
       <c r="D184" s="7"/>
-      <c r="E184" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F184" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G184" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="E184" s="7"/>
+      <c r="F184" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G184" s="7"/>
       <c r="H184" s="7"/>
     </row>
-    <row r="185" spans="1:8">
-      <c r="A185" s="8"/>
-      <c r="B185" s="8"/>
-      <c r="C185" s="8"/>
-      <c r="D185" s="7"/>
+    <row r="185" spans="1:8" ht="40.5">
+      <c r="A185" s="7"/>
+      <c r="B185" s="7"/>
+      <c r="C185" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="E185" s="7"/>
-      <c r="F185" s="13" t="s">
-        <v>66</v>
+      <c r="F185" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="G185" s="7"/>
       <c r="H185" s="7"/>
     </row>
     <row r="186" spans="1:8" ht="27">
-      <c r="A186" s="8"/>
-      <c r="B186" s="8"/>
+      <c r="A186" s="7"/>
+      <c r="B186" s="7"/>
       <c r="C186" s="8"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G186" s="7" t="s">
-        <v>67</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G186" s="7"/>
       <c r="H186" s="7"/>
     </row>
-    <row r="187" spans="1:8" ht="27">
-      <c r="A187" s="8"/>
-      <c r="B187" s="8"/>
+    <row r="187" spans="1:8">
+      <c r="A187" s="7"/>
+      <c r="B187" s="7"/>
       <c r="C187" s="8"/>
-      <c r="D187" s="7"/>
+      <c r="D187" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E187" s="7"/>
       <c r="F187" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G187" s="7" t="s">
-        <v>70</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="G187" s="7"/>
       <c r="H187" s="7"/>
     </row>
-    <row r="188" spans="1:8" ht="40.5">
-      <c r="A188" s="8"/>
-      <c r="B188" s="8"/>
-      <c r="C188" s="8" t="s">
-        <v>62</v>
-      </c>
+    <row r="188" spans="1:8" ht="27">
+      <c r="A188" s="7"/>
+      <c r="B188" s="7"/>
+      <c r="C188" s="8"/>
       <c r="D188" s="7"/>
-      <c r="E188" s="7" t="s">
-        <v>64</v>
-      </c>
+      <c r="E188" s="7"/>
       <c r="F188" s="7" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
     </row>
-    <row r="189" spans="1:8" ht="27">
-      <c r="A189" s="8"/>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
-      <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G189" s="7"/>
-      <c r="H189" s="7"/>
-    </row>
-    <row r="190" spans="1:8" ht="27">
-      <c r="A190" s="8"/>
-      <c r="B190" s="8"/>
+    <row r="189" spans="1:8" ht="40.5">
+      <c r="A189" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189" s="5"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="7"/>
+      <c r="B190" s="7"/>
       <c r="C190" s="8"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
-      <c r="F190" s="12" t="s">
-        <v>63</v>
-      </c>
+      <c r="F190" s="7"/>
       <c r="G190" s="7"/>
       <c r="H190" s="7"/>
     </row>
     <row r="191" spans="1:8" ht="40.5">
-      <c r="A191" s="7"/>
-      <c r="B191" s="7"/>
-      <c r="C191" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D191" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E191" s="7"/>
-      <c r="F191" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G191" s="7"/>
-      <c r="H191" s="7"/>
-    </row>
-    <row r="192" spans="1:8" ht="27">
-      <c r="A192" s="7"/>
-      <c r="B192" s="7"/>
+      <c r="A191" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D191" s="5"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
+      <c r="G191" s="4"/>
+      <c r="H191" s="4"/>
+    </row>
+    <row r="192" spans="1:8">
       <c r="C192" s="8"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
-      <c r="F192" s="7" t="s">
-        <v>97</v>
-      </c>
+      <c r="F192" s="7"/>
       <c r="G192" s="7"/>
       <c r="H192" s="7"/>
     </row>
-    <row r="193" spans="1:8">
-      <c r="A193" s="7"/>
-      <c r="B193" s="7"/>
-      <c r="C193" s="8"/>
-      <c r="D193" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G193" s="7"/>
-      <c r="H193" s="7"/>
-    </row>
-    <row r="194" spans="1:8" ht="27">
-      <c r="A194" s="7"/>
-      <c r="B194" s="7"/>
+    <row r="193" spans="1:8" ht="40.5">
+      <c r="A193" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C193" s="5"/>
+      <c r="D193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4"/>
+      <c r="G193" s="4"/>
+      <c r="H193" s="4"/>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" s="8"/>
+      <c r="B194" s="8"/>
       <c r="C194" s="8"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7"/>
-      <c r="F194" s="7" t="s">
-        <v>97</v>
-      </c>
+      <c r="F194" s="7"/>
       <c r="G194" s="7"/>
       <c r="H194" s="7"/>
     </row>
-    <row r="195" spans="1:8" ht="40.5">
-      <c r="A195" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D195" s="5"/>
-      <c r="E195" s="4"/>
-      <c r="F195" s="4"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
+    <row r="195" spans="1:8">
+      <c r="A195" s="8"/>
+      <c r="B195" s="8"/>
+      <c r="C195" s="8"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
+      <c r="G195" s="7"/>
+      <c r="H195" s="7"/>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" s="7"/>
-      <c r="B196" s="7"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
-      <c r="G196" s="7"/>
-      <c r="H196" s="7"/>
-    </row>
-    <row r="197" spans="1:8" ht="40.5">
-      <c r="A197" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D197" s="5"/>
-      <c r="E197" s="4"/>
-      <c r="F197" s="4"/>
-      <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
-    </row>
-    <row r="198" spans="1:8">
-      <c r="C198" s="8"/>
-      <c r="D198" s="7"/>
-      <c r="E198" s="7"/>
-      <c r="F198" s="7"/>
-      <c r="G198" s="7"/>
-      <c r="H198" s="7"/>
-    </row>
-    <row r="199" spans="1:8" ht="40.5">
-      <c r="A199" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C199" s="5"/>
-      <c r="D199" s="4"/>
-      <c r="E199" s="4"/>
-      <c r="F199" s="4"/>
-      <c r="G199" s="4"/>
-      <c r="H199" s="4"/>
-    </row>
-    <row r="200" spans="1:8">
-      <c r="A200" s="8"/>
-      <c r="B200" s="8"/>
-      <c r="C200" s="8"/>
-      <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
-      <c r="G200" s="7"/>
-      <c r="H200" s="7"/>
-    </row>
-    <row r="201" spans="1:8">
-      <c r="A201" s="8"/>
-      <c r="B201" s="8"/>
-      <c r="C201" s="8"/>
-      <c r="D201" s="7"/>
-      <c r="E201" s="7"/>
-      <c r="F201" s="7"/>
-      <c r="G201" s="7"/>
-      <c r="H201" s="7"/>
-    </row>
-    <row r="202" spans="1:8">
-      <c r="D202" s="9"/>
-      <c r="E202" s="9"/>
-      <c r="F202" s="9"/>
-      <c r="G202" s="9"/>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
+      <c r="F196" s="9"/>
+      <c r="G196" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H110">
+  <autoFilter ref="A1:H106">
     <filterColumn colId="4"/>
   </autoFilter>
   <mergeCells count="1">

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$104</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -722,7 +722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F133" authorId="0">
+    <comment ref="F131" authorId="0">
       <text>
         <r>
           <rPr>
@@ -748,7 +748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F150" authorId="0">
+    <comment ref="F148" authorId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A163" authorId="0">
+    <comment ref="A161" authorId="0">
       <text>
         <r>
           <rPr>
@@ -808,7 +808,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="193">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -846,14 +846,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动coord节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>启动catalog节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -866,10 +858,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>大压力高并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>umount盘（低优先级）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -902,13 +890,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建cataRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除coordRG</t>
-  </si>
-  <si>
     <t>创建coordRG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -938,10 +919,6 @@
   </si>
   <si>
     <t>停止dataNode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停止coord节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -954,28 +931,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建coord节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>操作过程中异常，coordRG创建成功/失败；
 故障恢复后创建成功的coordRG正常可用，在coordRG创建coord节点创建成功；创建失败可以再次创建；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>coord处理节点跟catalog编目主节点不在一个主机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM所在主机网络拥塞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1008,18 +969,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>coord处理节点所在主机时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>磁盘满</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>coord处理节点所在主机磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>重复多次启停coord主节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1084,18 +1037,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>少于(n+1/2)个catalog备节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>超过(n+1/2)个catalog备节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建/删除失败；故障恢复后再次创建/删除成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>操作过程中异常，cataRG创建失败；故障恢复后创建成功的cataRG正常可用，在cataRG创建catalog节点创建成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1153,10 +1094,6 @@
   </si>
   <si>
     <t>创建节点组和节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程退出，操作失败；CM重启完成后可以继续创建/删除节点组和节点；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1502,14 +1439,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建coord节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动dataNode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>停止</t>
     </r>
@@ -1726,10 +1655,6 @@
     <t>目标主机磁盘满</t>
   </si>
   <si>
-    <t>catalog主节点所在主机CUP耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目标主机内存耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1743,10 +1668,6 @@
   </si>
   <si>
     <t>数据节点启停操作在内存耗尽故障场景考虑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标主机磁盘满</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1863,10 +1784,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>删除catalog节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目标主机断网</t>
   </si>
   <si>
@@ -1934,23 +1851,107 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>coord处理节点网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord处理节点所在主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复多次强制detach节点后再次attach到同一个节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分离前节点所在主机断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除coordRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>目标主机CM网络拥塞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>coord处理节点网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标主机网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点网络拥塞</t>
+    <t>CM所在主机网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大压力高并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动coord节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1958,59 +1959,38 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>目标主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord处理节点所在主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>少于(n+1/2)个catalog备节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超过(n+1/2)个catalog备节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程退出，操作失败；CM重启完成后可以继续创建/删除节点组和节点；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除失败；故障恢复后再次创建/删除成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机CPU耗尽</t>
+  </si>
+  <si>
     <t>目标主机内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标主机时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord处理节点所在主机时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点所在主机时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标主机磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点所在主机磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复多次强制detach节点后再次attach到同一个节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源主机断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分离前节点所在主机断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源主机网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源主机CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源主机内存耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2562,7 +2542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2581,10 +2561,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -2604,7 +2584,7 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="33.75" customHeight="1">
       <c r="A2" s="17" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -2622,17 +2602,17 @@
         <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="H3" s="11"/>
     </row>
@@ -2643,10 +2623,10 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="H4" s="7"/>
     </row>
@@ -2655,15 +2635,15 @@
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2673,7 +2653,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -2685,10 +2665,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="H7" s="7"/>
     </row>
@@ -2697,11 +2677,11 @@
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="7" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -2713,10 +2693,10 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H9" s="7"/>
     </row>
@@ -2727,10 +2707,10 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="15" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -2741,10 +2721,10 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H11" s="7"/>
     </row>
@@ -2753,17 +2733,17 @@
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
       <c r="D12" s="13" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27">
@@ -2773,10 +2753,10 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="H13" s="7"/>
     </row>
@@ -2784,17 +2764,17 @@
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="H14" s="7"/>
     </row>
@@ -2805,10 +2785,10 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="H15" s="7"/>
     </row>
@@ -2817,15 +2797,15 @@
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
       <c r="D16" s="13" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2835,7 +2815,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -2844,17 +2824,17 @@
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="8" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="H18" s="7"/>
     </row>
@@ -2865,10 +2845,10 @@
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="H19" s="7"/>
     </row>
@@ -2877,14 +2857,14 @@
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
       <c r="D20" s="7" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="H20" s="7"/>
     </row>
@@ -2894,32 +2874,32 @@
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" ht="40.5">
       <c r="A22" s="4" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>8</v>
@@ -2933,7 +2913,7 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -2943,13 +2923,13 @@
       <c r="B24" s="7"/>
       <c r="C24" s="8"/>
       <c r="D24" s="7" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -2961,7 +2941,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -2973,11 +2953,11 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="12" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2987,7 +2967,7 @@
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -2997,17 +2977,17 @@
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
       <c r="D28" s="13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="13" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="54">
@@ -3017,13 +2997,13 @@
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27">
@@ -3033,10 +3013,10 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="13" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="H30" s="7"/>
     </row>
@@ -3045,11 +3025,11 @@
       <c r="B31" s="7"/>
       <c r="C31" s="8"/>
       <c r="D31" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
@@ -3061,10 +3041,10 @@
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H32" s="7"/>
     </row>
@@ -3075,10 +3055,10 @@
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="15" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H33" s="7"/>
     </row>
@@ -3089,10 +3069,10 @@
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H34" s="7"/>
     </row>
@@ -3101,17 +3081,17 @@
       <c r="B35" s="7"/>
       <c r="C35" s="8"/>
       <c r="D35" s="13" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27">
@@ -3121,10 +3101,10 @@
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="H36" s="7"/>
     </row>
@@ -3132,14 +3112,14 @@
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="8" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
@@ -3151,7 +3131,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
@@ -3161,17 +3141,17 @@
       <c r="B39" s="7"/>
       <c r="C39" s="8"/>
       <c r="D39" s="13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="27">
@@ -3181,10 +3161,10 @@
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H40" s="7"/>
     </row>
@@ -3192,14 +3172,14 @@
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="8" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
@@ -3211,7 +3191,7 @@
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
@@ -3221,11 +3201,11 @@
       <c r="B43" s="7"/>
       <c r="C43" s="8"/>
       <c r="D43" s="7" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -3237,30 +3217,30 @@
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="40.5">
       <c r="A45" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="H45" s="11"/>
     </row>
@@ -3271,7 +3251,7 @@
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
@@ -3281,11 +3261,11 @@
       <c r="B47" s="7"/>
       <c r="C47" s="8"/>
       <c r="D47" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
@@ -3297,7 +3277,7 @@
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -3309,7 +3289,7 @@
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="14" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
@@ -3319,15 +3299,15 @@
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
       <c r="D50" s="13" t="s">
-        <v>24</v>
+        <v>174</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="7" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -3337,7 +3317,7 @@
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
@@ -3347,11 +3327,11 @@
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
       <c r="D52" s="7" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
@@ -3363,10 +3343,10 @@
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H53" s="7"/>
     </row>
@@ -3377,7 +3357,7 @@
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="F54" s="12" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -3389,10 +3369,10 @@
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H55" s="7"/>
     </row>
@@ -3401,17 +3381,17 @@
       <c r="B56" s="7"/>
       <c r="C56" s="8"/>
       <c r="D56" s="13" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="27">
@@ -3421,10 +3401,10 @@
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="H57" s="7"/>
     </row>
@@ -3432,14 +3412,14 @@
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="8" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="12" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -3451,7 +3431,7 @@
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
@@ -3463,7 +3443,7 @@
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -3473,15 +3453,15 @@
       <c r="B61" s="7"/>
       <c r="C61" s="8"/>
       <c r="D61" s="13" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="7" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -3491,7 +3471,7 @@
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -3500,14 +3480,14 @@
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="8" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -3517,34 +3497,34 @@
       <c r="B64" s="7"/>
       <c r="C64" s="8"/>
       <c r="D64" s="7" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
     </row>
     <row r="65" spans="1:8" ht="40.5">
       <c r="A65" s="4" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H65" s="4"/>
     </row>
@@ -3555,7 +3535,7 @@
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
@@ -3567,7 +3547,7 @@
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -3577,11 +3557,11 @@
       <c r="B68" s="7"/>
       <c r="C68" s="8"/>
       <c r="D68" s="7" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -3593,7 +3573,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -3603,11 +3583,11 @@
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
       <c r="D70" s="7" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -3619,7 +3599,7 @@
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -3629,11 +3609,11 @@
       <c r="B72" s="7"/>
       <c r="C72" s="8"/>
       <c r="D72" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -3645,7 +3625,7 @@
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -3655,11 +3635,11 @@
       <c r="B74" s="7"/>
       <c r="C74" s="8"/>
       <c r="D74" s="13" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
@@ -3671,7 +3651,7 @@
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
@@ -3681,11 +3661,11 @@
       <c r="B76" s="7"/>
       <c r="C76" s="8"/>
       <c r="D76" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="7" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
@@ -3697,7 +3677,7 @@
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
@@ -3707,11 +3687,11 @@
       <c r="B78" s="7"/>
       <c r="C78" s="8"/>
       <c r="D78" s="13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
@@ -3723,7 +3703,7 @@
       <c r="D79" s="7"/>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
@@ -3733,11 +3713,11 @@
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
       <c r="D80" s="7" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -3749,7 +3729,7 @@
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
@@ -3758,20 +3738,20 @@
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3779,14 +3759,14 @@
       <c r="B83" s="7"/>
       <c r="C83" s="8"/>
       <c r="D83" s="7" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="7" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H83" s="7"/>
     </row>
@@ -3795,11 +3775,11 @@
       <c r="B84" s="7"/>
       <c r="C84" s="8"/>
       <c r="D84" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
@@ -3809,29 +3789,29 @@
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
       <c r="D85" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="13" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="40.5">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="8" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
@@ -3843,30 +3823,30 @@
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
     </row>
     <row r="88" spans="1:8" ht="40.5">
       <c r="A88" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H88" s="4"/>
     </row>
@@ -3877,7 +3857,7 @@
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
@@ -3889,7 +3869,7 @@
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
@@ -3899,11 +3879,11 @@
       <c r="B91" s="7"/>
       <c r="C91" s="8"/>
       <c r="D91" s="7" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
@@ -3915,7 +3895,7 @@
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
@@ -3925,11 +3905,11 @@
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
       <c r="D93" s="13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
@@ -3941,7 +3921,7 @@
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="7" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
@@ -3951,11 +3931,11 @@
       <c r="B95" s="7"/>
       <c r="C95" s="8"/>
       <c r="D95" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
@@ -3967,7 +3947,7 @@
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
@@ -3977,11 +3957,11 @@
       <c r="B97" s="7"/>
       <c r="C97" s="8"/>
       <c r="D97" s="13" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
@@ -3993,7 +3973,7 @@
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
       <c r="F98" s="7" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
@@ -4003,11 +3983,11 @@
       <c r="B99" s="7"/>
       <c r="C99" s="8"/>
       <c r="D99" s="7" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
@@ -4019,7 +3999,7 @@
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
@@ -4029,11 +4009,11 @@
       <c r="B101" s="7"/>
       <c r="C101" s="8"/>
       <c r="D101" s="7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
@@ -4045,145 +4025,147 @@
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
       <c r="F102" s="7" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
     </row>
-    <row r="103" spans="1:8" ht="27">
+    <row r="103" spans="1:8" ht="40.5">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="8"/>
       <c r="D103" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7"/>
+        <v>161</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H103" s="13" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="7"/>
+      <c r="D104" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G104" s="7"/>
+        <v>105</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H104" s="7"/>
     </row>
     <row r="105" spans="1:8" ht="40.5">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
-      <c r="C105" s="8"/>
+      <c r="C105" s="8" t="s">
+        <v>143</v>
+      </c>
       <c r="D105" s="7" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H105" s="13" t="s">
-        <v>129</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="8"/>
       <c r="D106" s="7" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>47</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="G106" s="7"/>
       <c r="H106" s="7"/>
     </row>
     <row r="107" spans="1:8" ht="40.5">
-      <c r="A107" s="7"/>
-      <c r="B107" s="7"/>
-      <c r="C107" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-    </row>
-    <row r="108" spans="1:8">
+      <c r="A107" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" ht="27">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="7" t="s">
-        <v>167</v>
-      </c>
+      <c r="D108" s="7"/>
       <c r="E108" s="7"/>
       <c r="F108" s="7" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
     </row>
-    <row r="109" spans="1:8" ht="40.5">
-      <c r="A109" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E109" s="4"/>
-      <c r="F109" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H109" s="4"/>
-    </row>
-    <row r="110" spans="1:8" ht="27">
+    <row r="109" spans="1:8">
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G109" s="7"/>
+      <c r="H109" s="7"/>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="8"/>
-      <c r="D110" s="7"/>
+      <c r="D110" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" ht="27">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="8"/>
       <c r="D111" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
@@ -4193,11 +4175,11 @@
       <c r="B112" s="7"/>
       <c r="C112" s="8"/>
       <c r="D112" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="7" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
@@ -4207,75 +4189,73 @@
       <c r="B113" s="7"/>
       <c r="C113" s="8"/>
       <c r="D113" s="7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E113" s="7"/>
       <c r="F113" s="7" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" ht="27">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
-      <c r="C114" s="8"/>
+      <c r="C114" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D114" s="7" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G114" s="7"/>
+        <v>106</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" ht="27">
+    <row r="115" spans="1:8">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="8"/>
       <c r="D115" s="7" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="E115" s="7"/>
       <c r="F115" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G115" s="7"/>
+        <v>106</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H115" s="7"/>
     </row>
     <row r="116" spans="1:8" ht="27">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
-      <c r="C116" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="C116" s="8"/>
       <c r="D116" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E116" s="7"/>
       <c r="F116" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>58</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G116" s="7"/>
       <c r="H116" s="7"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" ht="27">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="8"/>
-      <c r="D117" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="D117" s="7"/>
       <c r="E117" s="7"/>
       <c r="F117" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G117" s="7" t="s">
-        <v>47</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G117" s="7"/>
       <c r="H117" s="7"/>
     </row>
     <row r="118" spans="1:8" ht="27">
@@ -4283,11 +4263,11 @@
       <c r="B118" s="7"/>
       <c r="C118" s="8"/>
       <c r="D118" s="7" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
@@ -4296,50 +4276,54 @@
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
-      <c r="D119" s="7"/>
+      <c r="D119" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="E119" s="7"/>
       <c r="F119" s="7" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" ht="27">
+    <row r="120" spans="1:8">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="8"/>
-      <c r="D120" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="D120" s="7"/>
       <c r="E120" s="7"/>
       <c r="F120" s="7" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" ht="27">
+    <row r="121" spans="1:8">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="8"/>
       <c r="D121" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E121" s="7"/>
       <c r="F121" s="7" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" ht="40.5">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="7"/>
+      <c r="C122" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="E122" s="7"/>
       <c r="F122" s="7" t="s">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
@@ -4348,28 +4332,24 @@
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="8"/>
-      <c r="D123" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="D123" s="7"/>
       <c r="E123" s="7"/>
       <c r="F123" s="7" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" ht="40.5">
+    <row r="124" spans="1:8" ht="27">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
-      <c r="C124" s="8" t="s">
-        <v>164</v>
-      </c>
+      <c r="C124" s="8"/>
       <c r="D124" s="7" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
@@ -4381,67 +4361,67 @@
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
     </row>
-    <row r="126" spans="1:8" ht="27">
-      <c r="A126" s="7"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="8"/>
-      <c r="D126" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-    </row>
-    <row r="127" spans="1:8">
+    <row r="126" spans="1:8" ht="40.5">
+      <c r="A126" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H126" s="4"/>
+    </row>
+    <row r="127" spans="1:8" ht="27">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="8"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
     </row>
-    <row r="128" spans="1:8" ht="40.5">
-      <c r="A128" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E128" s="4"/>
-      <c r="F128" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H128" s="4"/>
-    </row>
-    <row r="129" spans="1:8" ht="27">
+    <row r="128" spans="1:8" ht="27">
+      <c r="A128" s="7"/>
+      <c r="B128" s="7"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E128" s="7"/>
+      <c r="F128" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="8"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
@@ -4451,11 +4431,11 @@
       <c r="B130" s="7"/>
       <c r="C130" s="8"/>
       <c r="D130" s="7" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E130" s="7"/>
       <c r="F130" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
@@ -4467,7 +4447,7 @@
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="7"/>
@@ -4477,11 +4457,11 @@
       <c r="B132" s="7"/>
       <c r="C132" s="8"/>
       <c r="D132" s="7" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E132" s="7"/>
       <c r="F132" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
@@ -4493,7 +4473,7 @@
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
@@ -4503,11 +4483,11 @@
       <c r="B134" s="7"/>
       <c r="C134" s="8"/>
       <c r="D134" s="7" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="7"/>
@@ -4519,7 +4499,7 @@
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="G135" s="7"/>
       <c r="H135" s="7"/>
@@ -4529,11 +4509,11 @@
       <c r="B136" s="7"/>
       <c r="C136" s="8"/>
       <c r="D136" s="7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E136" s="7"/>
       <c r="F136" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
@@ -4545,109 +4525,113 @@
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
       <c r="F137" s="7" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
     </row>
-    <row r="138" spans="1:8" ht="27">
+    <row r="138" spans="1:8" ht="40.5">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
-      <c r="C138" s="8"/>
+      <c r="C138" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D138" s="7" t="s">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G138" s="7"/>
+        <v>186</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="H138" s="7"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="8"/>
-      <c r="D139" s="7"/>
+      <c r="D139" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="E139" s="7"/>
       <c r="F139" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="G139" s="7"/>
+        <v>186</v>
+      </c>
+      <c r="G139" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" ht="40.5">
+    <row r="140" spans="1:8" ht="27">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="C140" s="8"/>
       <c r="D140" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>46</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="G140" s="7"/>
       <c r="H140" s="7"/>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" ht="27">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="8"/>
       <c r="D141" s="7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G141" s="7" t="s">
-        <v>47</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="G141" s="7"/>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8" ht="27">
+    <row r="142" spans="1:8">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="8"/>
       <c r="D142" s="7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E142" s="7"/>
       <c r="F142" s="7" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="G142" s="7"/>
       <c r="H142" s="7"/>
     </row>
-    <row r="143" spans="1:8" ht="27">
+    <row r="143" spans="1:8">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="8"/>
       <c r="D143" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E143" s="7"/>
       <c r="F143" s="7" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G143" s="7"/>
       <c r="H143" s="7"/>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" ht="40.5">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
-      <c r="C144" s="8"/>
+      <c r="C144" s="8" t="s">
+        <v>143</v>
+      </c>
       <c r="D144" s="7" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="E144" s="7"/>
       <c r="F144" s="7" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="G144" s="7"/>
       <c r="H144" s="7"/>
@@ -4656,28 +4640,24 @@
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
       <c r="C145" s="8"/>
-      <c r="D145" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="D145" s="7"/>
       <c r="E145" s="7"/>
       <c r="F145" s="7" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="7"/>
     </row>
-    <row r="146" spans="1:8" ht="40.5">
+    <row r="146" spans="1:8" ht="27">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="8" t="s">
-        <v>164</v>
-      </c>
+      <c r="C146" s="8"/>
       <c r="D146" s="7" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E146" s="7"/>
       <c r="F146" s="7" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="G146" s="7"/>
       <c r="H146" s="7"/>
@@ -4689,72 +4669,74 @@
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
       <c r="F147" s="7" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="G147" s="7"/>
       <c r="H147" s="7"/>
     </row>
-    <row r="148" spans="1:8" ht="27">
-      <c r="A148" s="7"/>
-      <c r="B148" s="7"/>
-      <c r="C148" s="8"/>
-      <c r="D148" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E148" s="7"/>
-      <c r="F148" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="G148" s="7"/>
-      <c r="H148" s="7"/>
-    </row>
-    <row r="149" spans="1:8">
+    <row r="148" spans="1:8" ht="40.5">
+      <c r="A148" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H148" s="4"/>
+    </row>
+    <row r="149" spans="1:8" ht="27">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
-      <c r="C149" s="8"/>
+      <c r="C149" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
       <c r="F149" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G149" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="H149" s="7"/>
     </row>
-    <row r="150" spans="1:8" ht="40.5">
-      <c r="A150" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E150" s="4"/>
-      <c r="F150" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H150" s="4"/>
+    <row r="150" spans="1:8" ht="27">
+      <c r="A150" s="7"/>
+      <c r="B150" s="7"/>
+      <c r="C150" s="8"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H150" s="7"/>
     </row>
     <row r="151" spans="1:8" ht="27">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
-      <c r="C151" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="C151" s="8"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
       <c r="F151" s="7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H151" s="7"/>
     </row>
@@ -4765,11 +4747,9 @@
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
       <c r="F152" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G152" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G152" s="7"/>
       <c r="H152" s="7"/>
     </row>
     <row r="153" spans="1:8" ht="27">
@@ -4779,11 +4759,9 @@
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
       <c r="F153" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G153" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="G153" s="7"/>
       <c r="H153" s="7"/>
     </row>
     <row r="154" spans="1:8" ht="27">
@@ -4793,46 +4771,50 @@
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
       <c r="F154" s="7" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
     </row>
-    <row r="155" spans="1:8" ht="27">
+    <row r="155" spans="1:8">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="8"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
       <c r="F155" s="7" t="s">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="G155" s="7"/>
       <c r="H155" s="7"/>
     </row>
-    <row r="156" spans="1:8" ht="27">
+    <row r="156" spans="1:8">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="8"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
       <c r="F156" s="7" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8">
-      <c r="A157" s="7"/>
-      <c r="B157" s="7"/>
-      <c r="C157" s="8"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="G157" s="7"/>
-      <c r="H157" s="7"/>
+    <row r="157" spans="1:8" ht="54">
+      <c r="A157" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D157" s="4"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="4"/>
+      <c r="G157" s="4"/>
+      <c r="H157" s="4"/>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="7"/>
@@ -4840,21 +4822,19 @@
       <c r="C158" s="8"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
-      <c r="F158" s="7" t="s">
-        <v>135</v>
-      </c>
+      <c r="F158" s="7"/>
       <c r="G158" s="7"/>
       <c r="H158" s="7"/>
     </row>
-    <row r="159" spans="1:8" ht="54">
+    <row r="159" spans="1:8" ht="27">
       <c r="A159" s="4" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="11"/>
@@ -4874,61 +4854,63 @@
     </row>
     <row r="161" spans="1:8" ht="27">
       <c r="A161" s="4" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C161" s="11" t="s">
-        <v>47</v>
-      </c>
+      <c r="C161" s="11"/>
       <c r="D161" s="4"/>
-      <c r="E161" s="11"/>
-      <c r="F161" s="4"/>
-      <c r="G161" s="4"/>
+      <c r="E161" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="H161" s="4"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" ht="27">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="8"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
-      <c r="F162" s="7"/>
-      <c r="G162" s="7"/>
+      <c r="F162" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="H162" s="7"/>
     </row>
-    <row r="163" spans="1:8" ht="27">
-      <c r="A163" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C163" s="11"/>
-      <c r="D163" s="4"/>
-      <c r="E163" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F163" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G163" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H163" s="4"/>
-    </row>
-    <row r="164" spans="1:8" ht="27">
+    <row r="163" spans="1:8">
+      <c r="A163" s="7"/>
+      <c r="B163" s="7"/>
+      <c r="C163" s="8"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H163" s="7"/>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="8"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G164" s="7" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="H164" s="7"/>
     </row>
@@ -4939,26 +4921,32 @@
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
       <c r="F165" s="7" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H165" s="7"/>
     </row>
-    <row r="166" spans="1:8">
-      <c r="A166" s="7"/>
-      <c r="B166" s="7"/>
-      <c r="C166" s="8"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="G166" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H166" s="7"/>
+    <row r="166" spans="1:8" ht="27">
+      <c r="A166" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="11"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H166" s="4"/>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="7"/>
@@ -4967,32 +4955,26 @@
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
       <c r="F167" s="7" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H167" s="7"/>
     </row>
-    <row r="168" spans="1:8" ht="27">
-      <c r="A168" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C168" s="11"/>
-      <c r="D168" s="4"/>
-      <c r="E168" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F168" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G168" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H168" s="4"/>
+    <row r="168" spans="1:8">
+      <c r="A168" s="7"/>
+      <c r="B168" s="7"/>
+      <c r="C168" s="8"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G168" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H168" s="7"/>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="7"/>
@@ -5001,10 +4983,10 @@
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
       <c r="F169" s="7" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H169" s="7"/>
     </row>
@@ -5015,26 +4997,28 @@
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
       <c r="F170" s="7" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H170" s="7"/>
     </row>
-    <row r="171" spans="1:8">
-      <c r="A171" s="7"/>
-      <c r="B171" s="7"/>
-      <c r="C171" s="8"/>
-      <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="G171" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H171" s="7"/>
+    <row r="171" spans="1:8" ht="39" customHeight="1">
+      <c r="A171" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C171" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
+      <c r="G171" s="4"/>
+      <c r="H171" s="4"/>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="7"/>
@@ -5042,88 +5026,86 @@
       <c r="C172" s="8"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
-      <c r="F172" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="F172" s="7"/>
+      <c r="G172" s="7"/>
       <c r="H172" s="7"/>
     </row>
-    <row r="173" spans="1:8" ht="39" customHeight="1">
+    <row r="173" spans="1:8" ht="54">
       <c r="A173" s="4" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C173" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D173" s="4"/>
-      <c r="E173" s="4"/>
-      <c r="F173" s="4"/>
-      <c r="G173" s="4"/>
+        <v>120</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D173" s="5"/>
+      <c r="E173" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>189</v>
+      </c>
       <c r="H173" s="4"/>
     </row>
-    <row r="174" spans="1:8">
-      <c r="A174" s="7"/>
-      <c r="B174" s="7"/>
+    <row r="174" spans="1:8" ht="27">
+      <c r="A174" s="8"/>
+      <c r="B174" s="8"/>
       <c r="C174" s="8"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
-      <c r="G174" s="7"/>
+      <c r="F174" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="H174" s="7"/>
     </row>
-    <row r="175" spans="1:8" ht="54">
-      <c r="A175" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D175" s="5"/>
-      <c r="E175" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F175" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="G175" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="H175" s="4"/>
+    <row r="175" spans="1:8" ht="27">
+      <c r="A175" s="8"/>
+      <c r="B175" s="8"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H175" s="7"/>
     </row>
     <row r="176" spans="1:8" ht="27">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
       <c r="D176" s="7"/>
-      <c r="E176" s="7"/>
+      <c r="E176" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="F176" s="7" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H176" s="7"/>
     </row>
-    <row r="177" spans="1:8" ht="27">
+    <row r="177" spans="1:8">
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
-      <c r="F177" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="F177" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G177" s="7"/>
       <c r="H177" s="7"/>
     </row>
     <row r="178" spans="1:8" ht="27">
@@ -5131,41 +5113,43 @@
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
       <c r="D178" s="7"/>
-      <c r="E178" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="E178" s="7"/>
       <c r="F178" s="7" t="s">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="H178" s="7"/>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" ht="27">
       <c r="A179" s="8"/>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7"/>
-      <c r="F179" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G179" s="7"/>
+      <c r="F179" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G179" s="7" t="s">
+        <v>190</v>
+      </c>
       <c r="H179" s="7"/>
     </row>
-    <row r="180" spans="1:8" ht="27">
+    <row r="180" spans="1:8" ht="40.5">
       <c r="A180" s="8"/>
       <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
+      <c r="C180" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
+      <c r="E180" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="F180" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>67</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="G180" s="7"/>
       <c r="H180" s="7"/>
     </row>
     <row r="181" spans="1:8" ht="27">
@@ -5175,65 +5159,61 @@
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
       <c r="F181" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G181" s="7" t="s">
-        <v>70</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G181" s="7"/>
       <c r="H181" s="7"/>
     </row>
-    <row r="182" spans="1:8" ht="40.5">
+    <row r="182" spans="1:8" ht="27">
       <c r="A182" s="8"/>
       <c r="B182" s="8"/>
-      <c r="C182" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="C182" s="8"/>
       <c r="D182" s="7"/>
-      <c r="E182" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F182" s="7" t="s">
-        <v>191</v>
+      <c r="E182" s="7"/>
+      <c r="F182" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
     </row>
-    <row r="183" spans="1:8" ht="27">
-      <c r="A183" s="8"/>
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
-      <c r="D183" s="7"/>
+    <row r="183" spans="1:8" ht="40.5">
+      <c r="A183" s="7"/>
+      <c r="B183" s="7"/>
+      <c r="C183" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="E183" s="7"/>
       <c r="F183" s="7" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
     </row>
     <row r="184" spans="1:8" ht="27">
-      <c r="A184" s="8"/>
-      <c r="B184" s="8"/>
+      <c r="A184" s="7"/>
+      <c r="B184" s="7"/>
       <c r="C184" s="8"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
-      <c r="F184" s="12" t="s">
-        <v>63</v>
+      <c r="F184" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
     </row>
-    <row r="185" spans="1:8" ht="40.5">
+    <row r="185" spans="1:8">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
-      <c r="C185" s="8" t="s">
-        <v>164</v>
-      </c>
+      <c r="C185" s="8"/>
       <c r="D185" s="7" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="7" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="G185" s="7"/>
       <c r="H185" s="7"/>
@@ -5245,46 +5225,46 @@
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="G186" s="7"/>
       <c r="H186" s="7"/>
     </row>
-    <row r="187" spans="1:8">
-      <c r="A187" s="7"/>
-      <c r="B187" s="7"/>
-      <c r="C187" s="8"/>
-      <c r="D187" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E187" s="7"/>
-      <c r="F187" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="G187" s="7"/>
-      <c r="H187" s="7"/>
-    </row>
-    <row r="188" spans="1:8" ht="27">
+    <row r="187" spans="1:8" ht="40.5">
+      <c r="A187" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D187" s="5"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="4"/>
+      <c r="G187" s="4"/>
+      <c r="H187" s="4"/>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
       <c r="C188" s="8"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
-      <c r="F188" s="7" t="s">
-        <v>97</v>
-      </c>
+      <c r="F188" s="7"/>
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
     </row>
     <row r="189" spans="1:8" ht="40.5">
       <c r="A189" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="D189" s="5"/>
       <c r="E189" s="4"/>
@@ -5293,8 +5273,6 @@
       <c r="H189" s="4"/>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" s="7"/>
-      <c r="B190" s="7"/>
       <c r="C190" s="8"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
@@ -5304,21 +5282,23 @@
     </row>
     <row r="191" spans="1:8" ht="40.5">
       <c r="A191" s="4" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D191" s="5"/>
+        <v>181</v>
+      </c>
+      <c r="D191" s="4"/>
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
       <c r="H191" s="4"/>
     </row>
     <row r="192" spans="1:8">
+      <c r="A192" s="8"/>
+      <c r="B192" s="8"/>
       <c r="C192" s="8"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
@@ -5326,48 +5306,24 @@
       <c r="G192" s="7"/>
       <c r="H192" s="7"/>
     </row>
-    <row r="193" spans="1:8" ht="40.5">
-      <c r="A193" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C193" s="5"/>
-      <c r="D193" s="4"/>
-      <c r="E193" s="4"/>
-      <c r="F193" s="4"/>
-      <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
+    <row r="193" spans="1:8">
+      <c r="A193" s="8"/>
+      <c r="B193" s="8"/>
+      <c r="C193" s="8"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7"/>
+      <c r="G193" s="7"/>
+      <c r="H193" s="7"/>
     </row>
     <row r="194" spans="1:8">
-      <c r="A194" s="8"/>
-      <c r="B194" s="8"/>
-      <c r="C194" s="8"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
-      <c r="G194" s="7"/>
-      <c r="H194" s="7"/>
-    </row>
-    <row r="195" spans="1:8">
-      <c r="A195" s="8"/>
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
-      <c r="D195" s="7"/>
-      <c r="E195" s="7"/>
-      <c r="F195" s="7"/>
-      <c r="G195" s="7"/>
-      <c r="H195" s="7"/>
-    </row>
-    <row r="196" spans="1:8">
-      <c r="D196" s="9"/>
-      <c r="E196" s="9"/>
-      <c r="F196" s="9"/>
-      <c r="G196" s="9"/>
+      <c r="D194" s="9"/>
+      <c r="E194" s="9"/>
+      <c r="F194" s="9"/>
+      <c r="G194" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H106">
+  <autoFilter ref="A1:H104">
     <filterColumn colId="4"/>
   </autoFilter>
   <mergeCells count="1">

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$100</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -222,7 +222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0">
+    <comment ref="C18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -242,7 +242,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-attach</t>
+attach/detach</t>
         </r>
         <r>
           <rPr>
@@ -252,7 +252,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>和</t>
+          <t>时会自动停止</t>
         </r>
         <r>
           <rPr>
@@ -261,7 +261,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>detach</t>
+          <t>/</t>
         </r>
         <r>
           <rPr>
@@ -271,22 +271,35 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>节点</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
+          <t>启动节点，流程跟节点启停流程一致，接口相同；</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>attach/detach</t>
+        </r>
+        <r>
+          <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>Author:</t>
+          <t>直接调的</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>createNode/removeNode</t>
         </r>
         <r>
           <rPr>
@@ -296,13 +309,110 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
+          <t>节点，跟创建</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>/</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>删除节点接口相同；各故障场景交叉考虑</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+attach</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>和</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>detach</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>节点</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
           <t xml:space="preserve">
 编目组在每个故障场景都考虑（创建编目组会同时创建一个节点，并启动节点，流程不一样）
 节点交叉在各个场景测试</t>
         </r>
       </text>
     </comment>
-    <comment ref="G22" authorId="0">
+    <comment ref="G20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -328,7 +438,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F23" authorId="0">
+    <comment ref="F21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -392,7 +502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0">
+    <comment ref="F28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -420,7 +530,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B45" authorId="0">
+    <comment ref="B41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -473,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D45" authorId="0">
+    <comment ref="D41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -500,7 +610,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G45" authorId="0">
+    <comment ref="G41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -526,7 +636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F46" authorId="0">
+    <comment ref="F42" authorId="0">
       <text>
         <r>
           <rPr>
@@ -590,7 +700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D65" authorId="0">
+    <comment ref="D61" authorId="0">
       <text>
         <r>
           <rPr>
@@ -633,6 +743,32 @@
           </rPr>
           <t>和内存交叉考虑
 协调节点抽测一个</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D74" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+删除只需要考虑一个组合节点</t>
         </r>
       </text>
     </comment>
@@ -643,46 +779,45 @@
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+CPU</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
+          <t>和内存交叉考虑</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D89" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">
-删除只需要考虑一个组合节点</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D82" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
           <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-CPU</t>
         </r>
         <r>
           <rPr>
@@ -692,11 +827,12 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>和内存交叉考虑</t>
+          <t xml:space="preserve">
+删除只需要考虑一个组合节点</t>
         </r>
       </text>
     </comment>
-    <comment ref="D93" authorId="0">
+    <comment ref="F127" authorId="0">
       <text>
         <r>
           <rPr>
@@ -718,37 +854,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-删除只需要考虑一个组合节点</t>
+catalog主节点所在主机内磁盘满，需要针对每个类型的节点和组</t>
         </r>
       </text>
     </comment>
-    <comment ref="F131" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-catalog主节点所在主机内磁盘满，需要针对每个类型的节点和组</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F148" authorId="0">
+    <comment ref="F142" authorId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A161" authorId="0">
+    <comment ref="A155" authorId="0">
       <text>
         <r>
           <rPr>
@@ -808,7 +918,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="193">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1803,10 +1913,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>目标主机断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>detach节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1819,18 +1925,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>attach失败；故障恢复后重新attach成功，节点正常可用，编目各节点信息完整一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>detach成功/失败；重新选主，故障恢复后检查detach成功的节点在目标主机和编目上没有该节点信息，可以再次attach成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>detach失败；故障恢复后检查detach成功的节点，目标主机和编目上没有该节点信息，可以再次attach成功，节点正常可用；故障恢复后检查detach失败的节点，可以再次detach，detach后目标主机和编目节点没有该节点的信息；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>网络闪断</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1887,10 +1985,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>catalog主节点所在主机磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CM正常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1899,22 +1993,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>源主机断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分离前节点所在主机断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>源主机网络闪断</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>源主机CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>源主机内存耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1991,6 +2073,34 @@
   </si>
   <si>
     <t>目标主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord节点与catalog主节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点与catalog备节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点与目标主机网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启停节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作失败；故障恢复后可以继续创建/删除节点组和节点，节点可以正常使用；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2100,7 +2210,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2116,6 +2226,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF008A3E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2184,7 +2300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2242,6 +2358,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2542,7 +2664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2774,7 +2896,7 @@
         <v>59</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H14" s="7"/>
     </row>
@@ -2823,88 +2945,86 @@
     <row r="18" spans="1:8" ht="54">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7" t="s">
-        <v>15</v>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21" t="s">
+        <v>59</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" ht="27">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7" t="s">
+      <c r="C19" s="20"/>
+      <c r="D19" s="21" t="s">
         <v>145</v>
       </c>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21" t="s">
+        <v>15</v>
+      </c>
       <c r="G19" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" ht="40.5">
+      <c r="A20" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="27">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="54">
+      <c r="B20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="7" t="s">
-        <v>170</v>
-      </c>
+      <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>151</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" ht="40.5">
-      <c r="A22" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4" t="s">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="11"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="7"/>
@@ -2913,26 +3033,24 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" ht="40.5">
+    <row r="24" spans="1:8" ht="27">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>47</v>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="H24" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="7"/>
@@ -2941,7 +3059,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -2950,61 +3068,63 @@
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="7"/>
+      <c r="D26" s="13" t="s">
+        <v>21</v>
+      </c>
       <c r="E26" s="7"/>
-      <c r="F26" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="G26" s="7"/>
+      <c r="F26" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="H26" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="54">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="8"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+        <v>140</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="27">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="13" t="s">
-        <v>21</v>
-      </c>
+      <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="54">
+        <v>153</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" ht="27">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="7"/>
+      <c r="D29" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>141</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
     </row>
     <row r="30" spans="1:8" ht="27">
       <c r="A30" s="7"/>
@@ -3012,177 +3132,185 @@
       <c r="C30" s="8"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>83</v>
+      <c r="F30" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27">
+    <row r="31" spans="1:8">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="D31" s="7"/>
       <c r="E31" s="7"/>
-      <c r="F31" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G31" s="7"/>
+      <c r="F31" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" ht="27">
+    <row r="32" spans="1:8">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="8"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" ht="27">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="7"/>
+      <c r="D33" s="13" t="s">
+        <v>91</v>
+      </c>
       <c r="E33" s="7"/>
-      <c r="F33" s="15" t="s">
-        <v>154</v>
+      <c r="F33" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8">
+        <v>92</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="27">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="8"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:8" ht="27">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="13" t="s">
-        <v>91</v>
+      <c r="C35" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="27">
+        <v>152</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>61</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
     <row r="37" spans="1:8" ht="27">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>95</v>
+      <c r="C37" s="8"/>
+      <c r="D37" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:8">
+        <v>152</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="27">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="8"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G38" s="7"/>
+        <v>150</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" ht="27">
+    <row r="39" spans="1:8" ht="40.5">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="27">
+      <c r="C39" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>63</v>
-      </c>
+      <c r="C40" s="20"/>
+      <c r="D40" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
     <row r="41" spans="1:8" ht="40.5">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
+      <c r="A41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H41" s="11"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="7"/>
@@ -3191,7 +3319,7 @@
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
@@ -3201,11 +3329,11 @@
       <c r="B43" s="7"/>
       <c r="C43" s="8"/>
       <c r="D43" s="7" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -3217,55 +3345,47 @@
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" ht="40.5">
-      <c r="A45" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="H45" s="11"/>
-    </row>
-    <row r="46" spans="1:8">
+    <row r="45" spans="1:8">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+    </row>
+    <row r="46" spans="1:8" ht="27">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="8"/>
-      <c r="D46" s="7"/>
+      <c r="D46" s="13" t="s">
+        <v>167</v>
+      </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
+      <c r="H46" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
@@ -3274,41 +3394,41 @@
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="7"/>
+      <c r="D48" s="7" t="s">
+        <v>75</v>
+      </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" ht="27">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="8"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
-      <c r="F49" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="G49" s="7"/>
+      <c r="F49" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="1:8" ht="27">
+    <row r="50" spans="1:8">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
-      <c r="D50" s="13" t="s">
-        <v>174</v>
-      </c>
+      <c r="D50" s="7"/>
       <c r="E50" s="7"/>
-      <c r="F50" s="7" t="s">
-        <v>137</v>
+      <c r="F50" s="12" t="s">
+        <v>156</v>
       </c>
       <c r="G50" s="7"/>
-      <c r="H50" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="H50" s="7"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="7"/>
@@ -3317,24 +3437,30 @@
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G51" s="7"/>
+        <v>155</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" ht="27">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
-      <c r="D52" s="7" t="s">
-        <v>75</v>
+      <c r="D52" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
+        <v>137</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="53" spans="1:8" ht="27">
       <c r="A53" s="7"/>
@@ -3343,21 +3469,25 @@
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" ht="27">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="7"/>
+      <c r="C54" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="E54" s="7"/>
       <c r="F54" s="12" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -3369,68 +3499,62 @@
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>65</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="G55" s="7"/>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8" ht="27">
+    <row r="56" spans="1:8">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="13" t="s">
-        <v>93</v>
-      </c>
+      <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>103</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
     </row>
     <row r="57" spans="1:8" ht="27">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8"/>
-      <c r="D57" s="7"/>
+      <c r="D57" s="13" t="s">
+        <v>97</v>
+      </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H57" s="7"/>
-    </row>
-    <row r="58" spans="1:8" ht="27">
+        <v>137</v>
+      </c>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
-      <c r="C58" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="C58" s="8"/>
+      <c r="D58" s="7"/>
       <c r="E58" s="7"/>
-      <c r="F58" s="12" t="s">
-        <v>157</v>
+      <c r="F58" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" ht="40.5">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7" t="s">
+      <c r="C59" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21" t="s">
         <v>137</v>
       </c>
       <c r="G59" s="7"/>
@@ -3439,103 +3563,99 @@
     <row r="60" spans="1:8">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7" t="s">
-        <v>158</v>
+      <c r="C60" s="20"/>
+      <c r="D60" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21" t="s">
+        <v>137</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+    <row r="61" spans="1:8" ht="40.5">
+      <c r="A61" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" ht="27">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
     </row>
-    <row r="63" spans="1:8" ht="40.5">
+    <row r="63" spans="1:8">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
-      <c r="C63" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="C63" s="8"/>
+      <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" ht="27">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="8"/>
       <c r="D64" s="7" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8" ht="40.5">
-      <c r="A65" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H65" s="4"/>
+    <row r="65" spans="1:8">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
     </row>
     <row r="66" spans="1:8" ht="27">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
-      <c r="D66" s="7"/>
+      <c r="D66" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
@@ -3547,7 +3667,7 @@
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -3557,11 +3677,11 @@
       <c r="B68" s="7"/>
       <c r="C68" s="8"/>
       <c r="D68" s="7" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -3573,7 +3693,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -3582,12 +3702,12 @@
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
-      <c r="D70" s="7" t="s">
-        <v>135</v>
+      <c r="D70" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -3599,7 +3719,7 @@
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -3609,11 +3729,11 @@
       <c r="B72" s="7"/>
       <c r="C72" s="8"/>
       <c r="D72" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -3625,7 +3745,7 @@
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -3635,11 +3755,11 @@
       <c r="B74" s="7"/>
       <c r="C74" s="8"/>
       <c r="D74" s="13" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
@@ -3651,7 +3771,7 @@
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
@@ -3661,11 +3781,11 @@
       <c r="B76" s="7"/>
       <c r="C76" s="8"/>
       <c r="D76" s="7" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
@@ -3677,35 +3797,45 @@
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" ht="27">
+    <row r="78" spans="1:8" ht="40.5">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="13" t="s">
-        <v>23</v>
+      <c r="C78" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
+        <v>157</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
-      <c r="D79" s="7"/>
+      <c r="D79" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G79" s="7"/>
+        <v>176</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H79" s="7"/>
     </row>
     <row r="80" spans="1:8" ht="27">
@@ -3713,148 +3843,138 @@
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
       <c r="D80" s="7" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" ht="27">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="8"/>
-      <c r="D81" s="7"/>
+      <c r="D81" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
+      <c r="H81" s="13" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="82" spans="1:8" ht="40.5">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>110</v>
-      </c>
+      <c r="C82" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="C83" s="20"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="G83" s="7"/>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8" ht="27">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
+    <row r="84" spans="1:8" ht="40.5">
+      <c r="A84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H84" s="4"/>
     </row>
     <row r="85" spans="1:8" ht="27">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="G85" s="7"/>
-      <c r="H85" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="40.5">
+      <c r="H85" s="7"/>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
-      <c r="C86" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="C86" s="8"/>
+      <c r="D86" s="7"/>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" ht="27">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="7"/>
+      <c r="D87" s="7" t="s">
+        <v>75</v>
+      </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
     </row>
-    <row r="88" spans="1:8" ht="40.5">
-      <c r="A88" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H88" s="4"/>
+    <row r="88" spans="1:8">
+      <c r="A88" s="7"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:8" ht="27">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="7"/>
+      <c r="D89" s="13" t="s">
+        <v>21</v>
+      </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
         <v>109</v>
@@ -3869,7 +3989,7 @@
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
@@ -3879,11 +3999,11 @@
       <c r="B91" s="7"/>
       <c r="C91" s="8"/>
       <c r="D91" s="7" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
-        <v>109</v>
+        <v>184</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
@@ -3895,7 +4015,7 @@
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7" t="s">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
@@ -3905,7 +4025,7 @@
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
       <c r="D93" s="13" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
@@ -3931,11 +4051,11 @@
       <c r="B95" s="7"/>
       <c r="C95" s="8"/>
       <c r="D95" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7" t="s">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
@@ -3947,7 +4067,7 @@
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
@@ -3956,8 +4076,8 @@
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="13" t="s">
-        <v>93</v>
+      <c r="D97" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
@@ -3973,47 +4093,57 @@
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
       <c r="F98" s="7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
     </row>
-    <row r="99" spans="1:8" ht="27">
+    <row r="99" spans="1:8" ht="40.5">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="8"/>
       <c r="D99" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
+        <v>158</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="8"/>
-      <c r="D100" s="7"/>
+      <c r="D100" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G100" s="7"/>
+      <c r="G100" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H100" s="7"/>
     </row>
-    <row r="101" spans="1:8" ht="27">
+    <row r="101" spans="1:8" ht="40.5">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7" t="s">
-        <v>109</v>
+      <c r="C101" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D101" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E101" s="21"/>
+      <c r="F101" s="21" t="s">
+        <v>108</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
@@ -4021,61 +4151,61 @@
     <row r="102" spans="1:8">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7" t="s">
-        <v>108</v>
+      <c r="C102" s="20"/>
+      <c r="D102" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E102" s="21"/>
+      <c r="F102" s="21" t="s">
+        <v>166</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
     </row>
     <row r="103" spans="1:8" ht="40.5">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H103" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+      <c r="A103" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" ht="27">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G104" s="7"/>
       <c r="H104" s="7"/>
     </row>
-    <row r="105" spans="1:8" ht="40.5">
+    <row r="105" spans="1:8">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
-      <c r="C105" s="8" t="s">
-        <v>143</v>
-      </c>
+      <c r="C105" s="8"/>
       <c r="D105" s="7" t="s">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
@@ -4085,97 +4215,97 @@
       <c r="B106" s="7"/>
       <c r="C106" s="8"/>
       <c r="D106" s="7" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8" ht="40.5">
-      <c r="A107" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H107" s="4"/>
-    </row>
-    <row r="108" spans="1:8" ht="27">
+    <row r="107" spans="1:8" ht="27">
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G107" s="7"/>
+      <c r="H107" s="7"/>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="7"/>
+      <c r="D108" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="E108" s="7"/>
       <c r="F108" s="7" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" ht="27">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="8"/>
       <c r="D109" s="7" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="7" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" ht="27">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
-      <c r="C110" s="8"/>
+      <c r="C110" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D110" s="7" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="G110" s="7"/>
+      <c r="G110" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="H110" s="7"/>
     </row>
-    <row r="111" spans="1:8" ht="27">
+    <row r="111" spans="1:8">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="8"/>
       <c r="D111" s="7" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="G111" s="7"/>
+      <c r="G111" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H111" s="7"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" ht="27">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="8"/>
       <c r="D112" s="7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="7" t="s">
@@ -4188,12 +4318,10 @@
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="8"/>
-      <c r="D113" s="7" t="s">
-        <v>35</v>
-      </c>
+      <c r="D113" s="7"/>
       <c r="E113" s="7"/>
       <c r="F113" s="7" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
@@ -4201,99 +4329,95 @@
     <row r="114" spans="1:8" ht="27">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
-      <c r="C114" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="C114" s="8"/>
       <c r="D114" s="7" t="s">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G114" s="7" t="s">
-        <v>46</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="G114" s="7"/>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" ht="27">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="8"/>
       <c r="D115" s="7" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="E115" s="7"/>
       <c r="F115" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G115" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="G115" s="7"/>
       <c r="H115" s="7"/>
     </row>
-    <row r="116" spans="1:8" ht="27">
+    <row r="116" spans="1:8">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="8"/>
-      <c r="D116" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="D116" s="7"/>
       <c r="E116" s="7"/>
       <c r="F116" s="7" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
     </row>
-    <row r="117" spans="1:8" ht="27">
+    <row r="117" spans="1:8">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="8"/>
-      <c r="D117" s="7"/>
+      <c r="D117" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E117" s="7"/>
       <c r="F117" s="7" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" ht="27">
+    <row r="118" spans="1:8" ht="40.5">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
-      <c r="C118" s="8"/>
+      <c r="C118" s="8" t="s">
+        <v>143</v>
+      </c>
       <c r="D118" s="7" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8" ht="27">
+    <row r="119" spans="1:8">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
-      <c r="D119" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="D119" s="7"/>
       <c r="E119" s="7"/>
       <c r="F119" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" ht="27">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="8"/>
-      <c r="D120" s="7"/>
+      <c r="D120" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
@@ -4302,40 +4426,44 @@
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="8"/>
-      <c r="D121" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="D121" s="7"/>
       <c r="E121" s="7"/>
       <c r="F121" s="7" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
     </row>
     <row r="122" spans="1:8" ht="40.5">
-      <c r="A122" s="7"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G122" s="7"/>
-      <c r="H122" s="7"/>
-    </row>
-    <row r="123" spans="1:8">
+      <c r="A122" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H122" s="4"/>
+    </row>
+    <row r="123" spans="1:8" ht="27">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="8"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
       <c r="F123" s="7" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
@@ -4345,11 +4473,11 @@
       <c r="B124" s="7"/>
       <c r="C124" s="8"/>
       <c r="D124" s="7" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
@@ -4361,41 +4489,33 @@
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
     </row>
-    <row r="126" spans="1:8" ht="40.5">
-      <c r="A126" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E126" s="4"/>
-      <c r="F126" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H126" s="4"/>
-    </row>
-    <row r="127" spans="1:8" ht="27">
+    <row r="126" spans="1:8" ht="27">
+      <c r="A126" s="7"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="8"/>
+      <c r="D126" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="8"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
@@ -4405,7 +4525,7 @@
       <c r="B128" s="7"/>
       <c r="C128" s="8"/>
       <c r="D128" s="7" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E128" s="7"/>
       <c r="F128" s="7" t="s">
@@ -4431,7 +4551,7 @@
       <c r="B130" s="7"/>
       <c r="C130" s="8"/>
       <c r="D130" s="7" t="s">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="E130" s="7"/>
       <c r="F130" s="7" t="s">
@@ -4457,7 +4577,7 @@
       <c r="B132" s="7"/>
       <c r="C132" s="8"/>
       <c r="D132" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E132" s="7"/>
       <c r="F132" s="7" t="s">
@@ -4478,30 +4598,38 @@
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
     </row>
-    <row r="134" spans="1:8" ht="27">
+    <row r="134" spans="1:8" ht="40.5">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
-      <c r="C134" s="8"/>
+      <c r="C134" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D134" s="7" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G134" s="7"/>
+        <v>179</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="H134" s="7"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="8"/>
-      <c r="D135" s="7"/>
+      <c r="D135" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="E135" s="7"/>
       <c r="F135" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G135" s="7"/>
+        <v>179</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H135" s="7"/>
     </row>
     <row r="136" spans="1:8" ht="27">
@@ -4509,43 +4637,41 @@
       <c r="B136" s="7"/>
       <c r="C136" s="8"/>
       <c r="D136" s="7" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E136" s="7"/>
       <c r="F136" s="7" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" ht="27">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="8"/>
-      <c r="D137" s="7"/>
+      <c r="D137" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="E137" s="7"/>
       <c r="F137" s="7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
     </row>
-    <row r="138" spans="1:8" ht="40.5">
+    <row r="138" spans="1:8">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
-      <c r="C138" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="C138" s="8"/>
       <c r="D138" s="7" t="s">
-        <v>182</v>
+        <v>26</v>
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="G138" s="7"/>
       <c r="H138" s="7"/>
     </row>
     <row r="139" spans="1:8">
@@ -4553,268 +4679,270 @@
       <c r="B139" s="7"/>
       <c r="C139" s="8"/>
       <c r="D139" s="7" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="E139" s="7"/>
       <c r="F139" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="G139" s="7"/>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" ht="27">
+    <row r="140" spans="1:8" ht="40.5">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="8"/>
+      <c r="C140" s="8" t="s">
+        <v>143</v>
+      </c>
       <c r="D140" s="7" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G140" s="7"/>
       <c r="H140" s="7"/>
     </row>
-    <row r="141" spans="1:8" ht="27">
+    <row r="141" spans="1:8">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="8"/>
       <c r="D141" s="7" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="7" t="s">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="G141" s="7"/>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8">
-      <c r="A142" s="7"/>
-      <c r="B142" s="7"/>
-      <c r="C142" s="8"/>
-      <c r="D142" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="G142" s="7"/>
-      <c r="H142" s="7"/>
-    </row>
-    <row r="143" spans="1:8">
+    <row r="142" spans="1:8" ht="40.5">
+      <c r="A142" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H142" s="4"/>
+    </row>
+    <row r="143" spans="1:8" ht="27">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
-      <c r="C143" s="8"/>
-      <c r="D143" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="C143" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D143" s="7"/>
       <c r="E143" s="7"/>
       <c r="F143" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G143" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="H143" s="7"/>
     </row>
-    <row r="144" spans="1:8" ht="40.5">
+    <row r="144" spans="1:8" ht="27">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
-      <c r="C144" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D144" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="C144" s="8"/>
+      <c r="D144" s="7"/>
       <c r="E144" s="7"/>
       <c r="F144" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="G144" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="H144" s="7"/>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" ht="27">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
       <c r="C145" s="8"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7"/>
       <c r="F145" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="G145" s="7"/>
+        <v>42</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="H145" s="7"/>
     </row>
     <row r="146" spans="1:8" ht="27">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="8"/>
-      <c r="D146" s="7" t="s">
-        <v>146</v>
-      </c>
+      <c r="D146" s="7"/>
       <c r="E146" s="7"/>
       <c r="F146" s="7" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="G146" s="7"/>
       <c r="H146" s="7"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" ht="27">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
       <c r="C147" s="8"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
       <c r="F147" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G147" s="7"/>
       <c r="H147" s="7"/>
     </row>
-    <row r="148" spans="1:8" ht="40.5">
-      <c r="A148" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E148" s="4"/>
-      <c r="F148" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G148" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H148" s="4"/>
-    </row>
-    <row r="149" spans="1:8" ht="27">
+    <row r="148" spans="1:8" ht="27">
+      <c r="A148" s="7"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
-      <c r="C149" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="C149" s="8"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
       <c r="F149" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G149" s="7" t="s">
-        <v>44</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="G149" s="7"/>
       <c r="H149" s="7"/>
     </row>
-    <row r="150" spans="1:8" ht="27">
+    <row r="150" spans="1:8">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="8"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
       <c r="F150" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G150" s="7" t="s">
-        <v>43</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="G150" s="7"/>
       <c r="H150" s="7"/>
     </row>
-    <row r="151" spans="1:8" ht="27">
-      <c r="A151" s="7"/>
-      <c r="B151" s="7"/>
-      <c r="C151" s="8"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G151" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H151" s="7"/>
-    </row>
-    <row r="152" spans="1:8" ht="27">
+    <row r="151" spans="1:8" ht="54">
+      <c r="A151" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D151" s="4"/>
+      <c r="E151" s="11"/>
+      <c r="F151" s="4"/>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4"/>
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="8"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
-      <c r="F152" s="7" t="s">
-        <v>116</v>
-      </c>
+      <c r="F152" s="7"/>
       <c r="G152" s="7"/>
       <c r="H152" s="7"/>
     </row>
     <row r="153" spans="1:8" ht="27">
-      <c r="A153" s="7"/>
-      <c r="B153" s="7"/>
-      <c r="C153" s="8"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="G153" s="7"/>
-      <c r="H153" s="7"/>
-    </row>
-    <row r="154" spans="1:8" ht="27">
+      <c r="A153" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D153" s="4"/>
+      <c r="E153" s="11"/>
+      <c r="F153" s="4"/>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="8"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
-      <c r="F154" s="7" t="s">
-        <v>113</v>
-      </c>
+      <c r="F154" s="7"/>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
     </row>
-    <row r="155" spans="1:8">
-      <c r="A155" s="7"/>
-      <c r="B155" s="7"/>
-      <c r="C155" s="8"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G155" s="7"/>
-      <c r="H155" s="7"/>
-    </row>
-    <row r="156" spans="1:8">
+    <row r="155" spans="1:8" ht="27">
+      <c r="A155" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" s="11"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H155" s="4"/>
+    </row>
+    <row r="156" spans="1:8" ht="27">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="8"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
       <c r="F156" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="G156" s="7"/>
+        <v>129</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8" ht="54">
-      <c r="A157" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C157" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D157" s="4"/>
-      <c r="E157" s="11"/>
-      <c r="F157" s="4"/>
-      <c r="G157" s="4"/>
-      <c r="H157" s="4"/>
+    <row r="157" spans="1:8">
+      <c r="A157" s="7"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H157" s="7"/>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="7"/>
@@ -4822,67 +4950,73 @@
       <c r="C158" s="8"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-      <c r="G158" s="7"/>
+      <c r="F158" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H158" s="7"/>
     </row>
-    <row r="159" spans="1:8" ht="27">
-      <c r="A159" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B159" s="4" t="s">
+    <row r="159" spans="1:8">
+      <c r="A159" s="7"/>
+      <c r="B159" s="7"/>
+      <c r="C159" s="8"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H159" s="7"/>
+    </row>
+    <row r="160" spans="1:8" ht="27">
+      <c r="A160" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B160" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C159" s="11" t="s">
+      <c r="C160" s="11"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H160" s="4"/>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="7"/>
+      <c r="B161" s="7"/>
+      <c r="C161" s="8"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G161" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D159" s="4"/>
-      <c r="E159" s="11"/>
-      <c r="F159" s="4"/>
-      <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
-    </row>
-    <row r="160" spans="1:8">
-      <c r="A160" s="7"/>
-      <c r="B160" s="7"/>
-      <c r="C160" s="8"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="7"/>
-      <c r="G160" s="7"/>
-      <c r="H160" s="7"/>
-    </row>
-    <row r="161" spans="1:8" ht="27">
-      <c r="A161" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C161" s="11"/>
-      <c r="D161" s="4"/>
-      <c r="E161" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F161" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G161" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H161" s="4"/>
-    </row>
-    <row r="162" spans="1:8" ht="27">
+      <c r="H161" s="7"/>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="8"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
       <c r="F162" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="H162" s="7"/>
     </row>
@@ -4893,7 +5027,7 @@
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
       <c r="F163" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>37</v>
@@ -4907,163 +5041,159 @@
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>37</v>
       </c>
       <c r="H164" s="7"/>
     </row>
-    <row r="165" spans="1:8">
-      <c r="A165" s="7"/>
-      <c r="B165" s="7"/>
-      <c r="C165" s="8"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="G165" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H165" s="7"/>
-    </row>
-    <row r="166" spans="1:8" ht="27">
-      <c r="A166" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C166" s="11"/>
-      <c r="D166" s="4"/>
-      <c r="E166" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F166" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G166" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H166" s="4"/>
-    </row>
-    <row r="167" spans="1:8">
-      <c r="A167" s="7"/>
-      <c r="B167" s="7"/>
-      <c r="C167" s="8"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G167" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H167" s="7"/>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="A168" s="7"/>
-      <c r="B168" s="7"/>
+    <row r="165" spans="1:8" ht="39" customHeight="1">
+      <c r="A165" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C165" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4"/>
+      <c r="G165" s="4"/>
+      <c r="H165" s="4"/>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="7"/>
+      <c r="B166" s="7"/>
+      <c r="C166" s="8"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
+    </row>
+    <row r="167" spans="1:8" ht="54">
+      <c r="A167" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D167" s="5"/>
+      <c r="E167" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H167" s="4"/>
+    </row>
+    <row r="168" spans="1:8" ht="27">
+      <c r="A168" s="8"/>
+      <c r="B168" s="8"/>
       <c r="C168" s="8"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
       <c r="F168" s="7" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="G168" s="7" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="H168" s="7"/>
     </row>
-    <row r="169" spans="1:8">
-      <c r="A169" s="7"/>
-      <c r="B169" s="7"/>
+    <row r="169" spans="1:8" ht="27">
+      <c r="A169" s="8"/>
+      <c r="B169" s="8"/>
       <c r="C169" s="8"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
-      <c r="F169" s="7" t="s">
-        <v>131</v>
+      <c r="F169" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="H169" s="7"/>
     </row>
-    <row r="170" spans="1:8">
-      <c r="A170" s="7"/>
-      <c r="B170" s="7"/>
+    <row r="170" spans="1:8" ht="27">
+      <c r="A170" s="8"/>
+      <c r="B170" s="8"/>
       <c r="C170" s="8"/>
       <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
+      <c r="E170" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="F170" s="7" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="H170" s="7"/>
     </row>
-    <row r="171" spans="1:8" ht="39" customHeight="1">
-      <c r="A171" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C171" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D171" s="4"/>
-      <c r="E171" s="4"/>
-      <c r="F171" s="4"/>
-      <c r="G171" s="4"/>
-      <c r="H171" s="4"/>
-    </row>
-    <row r="172" spans="1:8">
-      <c r="A172" s="7"/>
-      <c r="B172" s="7"/>
+    <row r="171" spans="1:8">
+      <c r="A171" s="8"/>
+      <c r="B171" s="8"/>
+      <c r="C171" s="8"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G171" s="7"/>
+      <c r="H171" s="7"/>
+    </row>
+    <row r="172" spans="1:8" ht="27">
+      <c r="A172" s="8"/>
+      <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
-      <c r="G172" s="7"/>
+      <c r="F172" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="H172" s="7"/>
     </row>
-    <row r="173" spans="1:8" ht="54">
-      <c r="A173" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D173" s="5"/>
-      <c r="E173" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F173" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G173" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="H173" s="4"/>
-    </row>
-    <row r="174" spans="1:8" ht="27">
+    <row r="173" spans="1:8" ht="27">
+      <c r="A173" s="8"/>
+      <c r="B173" s="8"/>
+      <c r="C173" s="8"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H173" s="7"/>
+    </row>
+    <row r="174" spans="1:8" ht="40.5">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
-      <c r="C174" s="8"/>
+      <c r="C174" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
+      <c r="E174" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="F174" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G174" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="G174" s="7"/>
       <c r="H174" s="7"/>
     </row>
     <row r="175" spans="1:8" ht="27">
@@ -5072,12 +5202,10 @@
       <c r="C175" s="8"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
-      <c r="F175" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G175" s="7" t="s">
-        <v>72</v>
-      </c>
+      <c r="F175" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G175" s="7"/>
       <c r="H175" s="7"/>
     </row>
     <row r="176" spans="1:8" ht="27">
@@ -5085,109 +5213,107 @@
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
       <c r="D176" s="7"/>
-      <c r="E176" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F176" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="E176" s="7"/>
+      <c r="F176" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G176" s="7"/>
       <c r="H176" s="7"/>
     </row>
-    <row r="177" spans="1:8">
-      <c r="A177" s="8"/>
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="7"/>
+    <row r="177" spans="1:8" ht="40.5">
+      <c r="A177" s="7"/>
+      <c r="B177" s="7"/>
+      <c r="C177" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="E177" s="7"/>
-      <c r="F177" s="13" t="s">
-        <v>54</v>
+      <c r="F177" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
     </row>
     <row r="178" spans="1:8" ht="27">
-      <c r="A178" s="8"/>
-      <c r="B178" s="8"/>
+      <c r="A178" s="7"/>
+      <c r="B178" s="7"/>
       <c r="C178" s="8"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
       <c r="F178" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="G178" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G178" s="7"/>
       <c r="H178" s="7"/>
     </row>
-    <row r="179" spans="1:8" ht="27">
-      <c r="A179" s="8"/>
-      <c r="B179" s="8"/>
+    <row r="179" spans="1:8">
+      <c r="A179" s="7"/>
+      <c r="B179" s="7"/>
       <c r="C179" s="8"/>
-      <c r="D179" s="7"/>
+      <c r="D179" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="E179" s="7"/>
       <c r="F179" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G179" s="7" t="s">
-        <v>190</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="G179" s="7"/>
       <c r="H179" s="7"/>
     </row>
-    <row r="180" spans="1:8" ht="40.5">
-      <c r="A180" s="8"/>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8" t="s">
-        <v>50</v>
-      </c>
+    <row r="180" spans="1:8" ht="27">
+      <c r="A180" s="7"/>
+      <c r="B180" s="7"/>
+      <c r="C180" s="8"/>
       <c r="D180" s="7"/>
-      <c r="E180" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="E180" s="7"/>
       <c r="F180" s="7" t="s">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="G180" s="7"/>
       <c r="H180" s="7"/>
     </row>
-    <row r="181" spans="1:8" ht="27">
-      <c r="A181" s="8"/>
-      <c r="B181" s="8"/>
-      <c r="C181" s="8"/>
-      <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
-      <c r="F181" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G181" s="7"/>
-      <c r="H181" s="7"/>
+    <row r="181" spans="1:8" ht="40.5">
+      <c r="A181" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D181" s="5"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H181" s="4"/>
     </row>
     <row r="182" spans="1:8" ht="27">
-      <c r="A182" s="8"/>
-      <c r="B182" s="8"/>
+      <c r="A182" s="7"/>
+      <c r="B182" s="7"/>
       <c r="C182" s="8"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
-      <c r="F182" s="12" t="s">
-        <v>51</v>
+      <c r="F182" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
     </row>
-    <row r="183" spans="1:8" ht="40.5">
+    <row r="183" spans="1:8" ht="27">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
-      <c r="C183" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D183" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="C183" s="8"/>
+      <c r="D183" s="7"/>
       <c r="E183" s="7"/>
       <c r="F183" s="7" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
@@ -5195,60 +5321,60 @@
     <row r="184" spans="1:8" ht="27">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
-      <c r="C184" s="8"/>
+      <c r="C184" s="8" t="s">
+        <v>191</v>
+      </c>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7" t="s">
-        <v>81</v>
+        <v>190</v>
       </c>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
     </row>
-    <row r="185" spans="1:8">
-      <c r="A185" s="7"/>
-      <c r="B185" s="7"/>
-      <c r="C185" s="8"/>
-      <c r="D185" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G185" s="7"/>
-      <c r="H185" s="7"/>
-    </row>
-    <row r="186" spans="1:8" ht="27">
-      <c r="A186" s="7"/>
-      <c r="B186" s="7"/>
+    <row r="185" spans="1:8" ht="40.5">
+      <c r="A185" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D185" s="5"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="4"/>
+      <c r="H185" s="4"/>
+    </row>
+    <row r="186" spans="1:8">
       <c r="C186" s="8"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
-      <c r="F186" s="7" t="s">
-        <v>81</v>
-      </c>
+      <c r="F186" s="7"/>
       <c r="G186" s="7"/>
       <c r="H186" s="7"/>
     </row>
     <row r="187" spans="1:8" ht="40.5">
       <c r="A187" s="4" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D187" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="D187" s="4"/>
       <c r="E187" s="4"/>
       <c r="F187" s="4"/>
       <c r="G187" s="4"/>
       <c r="H187" s="4"/>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="7"/>
-      <c r="B188" s="7"/>
+      <c r="A188" s="8"/>
+      <c r="B188" s="8"/>
       <c r="C188" s="8"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
@@ -5256,74 +5382,24 @@
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
     </row>
-    <row r="189" spans="1:8" ht="40.5">
-      <c r="A189" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D189" s="5"/>
-      <c r="E189" s="4"/>
-      <c r="F189" s="4"/>
-      <c r="G189" s="4"/>
-      <c r="H189" s="4"/>
+    <row r="189" spans="1:8">
+      <c r="A189" s="8"/>
+      <c r="B189" s="8"/>
+      <c r="C189" s="8"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
     </row>
     <row r="190" spans="1:8">
-      <c r="C190" s="8"/>
-      <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
-      <c r="G190" s="7"/>
-      <c r="H190" s="7"/>
-    </row>
-    <row r="191" spans="1:8" ht="40.5">
-      <c r="A191" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B191" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D191" s="4"/>
-      <c r="E191" s="4"/>
-      <c r="F191" s="4"/>
-      <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
-    </row>
-    <row r="192" spans="1:8">
-      <c r="A192" s="8"/>
-      <c r="B192" s="8"/>
-      <c r="C192" s="8"/>
-      <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
-      <c r="G192" s="7"/>
-      <c r="H192" s="7"/>
-    </row>
-    <row r="193" spans="1:8">
-      <c r="A193" s="8"/>
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
-      <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
-      <c r="G193" s="7"/>
-      <c r="H193" s="7"/>
-    </row>
-    <row r="194" spans="1:8">
-      <c r="D194" s="9"/>
-      <c r="E194" s="9"/>
-      <c r="F194" s="9"/>
-      <c r="G194" s="9"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="9"/>
+      <c r="F190" s="9"/>
+      <c r="G190" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H104">
+  <autoFilter ref="A1:H100">
     <filterColumn colId="4"/>
   </autoFilter>
   <mergeCells count="1">

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -918,7 +918,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="192">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1132,10 +1132,6 @@
   </si>
   <si>
     <t>反复多次启停coord节点、catalog节点、dataRG节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改一个主机的hostname</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2350,6 +2346,12 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2358,12 +2360,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2705,16 +2701,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="40.5">
       <c r="A3" s="4" t="s">
@@ -2727,14 +2723,14 @@
         <v>34</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H3" s="11"/>
     </row>
@@ -2745,10 +2741,10 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H4" s="7"/>
     </row>
@@ -2765,7 +2761,7 @@
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2775,7 +2771,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -2787,10 +2783,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H7" s="7"/>
     </row>
@@ -2815,10 +2811,10 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H9" s="7"/>
     </row>
@@ -2829,10 +2825,10 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -2843,10 +2839,10 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H11" s="7"/>
     </row>
@@ -2855,17 +2851,17 @@
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
       <c r="D12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27">
@@ -2875,10 +2871,10 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H13" s="7"/>
     </row>
@@ -2893,10 +2889,10 @@
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H14" s="7"/>
     </row>
@@ -2907,10 +2903,10 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H15" s="7"/>
     </row>
@@ -2919,7 +2915,7 @@
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
       <c r="D16" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
@@ -2927,7 +2923,7 @@
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2937,7 +2933,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -2945,40 +2941,40 @@
     <row r="18" spans="1:8" ht="54">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21" t="s">
-        <v>59</v>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" ht="27">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21" t="s">
+      <c r="C19" s="17"/>
+      <c r="D19" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" ht="40.5">
       <c r="A20" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
@@ -2987,7 +2983,7 @@
         <v>34</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
@@ -3005,7 +3001,7 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -3015,7 +3011,7 @@
       <c r="B22" s="7"/>
       <c r="C22" s="8"/>
       <c r="D22" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>31</v>
@@ -3045,7 +3041,7 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7" t="s">
@@ -3059,7 +3055,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -3073,13 +3069,13 @@
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="54">
@@ -3089,13 +3085,13 @@
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27">
@@ -3105,10 +3101,10 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H28" s="7"/>
     </row>
@@ -3133,10 +3129,10 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H30" s="7"/>
     </row>
@@ -3147,10 +3143,10 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H31" s="7"/>
     </row>
@@ -3161,10 +3157,10 @@
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H32" s="7"/>
     </row>
@@ -3173,17 +3169,17 @@
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
       <c r="D33" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="27">
@@ -3193,10 +3189,10 @@
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H34" s="7"/>
     </row>
@@ -3207,11 +3203,11 @@
         <v>50</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
@@ -3223,7 +3219,7 @@
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
@@ -3237,13 +3233,13 @@
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27">
@@ -3253,25 +3249,25 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H38" s="7"/>
     </row>
     <row r="39" spans="1:8" ht="40.5">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="D39" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21" t="s">
-        <v>150</v>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
@@ -3279,13 +3275,13 @@
     <row r="40" spans="1:8">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21" t="s">
-        <v>165</v>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18" t="s">
+        <v>164</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -3301,14 +3297,14 @@
         <v>34</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H41" s="11"/>
     </row>
@@ -3319,7 +3315,7 @@
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
@@ -3333,7 +3329,7 @@
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -3345,7 +3341,7 @@
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
@@ -3357,7 +3353,7 @@
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
@@ -3367,15 +3363,15 @@
       <c r="B46" s="7"/>
       <c r="C46" s="8"/>
       <c r="D46" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -3385,7 +3381,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
@@ -3395,11 +3391,11 @@
       <c r="B48" s="7"/>
       <c r="C48" s="8"/>
       <c r="D48" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -3411,10 +3407,10 @@
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H49" s="7"/>
     </row>
@@ -3425,7 +3421,7 @@
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -3437,10 +3433,10 @@
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H51" s="7"/>
     </row>
@@ -3449,17 +3445,17 @@
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
       <c r="D52" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="27">
@@ -3469,10 +3465,10 @@
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H53" s="7"/>
     </row>
@@ -3487,7 +3483,7 @@
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -3499,7 +3495,7 @@
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
@@ -3511,7 +3507,7 @@
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -3521,15 +3517,15 @@
       <c r="B57" s="7"/>
       <c r="C57" s="8"/>
       <c r="D57" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -3539,7 +3535,7 @@
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -3547,15 +3543,15 @@
     <row r="59" spans="1:8" ht="40.5">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D59" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="D59" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21" t="s">
-        <v>137</v>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
@@ -3563,20 +3559,20 @@
     <row r="60" spans="1:8">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21" t="s">
-        <v>137</v>
+      <c r="C60" s="17"/>
+      <c r="D60" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
     <row r="61" spans="1:8" ht="40.5">
       <c r="A61" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>10</v>
@@ -3603,7 +3599,7 @@
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -3615,7 +3611,7 @@
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -3625,11 +3621,11 @@
       <c r="B64" s="7"/>
       <c r="C64" s="8"/>
       <c r="D64" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -3641,7 +3637,7 @@
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
@@ -3651,11 +3647,11 @@
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
       <c r="D66" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
@@ -3667,7 +3663,7 @@
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -3681,7 +3677,7 @@
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -3693,7 +3689,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -3703,11 +3699,11 @@
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
       <c r="D70" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -3719,7 +3715,7 @@
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -3733,7 +3729,7 @@
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -3745,7 +3741,7 @@
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -3759,7 +3755,7 @@
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
@@ -3771,7 +3767,7 @@
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
@@ -3785,7 +3781,7 @@
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
@@ -3797,7 +3793,7 @@
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
@@ -3809,17 +3805,17 @@
         <v>25</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>36</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3827,11 +3823,11 @@
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
       <c r="D79" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>37</v>
@@ -3847,7 +3843,7 @@
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -3861,25 +3857,25 @@
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="40.5">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="20" t="s">
+      <c r="C82" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D82" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="D82" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21" t="s">
-        <v>186</v>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18" t="s">
+        <v>185</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
@@ -3887,11 +3883,11 @@
     <row r="83" spans="1:8">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21" t="s">
-        <v>186</v>
+      <c r="C83" s="17"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18" t="s">
+        <v>185</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
@@ -3925,7 +3921,7 @@
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
@@ -3937,7 +3933,7 @@
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
@@ -3947,11 +3943,11 @@
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
       <c r="D87" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
@@ -3963,7 +3959,7 @@
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
@@ -3977,7 +3973,7 @@
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
@@ -3989,7 +3985,7 @@
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
@@ -4003,7 +3999,7 @@
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
@@ -4015,7 +4011,7 @@
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
@@ -4025,11 +4021,11 @@
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
       <c r="D93" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
@@ -4041,7 +4037,7 @@
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
@@ -4055,7 +4051,7 @@
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
@@ -4067,7 +4063,7 @@
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
@@ -4081,7 +4077,7 @@
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
@@ -4093,7 +4089,7 @@
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
       <c r="F98" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
@@ -4107,13 +4103,13 @@
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>36</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -4125,7 +4121,7 @@
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G100" s="7" t="s">
         <v>37</v>
@@ -4135,15 +4131,15 @@
     <row r="101" spans="1:8" ht="40.5">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
-      <c r="C101" s="20" t="s">
+      <c r="C101" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D101" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="D101" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21" t="s">
-        <v>108</v>
+      <c r="E101" s="18"/>
+      <c r="F101" s="18" t="s">
+        <v>107</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
@@ -4151,20 +4147,20 @@
     <row r="102" spans="1:8">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
-      <c r="C102" s="20"/>
-      <c r="D102" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21" t="s">
-        <v>166</v>
+      <c r="C102" s="17"/>
+      <c r="D102" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E102" s="18"/>
+      <c r="F102" s="18" t="s">
+        <v>165</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
     </row>
     <row r="103" spans="1:8" ht="40.5">
       <c r="A103" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>10</v>
@@ -4177,7 +4173,7 @@
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>45</v>
@@ -4191,7 +4187,7 @@
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
@@ -4201,11 +4197,11 @@
       <c r="B105" s="7"/>
       <c r="C105" s="8"/>
       <c r="D105" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
@@ -4215,11 +4211,11 @@
       <c r="B106" s="7"/>
       <c r="C106" s="8"/>
       <c r="D106" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
@@ -4233,7 +4229,7 @@
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
@@ -4247,7 +4243,7 @@
       </c>
       <c r="E108" s="7"/>
       <c r="F108" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
@@ -4261,7 +4257,7 @@
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
@@ -4273,11 +4269,11 @@
         <v>25</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G110" s="7" t="s">
         <v>46</v>
@@ -4289,11 +4285,11 @@
       <c r="B111" s="7"/>
       <c r="C111" s="8"/>
       <c r="D111" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G111" s="7" t="s">
         <v>37</v>
@@ -4309,7 +4305,7 @@
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
@@ -4321,7 +4317,7 @@
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
       <c r="F113" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
@@ -4335,7 +4331,7 @@
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
@@ -4349,7 +4345,7 @@
       </c>
       <c r="E115" s="7"/>
       <c r="F115" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
@@ -4361,7 +4357,7 @@
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
       <c r="F116" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
@@ -4375,7 +4371,7 @@
       </c>
       <c r="E117" s="7"/>
       <c r="F117" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
@@ -4384,14 +4380,14 @@
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D118" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
@@ -4403,7 +4399,7 @@
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
       <c r="F119" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
@@ -4413,11 +4409,11 @@
       <c r="B120" s="7"/>
       <c r="C120" s="8"/>
       <c r="D120" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
@@ -4429,7 +4425,7 @@
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
       <c r="F121" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
@@ -4449,7 +4445,7 @@
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G122" s="4" t="s">
         <v>30</v>
@@ -4463,7 +4459,7 @@
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
       <c r="F123" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
@@ -4473,11 +4469,11 @@
       <c r="B124" s="7"/>
       <c r="C124" s="8"/>
       <c r="D124" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
@@ -4489,7 +4485,7 @@
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
@@ -4499,11 +4495,11 @@
       <c r="B126" s="7"/>
       <c r="C126" s="8"/>
       <c r="D126" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E126" s="7"/>
       <c r="F126" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
@@ -4515,7 +4511,7 @@
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
@@ -4529,7 +4525,7 @@
       </c>
       <c r="E128" s="7"/>
       <c r="F128" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="7"/>
@@ -4541,7 +4537,7 @@
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
@@ -4555,7 +4551,7 @@
       </c>
       <c r="E130" s="7"/>
       <c r="F130" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
@@ -4567,7 +4563,7 @@
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="7"/>
@@ -4581,7 +4577,7 @@
       </c>
       <c r="E132" s="7"/>
       <c r="F132" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
@@ -4593,7 +4589,7 @@
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
@@ -4605,11 +4601,11 @@
         <v>25</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G134" s="7" t="s">
         <v>36</v>
@@ -4621,11 +4617,11 @@
       <c r="B135" s="7"/>
       <c r="C135" s="8"/>
       <c r="D135" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E135" s="7"/>
       <c r="F135" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>37</v>
@@ -4641,7 +4637,7 @@
       </c>
       <c r="E136" s="7"/>
       <c r="F136" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
@@ -4655,7 +4651,7 @@
       </c>
       <c r="E137" s="7"/>
       <c r="F137" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
@@ -4669,7 +4665,7 @@
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G138" s="7"/>
       <c r="H138" s="7"/>
@@ -4683,7 +4679,7 @@
       </c>
       <c r="E139" s="7"/>
       <c r="F139" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G139" s="7"/>
       <c r="H139" s="7"/>
@@ -4692,14 +4688,14 @@
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D140" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G140" s="7"/>
       <c r="H140" s="7"/>
@@ -4709,31 +4705,31 @@
       <c r="B141" s="7"/>
       <c r="C141" s="8"/>
       <c r="D141" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G141" s="7"/>
       <c r="H141" s="7"/>
     </row>
     <row r="142" spans="1:8" ht="40.5">
       <c r="A142" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>30</v>
@@ -4791,7 +4787,7 @@
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
       <c r="F146" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G146" s="7"/>
       <c r="H146" s="7"/>
@@ -4803,7 +4799,7 @@
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
       <c r="F147" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G147" s="7"/>
       <c r="H147" s="7"/>
@@ -4815,7 +4811,7 @@
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
       <c r="F148" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G148" s="7"/>
       <c r="H148" s="7"/>
@@ -4827,7 +4823,7 @@
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
       <c r="F149" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G149" s="7"/>
       <c r="H149" s="7"/>
@@ -4839,20 +4835,20 @@
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
       <c r="F150" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G150" s="7"/>
       <c r="H150" s="7"/>
     </row>
     <row r="151" spans="1:8" ht="54">
       <c r="A151" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B151" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B151" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="C151" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D151" s="4"/>
       <c r="E151" s="11"/>
@@ -4872,7 +4868,7 @@
     </row>
     <row r="153" spans="1:8" ht="27">
       <c r="A153" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>7</v>
@@ -4898,7 +4894,7 @@
     </row>
     <row r="155" spans="1:8" ht="27">
       <c r="A155" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>7</v>
@@ -4906,13 +4902,13 @@
       <c r="C155" s="11"/>
       <c r="D155" s="4"/>
       <c r="E155" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H155" s="4"/>
     </row>
@@ -4923,10 +4919,10 @@
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
       <c r="F156" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H156" s="7"/>
     </row>
@@ -4937,7 +4933,7 @@
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
       <c r="F157" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G157" s="7" t="s">
         <v>37</v>
@@ -4951,7 +4947,7 @@
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
       <c r="F158" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>37</v>
@@ -4965,7 +4961,7 @@
       <c r="D159" s="7"/>
       <c r="E159" s="7"/>
       <c r="F159" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>37</v>
@@ -4974,7 +4970,7 @@
     </row>
     <row r="160" spans="1:8" ht="27">
       <c r="A160" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>7</v>
@@ -4982,13 +4978,13 @@
       <c r="C160" s="11"/>
       <c r="D160" s="4"/>
       <c r="E160" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H160" s="4"/>
     </row>
@@ -4999,7 +4995,7 @@
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
       <c r="F161" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>37</v>
@@ -5013,7 +5009,7 @@
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
       <c r="F162" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>37</v>
@@ -5027,7 +5023,7 @@
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
       <c r="F163" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>37</v>
@@ -5041,7 +5037,7 @@
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>37</v>
@@ -5050,13 +5046,13 @@
     </row>
     <row r="165" spans="1:8" ht="39" customHeight="1">
       <c r="A165" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
@@ -5076,23 +5072,23 @@
     </row>
     <row r="167" spans="1:8" ht="54">
       <c r="A167" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D167" s="5"/>
       <c r="E167" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H167" s="4"/>
     </row>
@@ -5106,7 +5102,7 @@
         <v>48</v>
       </c>
       <c r="G168" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H168" s="7"/>
     </row>
@@ -5117,10 +5113,10 @@
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
       <c r="F169" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H169" s="7"/>
     </row>
@@ -5129,14 +5125,12 @@
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
       <c r="D170" s="7"/>
-      <c r="E170" s="7" t="s">
-        <v>53</v>
-      </c>
+      <c r="E170" s="7"/>
       <c r="F170" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H170" s="7"/>
     </row>
@@ -5147,7 +5141,7 @@
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
       <c r="F171" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
@@ -5159,10 +5153,10 @@
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
       <c r="F172" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H172" s="7"/>
     </row>
@@ -5173,10 +5167,10 @@
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
       <c r="F173" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H173" s="7"/>
     </row>
@@ -5191,7 +5185,7 @@
         <v>52</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
@@ -5203,7 +5197,7 @@
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
       <c r="F175" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G175" s="7"/>
       <c r="H175" s="7"/>
@@ -5224,14 +5218,14 @@
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D177" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="D177" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="E177" s="7"/>
       <c r="F177" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
@@ -5243,7 +5237,7 @@
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
       <c r="F178" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G178" s="7"/>
       <c r="H178" s="7"/>
@@ -5253,11 +5247,11 @@
       <c r="B179" s="7"/>
       <c r="C179" s="8"/>
       <c r="D179" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E179" s="7"/>
       <c r="F179" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G179" s="7"/>
       <c r="H179" s="7"/>
@@ -5269,7 +5263,7 @@
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
       <c r="F180" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G180" s="7"/>
       <c r="H180" s="7"/>
@@ -5287,10 +5281,10 @@
       <c r="D181" s="5"/>
       <c r="E181" s="4"/>
       <c r="F181" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H181" s="4"/>
     </row>
@@ -5301,7 +5295,7 @@
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
       <c r="F182" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
@@ -5313,7 +5307,7 @@
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
       <c r="F183" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
@@ -5322,12 +5316,12 @@
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
@@ -5340,7 +5334,7 @@
         <v>7</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D185" s="5"/>
       <c r="E185" s="4"/>
@@ -5358,13 +5352,13 @@
     </row>
     <row r="187" spans="1:8" ht="40.5">
       <c r="A187" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -918,7 +918,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="196">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2068,35 +2068,51 @@
     <t>catalog主节点所在主机CPU耗尽</t>
   </si>
   <si>
+    <t>catalog主节点CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord节点与catalog主节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点与catalog备节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点与目标主机网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启停节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作失败；故障恢复后可以继续创建/删除节点组和节点，节点可以正常使用；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataNode（数据节点）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建coord节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>目标主机内存耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>catalog主节点CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源主机磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord节点与catalog主节点网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点与catalog备节点网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点与目标主机网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启停节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作失败；故障恢复后可以继续创建/删除节点组和节点，节点可以正常使用；</t>
+    <t>创建catalog节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3776,11 +3792,11 @@
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="8"/>
-      <c r="D76" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7" t="s">
+      <c r="D76" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14" t="s">
         <v>183</v>
       </c>
       <c r="G76" s="7"/>
@@ -3790,10 +3806,10 @@
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="8"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7" t="s">
-        <v>156</v>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14" t="s">
+        <v>175</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
@@ -3875,7 +3891,7 @@
       </c>
       <c r="E82" s="18"/>
       <c r="F82" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
@@ -3887,7 +3903,7 @@
       <c r="D83" s="18"/>
       <c r="E83" s="18"/>
       <c r="F83" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
@@ -3942,12 +3958,12 @@
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7" t="s">
-        <v>108</v>
+      <c r="D87" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14" t="s">
+        <v>193</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
@@ -3956,10 +3972,10 @@
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7" t="s">
-        <v>184</v>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14" t="s">
+        <v>194</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
@@ -3994,11 +4010,11 @@
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7" t="s">
+      <c r="D91" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14" t="s">
         <v>183</v>
       </c>
       <c r="G91" s="7"/>
@@ -4008,9 +4024,9 @@
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="8"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7" t="s">
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14" t="s">
         <v>103</v>
       </c>
       <c r="G92" s="7"/>
@@ -4709,7 +4725,7 @@
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G141" s="7"/>
       <c r="H141" s="7"/>
@@ -5281,10 +5297,10 @@
       <c r="D181" s="5"/>
       <c r="E181" s="4"/>
       <c r="F181" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H181" s="4"/>
     </row>
@@ -5295,7 +5311,7 @@
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
       <c r="F182" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
@@ -5307,7 +5323,7 @@
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
       <c r="F183" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
@@ -5316,12 +5332,12 @@
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_review.xlsx
@@ -918,7 +918,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="196">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4703,14 +4703,14 @@
     <row r="140" spans="1:8" ht="40.5">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D140" s="7" t="s">
+      <c r="D140" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7" t="s">
+      <c r="E140" s="18"/>
+      <c r="F140" s="18" t="s">
         <v>111</v>
       </c>
       <c r="G140" s="7"/>
@@ -4719,12 +4719,12 @@
     <row r="141" spans="1:8">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
-      <c r="C141" s="8"/>
-      <c r="D141" s="7" t="s">
+      <c r="C141" s="17"/>
+      <c r="D141" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E141" s="7"/>
-      <c r="F141" s="7" t="s">
+      <c r="E141" s="18"/>
+      <c r="F141" s="18" t="s">
         <v>185</v>
       </c>
       <c r="G141" s="7"/>
@@ -4740,9 +4740,7 @@
       <c r="C142" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D142" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="D142" s="4"/>
       <c r="E142" s="4"/>
       <c r="F142" s="4" t="s">
         <v>77</v>
